--- a/data/england/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/england/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP133"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13212,7 +13212,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>vTxmzPZG</t>
+          <t>hKbGXJpI</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -13220,61 +13220,61 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
+          <t xml:space="preserve">villa park
+  birmingham </t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>25586</v>
+        <v>42789</v>
       </c>
       <c r="F59" t="n">
-        <v>24298</v>
+        <v>42354</v>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>S66R0t75</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>2.58</v>
+        <v>0.85</v>
       </c>
       <c r="L59" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="M59" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="N59" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="O59" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P59" t="n">
         <v>21</v>
       </c>
       <c r="Q59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R59" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="S59" t="n">
         <v>13</v>
@@ -13284,19 +13284,19 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="W59" t="n">
         <v>48</v>
       </c>
       <c r="X59" t="n">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
@@ -13306,135 +13306,131 @@
       </c>
       <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr"/>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
+      <c r="AC59" t="inlineStr"/>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="AE59" t="n">
-        <v>24.27272727272727</v>
+        <v>26</v>
       </c>
       <c r="AF59" t="n">
-        <v>179.4545454545455</v>
+        <v>182.4545454545455</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.090909090909091</v>
+        <v>2.181818181818182</v>
       </c>
       <c r="AH59" t="n">
-        <v>69.72727272727273</v>
+        <v>80.18181818181819</v>
       </c>
       <c r="AI59" t="n">
-        <v>2984090.909090909</v>
+        <v>27100000</v>
       </c>
       <c r="AJ59" t="n">
-        <v>74.72727272727273</v>
+        <v>82</v>
       </c>
       <c r="AK59" t="n">
-        <v>26.27272727272727</v>
+        <v>24</v>
       </c>
       <c r="AL59" t="n">
-        <v>182.1818181818182</v>
+        <v>183.5555555555555</v>
       </c>
       <c r="AM59" t="n">
-        <v>1</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AN59" t="n">
-        <v>71.18181818181819</v>
+        <v>78.33333333333333</v>
       </c>
       <c r="AO59" t="n">
-        <v>2827272.727272727</v>
+        <v>19111111.11111111</v>
       </c>
       <c r="AP59" t="n">
-        <v>74.63636363636364</v>
+        <v>83.11111111111111</v>
       </c>
       <c r="AQ59" t="n">
-        <v>23.58823529411765</v>
+        <v>24.875</v>
       </c>
       <c r="AR59" t="n">
-        <v>181.5882352941177</v>
+        <v>183.5</v>
       </c>
       <c r="AS59" t="n">
-        <v>1</v>
+        <v>1.791666666666667</v>
       </c>
       <c r="AT59" t="n">
-        <v>69.82352941176471</v>
+        <v>75.75</v>
       </c>
       <c r="AU59" t="n">
-        <v>3104411.764705882</v>
+        <v>18576041.66666667</v>
       </c>
       <c r="AV59" t="n">
-        <v>75.94117647058823</v>
+        <v>80.41666666666667</v>
       </c>
       <c r="AW59" t="n">
-        <v>25.08333333333333</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AX59" t="n">
-        <v>183.5</v>
+        <v>186.3636363636364</v>
       </c>
       <c r="AY59" t="n">
-        <v>1</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="AZ59" t="n">
-        <v>69.58333333333333</v>
+        <v>72.63636363636364</v>
       </c>
       <c r="BA59" t="n">
-        <v>2429166.666666667</v>
+        <v>9713636.363636363</v>
       </c>
       <c r="BB59" t="n">
-        <v>74.33333333333333</v>
+        <v>81</v>
       </c>
       <c r="BC59" t="n">
-        <v>22</v>
+        <v>24.8</v>
       </c>
       <c r="BD59" t="n">
-        <v>178</v>
+        <v>184.4</v>
       </c>
       <c r="BE59" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="BF59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BG59" t="n">
-        <v>74</v>
+        <v>397</v>
       </c>
       <c r="BH59" t="n">
-        <v>9500000</v>
+        <v>114000000</v>
       </c>
       <c r="BI59" t="n">
-        <v>83</v>
+        <v>406</v>
       </c>
       <c r="BJ59" t="n">
-        <v>25.5</v>
+        <v>22.9</v>
       </c>
       <c r="BK59" t="n">
-        <v>182.5</v>
+        <v>181.6</v>
       </c>
       <c r="BL59" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="BM59" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BN59" t="n">
-        <v>140</v>
+        <v>767</v>
       </c>
       <c r="BO59" t="n">
-        <v>4500000</v>
+        <v>235050000</v>
       </c>
       <c r="BP59" t="n">
-        <v>145</v>
+        <v>826</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hKbGXJpI</t>
+          <t>vTxmzPZG</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -13442,61 +13438,61 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">kitchen a 
   eng </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>42789</v>
+        <v>25586</v>
       </c>
       <c r="F60" t="n">
-        <v>42354</v>
+        <v>24298</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>S66R0t75</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0.85</v>
+        <v>2.58</v>
       </c>
       <c r="L60" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="M60" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="N60" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="O60" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P60" t="n">
         <v>21</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R60" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="S60" t="n">
         <v>13</v>
@@ -13506,19 +13502,19 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>zuJM7XDg</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="W60" t="n">
         <v>48</v>
       </c>
       <c r="X60" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="Y60" t="n">
         <v>0</v>
@@ -13528,125 +13524,129 @@
       </c>
       <c r="AA60" t="inlineStr"/>
       <c r="AB60" t="inlineStr"/>
-      <c r="AC60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="AE60" t="n">
-        <v>26</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="AF60" t="n">
-        <v>182.4545454545455</v>
+        <v>179.4545454545455</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.181818181818182</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AH60" t="n">
-        <v>80.18181818181819</v>
+        <v>69.72727272727273</v>
       </c>
       <c r="AI60" t="n">
-        <v>27100000</v>
+        <v>2984090.909090909</v>
       </c>
       <c r="AJ60" t="n">
-        <v>82</v>
+        <v>74.72727272727273</v>
       </c>
       <c r="AK60" t="n">
-        <v>24</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="AL60" t="n">
-        <v>183.5555555555555</v>
+        <v>182.1818181818182</v>
       </c>
       <c r="AM60" t="n">
-        <v>1.777777777777778</v>
+        <v>1</v>
       </c>
       <c r="AN60" t="n">
-        <v>78.33333333333333</v>
+        <v>71.18181818181819</v>
       </c>
       <c r="AO60" t="n">
-        <v>19111111.11111111</v>
+        <v>2827272.727272727</v>
       </c>
       <c r="AP60" t="n">
-        <v>83.11111111111111</v>
+        <v>74.63636363636364</v>
       </c>
       <c r="AQ60" t="n">
-        <v>24.875</v>
+        <v>23.58823529411765</v>
       </c>
       <c r="AR60" t="n">
+        <v>181.5882352941177</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>69.82352941176471</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>3104411.764705882</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>75.94117647058823</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>25.08333333333333</v>
+      </c>
+      <c r="AX60" t="n">
         <v>183.5</v>
       </c>
-      <c r="AS60" t="n">
-        <v>1.791666666666667</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>75.75</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>18576041.66666667</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>80.41666666666667</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>23.90909090909091</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>186.3636363636364</v>
-      </c>
       <c r="AY60" t="n">
-        <v>1.545454545454545</v>
+        <v>1</v>
       </c>
       <c r="AZ60" t="n">
-        <v>72.63636363636364</v>
+        <v>69.58333333333333</v>
       </c>
       <c r="BA60" t="n">
-        <v>9713636.363636363</v>
+        <v>2429166.666666667</v>
       </c>
       <c r="BB60" t="n">
-        <v>81</v>
+        <v>74.33333333333333</v>
       </c>
       <c r="BC60" t="n">
-        <v>24.8</v>
+        <v>22</v>
       </c>
       <c r="BD60" t="n">
-        <v>184.4</v>
+        <v>178</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="BF60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BG60" t="n">
-        <v>397</v>
+        <v>74</v>
       </c>
       <c r="BH60" t="n">
-        <v>114000000</v>
+        <v>9500000</v>
       </c>
       <c r="BI60" t="n">
-        <v>406</v>
+        <v>83</v>
       </c>
       <c r="BJ60" t="n">
-        <v>22.9</v>
+        <v>25.5</v>
       </c>
       <c r="BK60" t="n">
-        <v>181.6</v>
+        <v>182.5</v>
       </c>
       <c r="BL60" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="BM60" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BN60" t="n">
-        <v>767</v>
+        <v>140</v>
       </c>
       <c r="BO60" t="n">
-        <v>235050000</v>
+        <v>4500000</v>
       </c>
       <c r="BP60" t="n">
-        <v>826</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61">
@@ -14084,7 +14084,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>4bSYk10n</t>
+          <t>hCzywRkb</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -14092,83 +14092,83 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">backhouse a 
   eng </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">ewood park
+  blackburn </t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>52305</v>
+        <v>31367</v>
       </c>
       <c r="F63" t="n">
-        <v>52196</v>
+        <v>20026</v>
       </c>
       <c r="G63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>MeKPSerA</t>
+          <t>GOvB22xg</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="L63" t="n">
-        <v>1.64</v>
+        <v>0.28</v>
       </c>
       <c r="M63" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="O63" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P63" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="n">
         <v>9</v>
       </c>
-      <c r="T63" t="n">
-        <v>10</v>
-      </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="W63" t="n">
         <v>48</v>
       </c>
       <c r="X63" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="Y63" t="n">
         <v>0</v>
@@ -14180,129 +14180,133 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr"/>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
       <c r="AE63" t="n">
-        <v>25.7</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="AF63" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AH63" t="n">
-        <v>77.59999999999999</v>
+        <v>70.18181818181819</v>
       </c>
       <c r="AI63" t="n">
-        <v>18970000</v>
+        <v>2213636.363636364</v>
       </c>
       <c r="AJ63" t="n">
-        <v>81.5</v>
+        <v>72.90909090909091</v>
       </c>
       <c r="AK63" t="n">
-        <v>24.09090909090909</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="AL63" t="n">
-        <v>181.8181818181818</v>
+        <v>181.4444444444445</v>
       </c>
       <c r="AM63" t="n">
         <v>1</v>
       </c>
       <c r="AN63" t="n">
-        <v>71.09090909090909</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="AO63" t="n">
-        <v>3847727.272727273</v>
+        <v>4200000</v>
       </c>
       <c r="AP63" t="n">
-        <v>76.72727272727273</v>
+        <v>77</v>
       </c>
       <c r="AQ63" t="n">
-        <v>26.08333333333333</v>
+        <v>20.8</v>
       </c>
       <c r="AR63" t="n">
-        <v>182.3333333333333</v>
+        <v>178.2666666666667</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AT63" t="n">
-        <v>72.75</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AU63" t="n">
-        <v>9826041.666666666</v>
+        <v>1715000</v>
       </c>
       <c r="AV63" t="n">
-        <v>77.75</v>
+        <v>76.06666666666666</v>
       </c>
       <c r="AW63" t="n">
-        <v>23.22222222222222</v>
+        <v>24.71428571428572</v>
       </c>
       <c r="AX63" t="n">
-        <v>179.5555555555555</v>
+        <v>182.9285714285714</v>
       </c>
       <c r="AY63" t="n">
         <v>1</v>
       </c>
       <c r="AZ63" t="n">
-        <v>68.55555555555556</v>
+        <v>68.42857142857143</v>
       </c>
       <c r="BA63" t="n">
-        <v>3094444.444444444</v>
+        <v>2507142.857142857</v>
       </c>
       <c r="BB63" t="n">
-        <v>75.88888888888889</v>
+        <v>74.07142857142857</v>
       </c>
       <c r="BC63" t="n">
-        <v>26.33333333333333</v>
+        <v>25.2</v>
       </c>
       <c r="BD63" t="n">
-        <v>185.1111111111111</v>
+        <v>179.6</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.888888888888889</v>
+        <v>1</v>
       </c>
       <c r="BF63" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BG63" t="n">
-        <v>721</v>
+        <v>345</v>
       </c>
       <c r="BH63" t="n">
-        <v>262600000</v>
+        <v>8800000</v>
       </c>
       <c r="BI63" t="n">
-        <v>744</v>
+        <v>364</v>
       </c>
       <c r="BJ63" t="n">
-        <v>25.75</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="BK63" t="n">
-        <v>182</v>
+        <v>178.6666666666667</v>
       </c>
       <c r="BL63" t="n">
         <v>1</v>
       </c>
       <c r="BM63" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BN63" t="n">
-        <v>562</v>
+        <v>211</v>
       </c>
       <c r="BO63" t="n">
-        <v>17700000</v>
+        <v>9000000</v>
       </c>
       <c r="BP63" t="n">
-        <v>599</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>nsKknJaB</t>
+          <t>4bSYk10n</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -14310,76 +14314,76 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>31750</v>
+        <v>52305</v>
       </c>
       <c r="F64" t="n">
-        <v>31531</v>
+        <v>52196</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H64" t="n">
         <v>1</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>SlybbadF</t>
+          <t>MeKPSerA</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>1.17</v>
+        <v>2.43</v>
       </c>
       <c r="L64" t="n">
-        <v>0.45</v>
+        <v>1.64</v>
       </c>
       <c r="M64" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N64" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O64" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="P64" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>7</v>
+      </c>
+      <c r="R64" t="n">
+        <v>5</v>
+      </c>
+      <c r="S64" t="n">
         <v>9</v>
       </c>
-      <c r="Q64" t="n">
-        <v>5</v>
-      </c>
-      <c r="R64" t="n">
-        <v>6</v>
-      </c>
-      <c r="S64" t="n">
-        <v>14</v>
-      </c>
       <c r="T64" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>MBpIn2MH</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="W64" t="n">
@@ -14396,110 +14400,110 @@
       </c>
       <c r="AA64" t="inlineStr"/>
       <c r="AB64" t="inlineStr"/>
-      <c r="AC64" t="inlineStr"/>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>185</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>18970000</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>181.8181818181818</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>3847727.272727273</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>76.72727272727273</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>26.08333333333333</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>9826041.666666666</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>179.5555555555555</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>3094444.444444444</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="BC64" t="n">
         <v>26.33333333333333</v>
       </c>
-      <c r="AF64" t="n">
-        <v>182.7777777777778</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.444444444444444</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>76.77777777777777</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>12888888.88888889</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>79.66666666666667</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>25.36363636363636</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>184.2727272727273</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>1.090909090909091</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>72.27272727272727</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>3927272.727272727</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>76</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>24.09090909090909</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>179.9090909090909</v>
-      </c>
-      <c r="AS64" t="n">
-        <v>1.363636363636364</v>
-      </c>
-      <c r="AT64" t="n">
-        <v>72.36363636363636</v>
-      </c>
-      <c r="AU64" t="n">
-        <v>8129545.454545454</v>
-      </c>
-      <c r="AV64" t="n">
-        <v>78.81818181818181</v>
-      </c>
-      <c r="AW64" t="n">
-        <v>28.0625</v>
-      </c>
-      <c r="AX64" t="n">
-        <v>183.3125</v>
-      </c>
-      <c r="AY64" t="n">
-        <v>1.1875</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>71.125</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>2609375</v>
-      </c>
-      <c r="BB64" t="n">
-        <v>72.3125</v>
-      </c>
-      <c r="BC64" t="n">
-        <v>26.25</v>
-      </c>
       <c r="BD64" t="n">
-        <v>180.5</v>
+        <v>185.1111111111111</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.5</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="BF64" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BG64" t="n">
-        <v>308</v>
+        <v>721</v>
       </c>
       <c r="BH64" t="n">
-        <v>52500000</v>
+        <v>262600000</v>
       </c>
       <c r="BI64" t="n">
-        <v>321</v>
+        <v>744</v>
       </c>
       <c r="BJ64" t="n">
-        <v>26.625</v>
+        <v>25.75</v>
       </c>
       <c r="BK64" t="n">
-        <v>182.5</v>
+        <v>182</v>
       </c>
       <c r="BL64" t="n">
         <v>1</v>
@@ -14508,19 +14512,19 @@
         <v>8</v>
       </c>
       <c r="BN64" t="n">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="BO64" t="n">
-        <v>24900000</v>
+        <v>17700000</v>
       </c>
       <c r="BP64" t="n">
-        <v>590</v>
+        <v>599</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Q7TUjsot</t>
+          <t>nsKknJaB</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -14528,76 +14532,76 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>75635</v>
+        <v>31750</v>
       </c>
       <c r="F65" t="n">
-        <v>73571</v>
+        <v>31531</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
         <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>z3dmTMMO</t>
+          <t>SlybbadF</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="L65" t="n">
-        <v>1.57</v>
+        <v>0.45</v>
       </c>
       <c r="M65" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="N65" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="O65" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="P65" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T65" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="W65" t="n">
@@ -14614,135 +14618,131 @@
       </c>
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
+      <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="AE65" t="n">
-        <v>24.77777777777778</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AF65" t="n">
-        <v>184.1111111111111</v>
+        <v>182.7777777777778</v>
       </c>
       <c r="AG65" t="n">
-        <v>2.333333333333333</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AH65" t="n">
-        <v>80.33333333333333</v>
+        <v>76.77777777777777</v>
       </c>
       <c r="AI65" t="n">
-        <v>31611111.11111111</v>
+        <v>12888888.88888889</v>
       </c>
       <c r="AJ65" t="n">
-        <v>85.11111111111111</v>
+        <v>79.66666666666667</v>
       </c>
       <c r="AK65" t="n">
-        <v>22.81818181818182</v>
+        <v>25.36363636363636</v>
       </c>
       <c r="AL65" t="n">
-        <v>185</v>
+        <v>184.2727272727273</v>
       </c>
       <c r="AM65" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AN65" t="n">
-        <v>72.45454545454545</v>
+        <v>72.27272727272727</v>
       </c>
       <c r="AO65" t="n">
-        <v>5100000</v>
+        <v>3927272.727272727</v>
       </c>
       <c r="AP65" t="n">
-        <v>78.90909090909091</v>
+        <v>76</v>
       </c>
       <c r="AQ65" t="n">
-        <v>24.35714285714286</v>
+        <v>24.09090909090909</v>
       </c>
       <c r="AR65" t="n">
-        <v>185.7142857142857</v>
+        <v>179.9090909090909</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.857142857142857</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AT65" t="n">
-        <v>77.14285714285714</v>
+        <v>72.36363636363636</v>
       </c>
       <c r="AU65" t="n">
-        <v>18666071.42857143</v>
+        <v>8129545.454545454</v>
       </c>
       <c r="AV65" t="n">
-        <v>81.78571428571429</v>
+        <v>78.81818181818181</v>
       </c>
       <c r="AW65" t="n">
-        <v>25.22222222222222</v>
+        <v>28.0625</v>
       </c>
       <c r="AX65" t="n">
-        <v>181.3333333333333</v>
+        <v>183.3125</v>
       </c>
       <c r="AY65" t="n">
-        <v>1.111111111111111</v>
+        <v>1.1875</v>
       </c>
       <c r="AZ65" t="n">
-        <v>73.55555555555556</v>
+        <v>71.125</v>
       </c>
       <c r="BA65" t="n">
-        <v>5833333.333333333</v>
+        <v>2609375</v>
       </c>
       <c r="BB65" t="n">
-        <v>77.44444444444444</v>
+        <v>72.3125</v>
       </c>
       <c r="BC65" t="n">
-        <v>26.44444444444444</v>
+        <v>26.25</v>
       </c>
       <c r="BD65" t="n">
-        <v>184</v>
+        <v>180.5</v>
       </c>
       <c r="BE65" t="n">
-        <v>2.111111111111111</v>
+        <v>1.5</v>
       </c>
       <c r="BF65" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BG65" t="n">
-        <v>701</v>
+        <v>308</v>
       </c>
       <c r="BH65" t="n">
-        <v>197775000</v>
+        <v>52500000</v>
       </c>
       <c r="BI65" t="n">
-        <v>728</v>
+        <v>321</v>
       </c>
       <c r="BJ65" t="n">
-        <v>25</v>
+        <v>26.625</v>
       </c>
       <c r="BK65" t="n">
-        <v>179.5</v>
+        <v>182.5</v>
       </c>
       <c r="BL65" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="BM65" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BN65" t="n">
-        <v>291</v>
+        <v>574</v>
       </c>
       <c r="BO65" t="n">
-        <v>18900000</v>
+        <v>24900000</v>
       </c>
       <c r="BP65" t="n">
-        <v>315</v>
+        <v>590</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hCzywRkb</t>
+          <t>Q7TUjsot</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -14750,83 +14750,83 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">backhouse a 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ewood park
-  blackburn </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>31367</v>
+        <v>75635</v>
       </c>
       <c r="F66" t="n">
-        <v>20026</v>
+        <v>73571</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>z3dmTMMO</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="L66" t="n">
-        <v>0.28</v>
+        <v>1.57</v>
       </c>
       <c r="M66" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N66" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O66" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P66" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R66" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T66" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>lYgfxNV9</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="W66" t="n">
         <v>48</v>
       </c>
       <c r="X66" t="n">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="Y66" t="n">
         <v>0</v>
@@ -14838,127 +14838,127 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>z3dmTMMO</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="AE66" t="n">
-        <v>25.90909090909091</v>
+        <v>24.77777777777778</v>
       </c>
       <c r="AF66" t="n">
-        <v>181</v>
+        <v>184.1111111111111</v>
       </c>
       <c r="AG66" t="n">
-        <v>1</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="AH66" t="n">
-        <v>70.18181818181819</v>
+        <v>80.33333333333333</v>
       </c>
       <c r="AI66" t="n">
-        <v>2213636.363636364</v>
+        <v>31611111.11111111</v>
       </c>
       <c r="AJ66" t="n">
-        <v>72.90909090909091</v>
+        <v>85.11111111111111</v>
       </c>
       <c r="AK66" t="n">
-        <v>23.66666666666667</v>
+        <v>22.81818181818182</v>
       </c>
       <c r="AL66" t="n">
-        <v>181.4444444444445</v>
+        <v>185</v>
       </c>
       <c r="AM66" t="n">
         <v>1</v>
       </c>
       <c r="AN66" t="n">
-        <v>71.33333333333333</v>
+        <v>72.45454545454545</v>
       </c>
       <c r="AO66" t="n">
-        <v>4200000</v>
+        <v>5100000</v>
       </c>
       <c r="AP66" t="n">
-        <v>77</v>
+        <v>78.90909090909091</v>
       </c>
       <c r="AQ66" t="n">
-        <v>20.8</v>
+        <v>24.35714285714286</v>
       </c>
       <c r="AR66" t="n">
-        <v>178.2666666666667</v>
+        <v>185.7142857142857</v>
       </c>
       <c r="AS66" t="n">
-        <v>1</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="AT66" t="n">
-        <v>65.59999999999999</v>
+        <v>77.14285714285714</v>
       </c>
       <c r="AU66" t="n">
-        <v>1715000</v>
+        <v>18666071.42857143</v>
       </c>
       <c r="AV66" t="n">
-        <v>76.06666666666666</v>
+        <v>81.78571428571429</v>
       </c>
       <c r="AW66" t="n">
-        <v>24.71428571428572</v>
+        <v>25.22222222222222</v>
       </c>
       <c r="AX66" t="n">
-        <v>182.9285714285714</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="AY66" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AZ66" t="n">
-        <v>68.42857142857143</v>
+        <v>73.55555555555556</v>
       </c>
       <c r="BA66" t="n">
-        <v>2507142.857142857</v>
+        <v>5833333.333333333</v>
       </c>
       <c r="BB66" t="n">
-        <v>74.07142857142857</v>
+        <v>77.44444444444444</v>
       </c>
       <c r="BC66" t="n">
-        <v>25.2</v>
+        <v>26.44444444444444</v>
       </c>
       <c r="BD66" t="n">
-        <v>179.6</v>
+        <v>184</v>
       </c>
       <c r="BE66" t="n">
-        <v>1</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="BF66" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BG66" t="n">
-        <v>345</v>
+        <v>701</v>
       </c>
       <c r="BH66" t="n">
-        <v>8800000</v>
+        <v>197775000</v>
       </c>
       <c r="BI66" t="n">
-        <v>364</v>
+        <v>728</v>
       </c>
       <c r="BJ66" t="n">
-        <v>23.33333333333333</v>
+        <v>25</v>
       </c>
       <c r="BK66" t="n">
-        <v>178.6666666666667</v>
+        <v>179.5</v>
       </c>
       <c r="BL66" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="BM66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN66" t="n">
-        <v>211</v>
+        <v>291</v>
       </c>
       <c r="BO66" t="n">
-        <v>9000000</v>
+        <v>18900000</v>
       </c>
       <c r="BP66" t="n">
-        <v>228</v>
+        <v>315</v>
       </c>
     </row>
     <row r="67">
@@ -24552,7 +24552,7 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>Wp2ZKhUC</t>
+          <t>pl6wKCqJ</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -24560,76 +24560,76 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
+          <t xml:space="preserve">martin s 
   eng </t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">hillsborough
+  sheffield </t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>23408</v>
+        <v>39732</v>
       </c>
       <c r="F111" t="n">
-        <v>16322</v>
+        <v>32041</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" t="n">
         <v>1</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>llcCvIcG</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>hSUajdSS</t>
         </is>
       </c>
       <c r="K111" t="n">
-        <v>0.92</v>
+        <v>1.22</v>
       </c>
       <c r="L111" t="n">
-        <v>0.67</v>
+        <v>0.49</v>
       </c>
       <c r="M111" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N111" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="O111" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P111" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q111" t="n">
+        <v>5</v>
+      </c>
+      <c r="R111" t="n">
         <v>2</v>
       </c>
-      <c r="R111" t="n">
-        <v>5</v>
-      </c>
       <c r="S111" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T111" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>6wEAqBAE</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>OS3AwgCU</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="W111" t="n">
@@ -24647,130 +24647,126 @@
       <c r="AA111" t="inlineStr"/>
       <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="inlineStr"/>
-      <c r="AD111" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
+      <c r="AD111" t="inlineStr"/>
       <c r="AE111" t="n">
-        <v>26.88888888888889</v>
+        <v>27.90909090909091</v>
       </c>
       <c r="AF111" t="n">
-        <v>183.5555555555555</v>
+        <v>182.9090909090909</v>
       </c>
       <c r="AG111" t="n">
         <v>1</v>
       </c>
       <c r="AH111" t="n">
-        <v>69.88888888888889</v>
+        <v>67.72727272727273</v>
       </c>
       <c r="AI111" t="n">
-        <v>1775000</v>
+        <v>1190909.090909091</v>
       </c>
       <c r="AJ111" t="n">
-        <v>71.33333333333333</v>
+        <v>69.90909090909091</v>
       </c>
       <c r="AK111" t="n">
-        <v>26.3</v>
+        <v>25.1</v>
       </c>
       <c r="AL111" t="n">
-        <v>182.6</v>
+        <v>185.8</v>
       </c>
       <c r="AM111" t="n">
         <v>1</v>
       </c>
       <c r="AN111" t="n">
-        <v>72.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AO111" t="n">
-        <v>3180000</v>
+        <v>2460000</v>
       </c>
       <c r="AP111" t="n">
-        <v>74.7</v>
+        <v>73.5</v>
       </c>
       <c r="AQ111" t="n">
-        <v>23.42857142857143</v>
+        <v>24.875</v>
       </c>
       <c r="AR111" t="n">
-        <v>182.2857142857143</v>
+        <v>184.8333333333333</v>
       </c>
       <c r="AS111" t="n">
         <v>1</v>
       </c>
       <c r="AT111" t="n">
-        <v>66.57142857142857</v>
+        <v>65.83333333333333</v>
       </c>
       <c r="AU111" t="n">
-        <v>1753571.428571429</v>
+        <v>1131250</v>
       </c>
       <c r="AV111" t="n">
-        <v>73.57142857142857</v>
+        <v>70.58333333333333</v>
       </c>
       <c r="AW111" t="n">
-        <v>25.15384615384615</v>
+        <v>24.76470588235294</v>
       </c>
       <c r="AX111" t="n">
-        <v>185.1538461538462</v>
+        <v>180.0588235294118</v>
       </c>
       <c r="AY111" t="n">
         <v>1</v>
       </c>
       <c r="AZ111" t="n">
-        <v>67.53846153846153</v>
+        <v>69.47058823529412</v>
       </c>
       <c r="BA111" t="n">
-        <v>2274615.384615385</v>
+        <v>2600000</v>
       </c>
       <c r="BB111" t="n">
-        <v>73.53846153846153</v>
+        <v>74.64705882352941</v>
       </c>
       <c r="BC111" t="n">
-        <v>25.33333333333333</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="BD111" t="n">
-        <v>184.6666666666667</v>
+        <v>180.3333333333333</v>
       </c>
       <c r="BE111" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BF111" t="n">
         <v>3</v>
       </c>
       <c r="BG111" t="n">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="BH111" t="n">
-        <v>40100000</v>
+        <v>4500000</v>
       </c>
       <c r="BI111" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="BJ111" t="n">
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="BK111" t="n">
-        <v>178</v>
+        <v>177.3333333333333</v>
       </c>
       <c r="BL111" t="n">
         <v>1</v>
       </c>
       <c r="BM111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN111" t="n">
-        <v>278</v>
+        <v>206</v>
       </c>
       <c r="BO111" t="n">
-        <v>7700000</v>
+        <v>4125000</v>
       </c>
       <c r="BP111" t="n">
-        <v>291</v>
+        <v>207</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>pl6wKCqJ</t>
+          <t>pS8oS9yt</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -24778,76 +24774,76 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">martin s 
+          <t xml:space="preserve">smith j 
   eng </t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">hillsborough
-  sheffield </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>39732</v>
+        <v>32384</v>
       </c>
       <c r="F112" t="n">
-        <v>32041</v>
+        <v>30347</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>llcCvIcG</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>hSUajdSS</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="L112" t="n">
-        <v>0.49</v>
+        <v>1.01</v>
       </c>
       <c r="M112" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="N112" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O112" t="n">
+        <v>13</v>
+      </c>
+      <c r="P112" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>4</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6</v>
+      </c>
+      <c r="S112" t="n">
+        <v>6</v>
+      </c>
+      <c r="T112" t="n">
         <v>15</v>
       </c>
-      <c r="P112" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>5</v>
-      </c>
-      <c r="R112" t="n">
-        <v>2</v>
-      </c>
-      <c r="S112" t="n">
-        <v>9</v>
-      </c>
-      <c r="T112" t="n">
-        <v>20</v>
-      </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>Y39YvFx6</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>C2sV0kf7</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="W112" t="n">
@@ -24865,105 +24861,109 @@
       <c r="AA112" t="inlineStr"/>
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr"/>
-      <c r="AD112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
       <c r="AE112" t="n">
-        <v>27.90909090909091</v>
+        <v>24.3</v>
       </c>
       <c r="AF112" t="n">
-        <v>182.9090909090909</v>
+        <v>178.7</v>
       </c>
       <c r="AG112" t="n">
         <v>1</v>
       </c>
       <c r="AH112" t="n">
-        <v>67.72727272727273</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AI112" t="n">
-        <v>1190909.090909091</v>
+        <v>4840000</v>
       </c>
       <c r="AJ112" t="n">
-        <v>69.90909090909091</v>
+        <v>76.8</v>
       </c>
       <c r="AK112" t="n">
-        <v>25.1</v>
+        <v>24.5</v>
       </c>
       <c r="AL112" t="n">
-        <v>185.8</v>
+        <v>183.3</v>
       </c>
       <c r="AM112" t="n">
         <v>1</v>
       </c>
       <c r="AN112" t="n">
-        <v>70.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="AO112" t="n">
-        <v>2460000</v>
+        <v>2680000</v>
       </c>
       <c r="AP112" t="n">
-        <v>73.5</v>
+        <v>74</v>
       </c>
       <c r="AQ112" t="n">
-        <v>24.875</v>
+        <v>26.21739130434782</v>
       </c>
       <c r="AR112" t="n">
-        <v>184.8333333333333</v>
+        <v>179.1304347826087</v>
       </c>
       <c r="AS112" t="n">
         <v>1</v>
       </c>
       <c r="AT112" t="n">
-        <v>65.83333333333333</v>
+        <v>72.26086956521739</v>
       </c>
       <c r="AU112" t="n">
-        <v>1131250</v>
+        <v>3373913.043478261</v>
       </c>
       <c r="AV112" t="n">
-        <v>70.58333333333333</v>
+        <v>75.04347826086956</v>
       </c>
       <c r="AW112" t="n">
-        <v>24.76470588235294</v>
+        <v>22.95652173913043</v>
       </c>
       <c r="AX112" t="n">
-        <v>180.0588235294118</v>
+        <v>183.0434782608696</v>
       </c>
       <c r="AY112" t="n">
         <v>1</v>
       </c>
       <c r="AZ112" t="n">
-        <v>69.47058823529412</v>
+        <v>68.39130434782609</v>
       </c>
       <c r="BA112" t="n">
-        <v>2600000</v>
+        <v>2358695.652173913</v>
       </c>
       <c r="BB112" t="n">
-        <v>74.64705882352941</v>
+        <v>74.95652173913044</v>
       </c>
       <c r="BC112" t="n">
-        <v>26.33333333333333</v>
+        <v>22.5</v>
       </c>
       <c r="BD112" t="n">
+        <v>179</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>132</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>150</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="BK112" t="n">
         <v>180.3333333333333</v>
-      </c>
-      <c r="BE112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF112" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG112" t="n">
-        <v>205</v>
-      </c>
-      <c r="BH112" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="BI112" t="n">
-        <v>213</v>
-      </c>
-      <c r="BJ112" t="n">
-        <v>27</v>
-      </c>
-      <c r="BK112" t="n">
-        <v>177.3333333333333</v>
       </c>
       <c r="BL112" t="n">
         <v>1</v>
@@ -24972,19 +24972,19 @@
         <v>3</v>
       </c>
       <c r="BN112" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="BO112" t="n">
-        <v>4125000</v>
+        <v>4200000</v>
       </c>
       <c r="BP112" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>pS8oS9yt</t>
+          <t>GpCmixS5</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -24992,76 +24992,76 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
+          <t xml:space="preserve">doughty l 
   eng </t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>32384</v>
+        <v>21088</v>
       </c>
       <c r="F113" t="n">
-        <v>30347</v>
+        <v>15327</v>
       </c>
       <c r="G113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="K113" t="n">
-        <v>1.64</v>
+        <v>0.75</v>
       </c>
       <c r="L113" t="n">
-        <v>1.01</v>
+        <v>0.06</v>
       </c>
       <c r="M113" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="N113" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="O113" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P113" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q113" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R113" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T113" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>n94TZqsm</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="W113" t="n">
@@ -25078,131 +25078,131 @@
       </c>
       <c r="AA113" t="inlineStr"/>
       <c r="AB113" t="inlineStr"/>
-      <c r="AC113" t="inlineStr"/>
-      <c r="AD113" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr"/>
       <c r="AE113" t="n">
-        <v>24.3</v>
+        <v>24.75</v>
       </c>
       <c r="AF113" t="n">
-        <v>178.7</v>
+        <v>179.875</v>
       </c>
       <c r="AG113" t="n">
         <v>1</v>
       </c>
       <c r="AH113" t="n">
-        <v>72.90000000000001</v>
+        <v>69.125</v>
       </c>
       <c r="AI113" t="n">
-        <v>4840000</v>
+        <v>1937500</v>
       </c>
       <c r="AJ113" t="n">
-        <v>76.8</v>
+        <v>73.75</v>
       </c>
       <c r="AK113" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>1110000</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AQ113" t="n">
         <v>24.5</v>
       </c>
-      <c r="AL113" t="n">
-        <v>183.3</v>
-      </c>
-      <c r="AM113" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN113" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="AO113" t="n">
-        <v>2680000</v>
-      </c>
-      <c r="AP113" t="n">
-        <v>74</v>
-      </c>
-      <c r="AQ113" t="n">
-        <v>26.21739130434782</v>
-      </c>
       <c r="AR113" t="n">
-        <v>179.1304347826087</v>
+        <v>181.4285714285714</v>
       </c>
       <c r="AS113" t="n">
         <v>1</v>
       </c>
       <c r="AT113" t="n">
-        <v>72.26086956521739</v>
+        <v>67.35714285714286</v>
       </c>
       <c r="AU113" t="n">
-        <v>3373913.043478261</v>
+        <v>1533928.571428571</v>
       </c>
       <c r="AV113" t="n">
-        <v>75.04347826086956</v>
+        <v>72.57142857142857</v>
       </c>
       <c r="AW113" t="n">
-        <v>22.95652173913043</v>
+        <v>28.5</v>
       </c>
       <c r="AX113" t="n">
-        <v>183.0434782608696</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="AY113" t="n">
         <v>1</v>
       </c>
       <c r="AZ113" t="n">
-        <v>68.39130434782609</v>
+        <v>65.66666666666667</v>
       </c>
       <c r="BA113" t="n">
-        <v>2358695.652173913</v>
+        <v>854166.6666666666</v>
       </c>
       <c r="BB113" t="n">
-        <v>74.95652173913044</v>
+        <v>68</v>
       </c>
       <c r="BC113" t="n">
-        <v>22.5</v>
+        <v>28.5</v>
       </c>
       <c r="BD113" t="n">
-        <v>179</v>
+        <v>175.25</v>
       </c>
       <c r="BE113" t="n">
         <v>1</v>
       </c>
       <c r="BF113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BG113" t="n">
-        <v>132</v>
+        <v>269</v>
       </c>
       <c r="BH113" t="n">
-        <v>3400000</v>
+        <v>3900000</v>
       </c>
       <c r="BI113" t="n">
-        <v>150</v>
+        <v>281</v>
       </c>
       <c r="BJ113" t="n">
-        <v>23.66666666666667</v>
+        <v>27.85714285714286</v>
       </c>
       <c r="BK113" t="n">
-        <v>180.3333333333333</v>
+        <v>185.5714285714286</v>
       </c>
       <c r="BL113" t="n">
         <v>1</v>
       </c>
       <c r="BM113" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BN113" t="n">
-        <v>199</v>
+        <v>470</v>
       </c>
       <c r="BO113" t="n">
-        <v>4200000</v>
+        <v>7850000</v>
       </c>
       <c r="BP113" t="n">
-        <v>217</v>
+        <v>483</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>GpCmixS5</t>
+          <t>OI7kRTjn</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -25210,76 +25210,76 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">doughty l 
+          <t xml:space="preserve">donohue m 
   eng </t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
+          <t xml:space="preserve">the hawthorns
+  west bromwich </t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21088</v>
+        <v>26688</v>
       </c>
       <c r="F114" t="n">
-        <v>15327</v>
+        <v>25366</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L114" t="n">
-        <v>0.06</v>
+        <v>0.35</v>
       </c>
       <c r="M114" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="N114" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="O114" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P114" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q114" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>tMUvLt7h</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>GKEUt35A</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="W114" t="n">
@@ -25296,131 +25296,131 @@
       </c>
       <c r="AA114" t="inlineStr"/>
       <c r="AB114" t="inlineStr"/>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr"/>
+      <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
       <c r="AE114" t="n">
-        <v>24.75</v>
+        <v>26.6</v>
       </c>
       <c r="AF114" t="n">
-        <v>179.875</v>
+        <v>184.7</v>
       </c>
       <c r="AG114" t="n">
         <v>1</v>
       </c>
       <c r="AH114" t="n">
-        <v>69.125</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AI114" t="n">
-        <v>1937500</v>
+        <v>2030000</v>
       </c>
       <c r="AJ114" t="n">
-        <v>73.75</v>
+        <v>72.5</v>
       </c>
       <c r="AK114" t="n">
-        <v>26.9</v>
+        <v>22</v>
       </c>
       <c r="AL114" t="n">
-        <v>181.4</v>
+        <v>182.25</v>
       </c>
       <c r="AM114" t="n">
         <v>1</v>
       </c>
       <c r="AN114" t="n">
-        <v>67.2</v>
+        <v>69.875</v>
       </c>
       <c r="AO114" t="n">
-        <v>1110000</v>
+        <v>3375000</v>
       </c>
       <c r="AP114" t="n">
-        <v>69.3</v>
+        <v>78.25</v>
       </c>
       <c r="AQ114" t="n">
-        <v>24.5</v>
+        <v>29.26086956521739</v>
       </c>
       <c r="AR114" t="n">
-        <v>181.4285714285714</v>
+        <v>185.7826086956522</v>
       </c>
       <c r="AS114" t="n">
-        <v>1</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AT114" t="n">
-        <v>67.35714285714286</v>
+        <v>70.82608695652173</v>
       </c>
       <c r="AU114" t="n">
-        <v>1533928.571428571</v>
+        <v>2082608.695652174</v>
       </c>
       <c r="AV114" t="n">
-        <v>72.57142857142857</v>
+        <v>71.39130434782609</v>
       </c>
       <c r="AW114" t="n">
-        <v>28.5</v>
+        <v>21.9375</v>
       </c>
       <c r="AX114" t="n">
-        <v>182.6666666666667</v>
+        <v>181.0625</v>
       </c>
       <c r="AY114" t="n">
         <v>1</v>
       </c>
       <c r="AZ114" t="n">
-        <v>65.66666666666667</v>
+        <v>66.8125</v>
       </c>
       <c r="BA114" t="n">
-        <v>854166.6666666666</v>
+        <v>1914062.5</v>
       </c>
       <c r="BB114" t="n">
-        <v>68</v>
+        <v>74.375</v>
       </c>
       <c r="BC114" t="n">
-        <v>28.5</v>
+        <v>23</v>
       </c>
       <c r="BD114" t="n">
-        <v>175.25</v>
+        <v>182</v>
       </c>
       <c r="BE114" t="n">
         <v>1</v>
       </c>
       <c r="BF114" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BG114" t="n">
-        <v>269</v>
+        <v>140</v>
       </c>
       <c r="BH114" t="n">
-        <v>3900000</v>
+        <v>4700000</v>
       </c>
       <c r="BI114" t="n">
-        <v>281</v>
+        <v>151</v>
       </c>
       <c r="BJ114" t="n">
-        <v>27.85714285714286</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="BK114" t="n">
-        <v>185.5714285714286</v>
+        <v>179.8333333333333</v>
       </c>
       <c r="BL114" t="n">
         <v>1</v>
       </c>
       <c r="BM114" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN114" t="n">
-        <v>470</v>
+        <v>397</v>
       </c>
       <c r="BO114" t="n">
-        <v>7850000</v>
+        <v>9075000</v>
       </c>
       <c r="BP114" t="n">
-        <v>483</v>
+        <v>437</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>25AIOzVm</t>
+          <t>td9MNfpf</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -25428,52 +25428,52 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">nield t 
+          <t xml:space="preserve">allison s 
   eng </t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>25586</v>
+        <v>29673</v>
       </c>
       <c r="F115" t="n">
-        <v>21225</v>
+        <v>28771</v>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>S66R0t75</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>6F0lvLNC</t>
         </is>
       </c>
       <c r="K115" t="n">
-        <v>1.18</v>
+        <v>1.86</v>
       </c>
       <c r="L115" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="M115" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N115" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O115" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="P115" t="n">
         <v>11</v>
@@ -25482,22 +25482,22 @@
         <v>5</v>
       </c>
       <c r="R115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S115" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T115" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>U3POrPvM</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="W115" t="n">
@@ -25516,115 +25516,133 @@
       <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="AD115" t="inlineStr"/>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
       <c r="AE115" t="n">
-        <v>24.27272727272727</v>
+        <v>25.36363636363636</v>
       </c>
       <c r="AF115" t="n">
-        <v>179.4545454545455</v>
+        <v>181.7272727272727</v>
       </c>
       <c r="AG115" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AH115" t="n">
-        <v>69.72727272727273</v>
+        <v>70.27272727272727</v>
       </c>
       <c r="AI115" t="n">
-        <v>2984090.909090909</v>
+        <v>2781818.181818182</v>
       </c>
       <c r="AJ115" t="n">
-        <v>74.72727272727273</v>
+        <v>75.27272727272727</v>
       </c>
       <c r="AK115" t="n">
-        <v>28</v>
+        <v>24.3</v>
       </c>
       <c r="AL115" t="n">
-        <v>184.9</v>
+        <v>181.4</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AN115" t="n">
-        <v>70.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="AO115" t="n">
-        <v>1845000</v>
+        <v>2410000</v>
       </c>
       <c r="AP115" t="n">
-        <v>71.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AQ115" t="n">
-        <v>25.39130434782609</v>
+        <v>26.08333333333333</v>
       </c>
       <c r="AR115" t="n">
-        <v>180.1739130434783</v>
+        <v>184.0416666666667</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.043478260869565</v>
+        <v>1</v>
       </c>
       <c r="AT115" t="n">
-        <v>71.43478260869566</v>
+        <v>69.625</v>
       </c>
       <c r="AU115" t="n">
-        <v>3593478.260869565</v>
+        <v>2129166.666666667</v>
       </c>
       <c r="AV115" t="n">
-        <v>75.21739130434783</v>
+        <v>72.125</v>
       </c>
       <c r="AW115" t="n">
+        <v>22.23076923076923</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>180.3076923076923</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>66</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>1940769.230769231</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>74.69230769230769</v>
+      </c>
+      <c r="BC115" t="n">
         <v>25</v>
       </c>
-      <c r="AX115" t="n">
-        <v>179.9545454545455</v>
-      </c>
-      <c r="AY115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ115" t="n">
-        <v>67</v>
-      </c>
-      <c r="BA115" t="n">
-        <v>1430681.818181818</v>
-      </c>
-      <c r="BB115" t="n">
-        <v>72.18181818181819</v>
-      </c>
-      <c r="BC115" t="inlineStr"/>
-      <c r="BD115" t="inlineStr"/>
-      <c r="BE115" t="inlineStr"/>
-      <c r="BF115" t="inlineStr"/>
-      <c r="BG115" t="inlineStr"/>
-      <c r="BH115" t="inlineStr"/>
-      <c r="BI115" t="inlineStr"/>
+      <c r="BD115" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>210</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>220</v>
+      </c>
       <c r="BJ115" t="n">
-        <v>22.66666666666667</v>
+        <v>24.42857142857143</v>
       </c>
       <c r="BK115" t="n">
-        <v>182.6666666666667</v>
+        <v>184.7142857142857</v>
       </c>
       <c r="BL115" t="n">
         <v>1</v>
       </c>
       <c r="BM115" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BN115" t="n">
-        <v>192</v>
+        <v>497</v>
       </c>
       <c r="BO115" t="n">
-        <v>3950000</v>
+        <v>21100000</v>
       </c>
       <c r="BP115" t="n">
-        <v>219</v>
+        <v>534</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>lOuihICa</t>
+          <t>Wp2ZKhUC</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -25632,76 +25650,76 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">finnie w 
+          <t xml:space="preserve">kitchen a 
   eng </t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">the den
-  london </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>20146</v>
+        <v>23408</v>
       </c>
       <c r="F116" t="n">
-        <v>17151</v>
+        <v>16322</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>1</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="K116" t="n">
-        <v>1.01</v>
+        <v>0.92</v>
       </c>
       <c r="L116" t="n">
-        <v>0.31</v>
+        <v>0.67</v>
       </c>
       <c r="M116" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N116" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O116" t="n">
+        <v>12</v>
+      </c>
+      <c r="P116" t="n">
         <v>15</v>
       </c>
-      <c r="P116" t="n">
-        <v>7</v>
-      </c>
       <c r="Q116" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T116" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>MsDWbjnD</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>OEy2L7Zo</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="W116" t="n">
@@ -25718,135 +25736,131 @@
       </c>
       <c r="AA116" t="inlineStr"/>
       <c r="AB116" t="inlineStr"/>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
+      <c r="AC116" t="inlineStr"/>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="AE116" t="n">
-        <v>24.2</v>
+        <v>26.88888888888889</v>
       </c>
       <c r="AF116" t="n">
-        <v>180.5</v>
+        <v>183.5555555555555</v>
       </c>
       <c r="AG116" t="n">
         <v>1</v>
       </c>
       <c r="AH116" t="n">
-        <v>68.90000000000001</v>
+        <v>69.88888888888889</v>
       </c>
       <c r="AI116" t="n">
-        <v>2492500</v>
+        <v>1775000</v>
       </c>
       <c r="AJ116" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>3180000</v>
+      </c>
+      <c r="AP116" t="n">
         <v>74.7</v>
       </c>
-      <c r="AK116" t="n">
-        <v>26.63636363636364</v>
-      </c>
-      <c r="AL116" t="n">
-        <v>183.5454545454545</v>
-      </c>
-      <c r="AM116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN116" t="n">
-        <v>70.45454545454545</v>
-      </c>
-      <c r="AO116" t="n">
-        <v>2081818.181818182</v>
-      </c>
-      <c r="AP116" t="n">
-        <v>72.18181818181819</v>
-      </c>
       <c r="AQ116" t="n">
-        <v>25.66666666666667</v>
+        <v>23.42857142857143</v>
       </c>
       <c r="AR116" t="n">
-        <v>178.1428571428571</v>
+        <v>182.2857142857143</v>
       </c>
       <c r="AS116" t="n">
         <v>1</v>
       </c>
       <c r="AT116" t="n">
-        <v>68.47619047619048</v>
+        <v>66.57142857142857</v>
       </c>
       <c r="AU116" t="n">
-        <v>1808571.428571429</v>
+        <v>1753571.428571429</v>
       </c>
       <c r="AV116" t="n">
-        <v>73.0952380952381</v>
+        <v>73.57142857142857</v>
       </c>
       <c r="AW116" t="n">
-        <v>24.28571428571428</v>
+        <v>25.15384615384615</v>
       </c>
       <c r="AX116" t="n">
-        <v>182.6666666666667</v>
+        <v>185.1538461538462</v>
       </c>
       <c r="AY116" t="n">
         <v>1</v>
       </c>
       <c r="AZ116" t="n">
-        <v>65.04761904761905</v>
+        <v>67.53846153846153</v>
       </c>
       <c r="BA116" t="n">
-        <v>1419285.714285714</v>
+        <v>2274615.384615385</v>
       </c>
       <c r="BB116" t="n">
-        <v>70.47619047619048</v>
+        <v>73.53846153846153</v>
       </c>
       <c r="BC116" t="n">
-        <v>30</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="BD116" t="n">
-        <v>188</v>
+        <v>184.6666666666667</v>
       </c>
       <c r="BE116" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BF116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BG116" t="n">
-        <v>70</v>
+        <v>224</v>
       </c>
       <c r="BH116" t="n">
-        <v>1300000</v>
+        <v>40100000</v>
       </c>
       <c r="BI116" t="n">
-        <v>70</v>
+        <v>232</v>
       </c>
       <c r="BJ116" t="n">
-        <v>24.2</v>
+        <v>25.5</v>
       </c>
       <c r="BK116" t="n">
-        <v>187.2</v>
+        <v>178</v>
       </c>
       <c r="BL116" t="n">
         <v>1</v>
       </c>
       <c r="BM116" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN116" t="n">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="BO116" t="n">
-        <v>7775000</v>
+        <v>7700000</v>
       </c>
       <c r="BP116" t="n">
-        <v>362</v>
+        <v>291</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>td9MNfpf</t>
+          <t>lOuihICa</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -25854,76 +25868,76 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">allison s 
+          <t xml:space="preserve">finnie w 
   eng </t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">the den
+  london </t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>29673</v>
+        <v>20146</v>
       </c>
       <c r="F117" t="n">
-        <v>28771</v>
+        <v>17151</v>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H117" t="n">
         <v>1</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>6F0lvLNC</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="K117" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="L117" t="n">
-        <v>1.26</v>
+        <v>0.31</v>
       </c>
       <c r="M117" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="N117" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O117" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="P117" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q117" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T117" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>phM8NElP</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="W117" t="n">
@@ -25942,133 +25956,133 @@
       <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="AE117" t="n">
-        <v>25.36363636363636</v>
+        <v>24.2</v>
       </c>
       <c r="AF117" t="n">
-        <v>181.7272727272727</v>
+        <v>180.5</v>
       </c>
       <c r="AG117" t="n">
         <v>1</v>
       </c>
       <c r="AH117" t="n">
-        <v>70.27272727272727</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AI117" t="n">
-        <v>2781818.181818182</v>
+        <v>2492500</v>
       </c>
       <c r="AJ117" t="n">
-        <v>75.27272727272727</v>
+        <v>74.7</v>
       </c>
       <c r="AK117" t="n">
-        <v>24.3</v>
+        <v>26.63636363636364</v>
       </c>
       <c r="AL117" t="n">
-        <v>181.4</v>
+        <v>183.5454545454545</v>
       </c>
       <c r="AM117" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AN117" t="n">
-        <v>69.7</v>
+        <v>70.45454545454545</v>
       </c>
       <c r="AO117" t="n">
-        <v>2410000</v>
+        <v>2081818.181818182</v>
       </c>
       <c r="AP117" t="n">
-        <v>75.59999999999999</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="AQ117" t="n">
-        <v>26.08333333333333</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="AR117" t="n">
-        <v>184.0416666666667</v>
+        <v>178.1428571428571</v>
       </c>
       <c r="AS117" t="n">
         <v>1</v>
       </c>
       <c r="AT117" t="n">
-        <v>69.625</v>
+        <v>68.47619047619048</v>
       </c>
       <c r="AU117" t="n">
-        <v>2129166.666666667</v>
+        <v>1808571.428571429</v>
       </c>
       <c r="AV117" t="n">
-        <v>72.125</v>
+        <v>73.0952380952381</v>
       </c>
       <c r="AW117" t="n">
-        <v>22.23076923076923</v>
+        <v>24.28571428571428</v>
       </c>
       <c r="AX117" t="n">
-        <v>180.3076923076923</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="AY117" t="n">
         <v>1</v>
       </c>
       <c r="AZ117" t="n">
-        <v>66</v>
+        <v>65.04761904761905</v>
       </c>
       <c r="BA117" t="n">
-        <v>1940769.230769231</v>
+        <v>1419285.714285714</v>
       </c>
       <c r="BB117" t="n">
-        <v>74.69230769230769</v>
+        <v>70.47619047619048</v>
       </c>
       <c r="BC117" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BD117" t="n">
-        <v>185.3333333333333</v>
+        <v>188</v>
       </c>
       <c r="BE117" t="n">
         <v>1</v>
       </c>
       <c r="BF117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BG117" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="BH117" t="n">
-        <v>6900000</v>
+        <v>1300000</v>
       </c>
       <c r="BI117" t="n">
-        <v>220</v>
+        <v>70</v>
       </c>
       <c r="BJ117" t="n">
-        <v>24.42857142857143</v>
+        <v>24.2</v>
       </c>
       <c r="BK117" t="n">
-        <v>184.7142857142857</v>
+        <v>187.2</v>
       </c>
       <c r="BL117" t="n">
         <v>1</v>
       </c>
       <c r="BM117" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BN117" t="n">
-        <v>497</v>
+        <v>339</v>
       </c>
       <c r="BO117" t="n">
-        <v>21100000</v>
+        <v>7775000</v>
       </c>
       <c r="BP117" t="n">
-        <v>534</v>
+        <v>362</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>vw81K9A1</t>
+          <t>IT65JTP7</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
@@ -26076,76 +26090,76 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
+          <t xml:space="preserve">turf moor
+  burnley </t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>17250</v>
+        <v>22546</v>
       </c>
       <c r="F118" t="n">
-        <v>17115</v>
+        <v>20687</v>
       </c>
       <c r="G118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>z3dmTMMO</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>MeKPSerA</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="K118" t="n">
-        <v>1.1</v>
+        <v>1.74</v>
       </c>
       <c r="L118" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="M118" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="N118" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="O118" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P118" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>3</v>
+      </c>
+      <c r="R118" t="n">
         <v>8</v>
       </c>
-      <c r="Q118" t="n">
-        <v>5</v>
-      </c>
-      <c r="R118" t="n">
-        <v>2</v>
-      </c>
       <c r="S118" t="n">
+        <v>18</v>
+      </c>
+      <c r="T118" t="n">
         <v>8</v>
       </c>
-      <c r="T118" t="n">
-        <v>11</v>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>6HLBNw1o</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="W118" t="n">
@@ -26162,127 +26176,135 @@
       </c>
       <c r="AA118" t="inlineStr"/>
       <c r="AB118" t="inlineStr"/>
-      <c r="AC118" t="inlineStr"/>
-      <c r="AD118" t="inlineStr"/>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
       <c r="AE118" t="n">
-        <v>25.81818181818182</v>
+        <v>22.81818181818182</v>
       </c>
       <c r="AF118" t="n">
-        <v>182.2727272727273</v>
+        <v>185</v>
       </c>
       <c r="AG118" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AH118" t="n">
-        <v>75.90909090909091</v>
+        <v>72.54545454545455</v>
       </c>
       <c r="AI118" t="n">
-        <v>10281818.18181818</v>
+        <v>5172727.272727272</v>
       </c>
       <c r="AJ118" t="n">
-        <v>78.36363636363636</v>
+        <v>78.90909090909091</v>
       </c>
       <c r="AK118" t="n">
-        <v>24.2</v>
+        <v>25.8</v>
       </c>
       <c r="AL118" t="n">
-        <v>183</v>
+        <v>183.8</v>
       </c>
       <c r="AM118" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AN118" t="n">
-        <v>72.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="AO118" t="n">
-        <v>4240000</v>
+        <v>11200000</v>
       </c>
       <c r="AP118" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>26.15789473684211</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>180.3157894736842</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>73.89473684210526</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>6489473.684210527</v>
+      </c>
+      <c r="AV118" t="n">
         <v>77</v>
       </c>
-      <c r="AQ118" t="n">
-        <v>25.11111111111111</v>
-      </c>
-      <c r="AR118" t="n">
-        <v>180.9444444444445</v>
-      </c>
-      <c r="AS118" t="n">
-        <v>1.055555555555556</v>
-      </c>
-      <c r="AT118" t="n">
-        <v>74.61111111111111</v>
-      </c>
-      <c r="AU118" t="n">
-        <v>9394444.444444444</v>
-      </c>
-      <c r="AV118" t="n">
-        <v>78.44444444444444</v>
-      </c>
       <c r="AW118" t="n">
-        <v>22.53846153846154</v>
+        <v>24.4375</v>
       </c>
       <c r="AX118" t="n">
-        <v>179.3076923076923</v>
+        <v>177.6875</v>
       </c>
       <c r="AY118" t="n">
-        <v>1</v>
+        <v>1.625</v>
       </c>
       <c r="AZ118" t="n">
-        <v>70.15384615384616</v>
+        <v>73.5625</v>
       </c>
       <c r="BA118" t="n">
-        <v>3205769.230769231</v>
+        <v>10643750</v>
       </c>
       <c r="BB118" t="n">
-        <v>77.30769230769231</v>
+        <v>80.4375</v>
       </c>
       <c r="BC118" t="n">
-        <v>27</v>
+        <v>24.8</v>
       </c>
       <c r="BD118" t="n">
-        <v>180.5</v>
+        <v>181.2</v>
       </c>
       <c r="BE118" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="BF118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG118" t="n">
-        <v>307</v>
+        <v>363</v>
       </c>
       <c r="BH118" t="n">
-        <v>36000000</v>
+        <v>22300000</v>
       </c>
       <c r="BI118" t="n">
-        <v>314</v>
+        <v>393</v>
       </c>
       <c r="BJ118" t="n">
-        <v>26.57142857142857</v>
+        <v>23.75</v>
       </c>
       <c r="BK118" t="n">
-        <v>182.2857142857143</v>
+        <v>177.125</v>
       </c>
       <c r="BL118" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="BM118" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN118" t="n">
-        <v>492</v>
+        <v>596</v>
       </c>
       <c r="BO118" t="n">
-        <v>14200000</v>
+        <v>75900000</v>
       </c>
       <c r="BP118" t="n">
-        <v>519</v>
+        <v>647</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>8rBEPGFs</t>
+          <t>25AIOzVm</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
@@ -26290,76 +26312,76 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">welch r 
+          <t xml:space="preserve">nield t 
   eng </t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>27000</v>
+        <v>25586</v>
       </c>
       <c r="F119" t="n">
-        <v>21003</v>
+        <v>21225</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>S66R0t75</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>0.58</v>
+        <v>1.18</v>
       </c>
       <c r="L119" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M119" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="N119" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O119" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P119" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q119" t="n">
+        <v>5</v>
+      </c>
+      <c r="R119" t="n">
         <v>3</v>
       </c>
-      <c r="R119" t="n">
-        <v>4</v>
-      </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T119" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>UwJevjpg</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>lhUKMQZu</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="W119" t="n">
@@ -26376,131 +26398,117 @@
       </c>
       <c r="AA119" t="inlineStr"/>
       <c r="AB119" t="inlineStr"/>
-      <c r="AC119" t="inlineStr"/>
-      <c r="AD119" t="inlineStr">
+      <c r="AC119" t="inlineStr">
         <is>
           <t>tUxUbLR2</t>
         </is>
       </c>
+      <c r="AD119" t="inlineStr"/>
       <c r="AE119" t="n">
-        <v>23.33333333333333</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="AF119" t="n">
-        <v>181.4444444444445</v>
+        <v>179.4545454545455</v>
       </c>
       <c r="AG119" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AH119" t="n">
-        <v>68.66666666666667</v>
+        <v>69.72727272727273</v>
       </c>
       <c r="AI119" t="n">
-        <v>2100000</v>
+        <v>2984090.909090909</v>
       </c>
       <c r="AJ119" t="n">
-        <v>74.33333333333333</v>
+        <v>74.72727272727273</v>
       </c>
       <c r="AK119" t="n">
-        <v>24.3</v>
+        <v>28</v>
       </c>
       <c r="AL119" t="n">
-        <v>183</v>
+        <v>184.9</v>
       </c>
       <c r="AM119" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AN119" t="n">
-        <v>67.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AO119" t="n">
-        <v>1745000</v>
+        <v>1845000</v>
       </c>
       <c r="AP119" t="n">
-        <v>73.8</v>
+        <v>71.8</v>
       </c>
       <c r="AQ119" t="n">
-        <v>24.71428571428572</v>
+        <v>25.39130434782609</v>
       </c>
       <c r="AR119" t="n">
-        <v>179.8571428571429</v>
+        <v>180.1739130434783</v>
       </c>
       <c r="AS119" t="n">
-        <v>1</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AT119" t="n">
-        <v>65</v>
+        <v>71.43478260869566</v>
       </c>
       <c r="AU119" t="n">
-        <v>1400357.142857143</v>
+        <v>3593478.260869565</v>
       </c>
       <c r="AV119" t="n">
-        <v>72.28571428571429</v>
+        <v>75.21739130434783</v>
       </c>
       <c r="AW119" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="AX119" t="n">
-        <v>180.3333333333333</v>
+        <v>179.9545454545455</v>
       </c>
       <c r="AY119" t="n">
         <v>1</v>
       </c>
       <c r="AZ119" t="n">
-        <v>66.73333333333333</v>
+        <v>67</v>
       </c>
       <c r="BA119" t="n">
-        <v>1391666.666666667</v>
+        <v>1430681.818181818</v>
       </c>
       <c r="BB119" t="n">
-        <v>71.53333333333333</v>
-      </c>
-      <c r="BC119" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD119" t="n">
-        <v>179</v>
-      </c>
-      <c r="BE119" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF119" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG119" t="n">
-        <v>133</v>
-      </c>
-      <c r="BH119" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="BI119" t="n">
-        <v>147</v>
-      </c>
+        <v>72.18181818181819</v>
+      </c>
+      <c r="BC119" t="inlineStr"/>
+      <c r="BD119" t="inlineStr"/>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr"/>
+      <c r="BG119" t="inlineStr"/>
+      <c r="BH119" t="inlineStr"/>
+      <c r="BI119" t="inlineStr"/>
       <c r="BJ119" t="n">
-        <v>26.8</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="BK119" t="n">
-        <v>181.4</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="BL119" t="n">
         <v>1</v>
       </c>
       <c r="BM119" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN119" t="n">
-        <v>326</v>
+        <v>192</v>
       </c>
       <c r="BO119" t="n">
-        <v>4225000</v>
+        <v>3950000</v>
       </c>
       <c r="BP119" t="n">
-        <v>345</v>
+        <v>219</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>YkKnUd7Q</t>
+          <t>8rBEPGFs</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
@@ -26508,76 +26516,76 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">bramall t 
+          <t xml:space="preserve">welch r 
   eng </t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  andrew s stadium
-  birmingham </t>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>29409</v>
+        <v>27000</v>
       </c>
       <c r="F120" t="n">
-        <v>26811</v>
+        <v>21003</v>
       </c>
       <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L120" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M120" t="n">
+        <v>62</v>
+      </c>
+      <c r="N120" t="n">
+        <v>38</v>
+      </c>
+      <c r="O120" t="n">
+        <v>9</v>
+      </c>
+      <c r="P120" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q120" t="n">
         <v>3</v>
       </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>SWk4muv7</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>GOvB22xg</t>
-        </is>
-      </c>
-      <c r="K120" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="M120" t="n">
-        <v>29</v>
-      </c>
-      <c r="N120" t="n">
-        <v>71</v>
-      </c>
-      <c r="O120" t="n">
-        <v>15</v>
-      </c>
-      <c r="P120" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q120" t="n">
+      <c r="R120" t="n">
         <v>4</v>
       </c>
-      <c r="R120" t="n">
-        <v>2</v>
-      </c>
       <c r="S120" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T120" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>neBDmKpm</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>lYgfxNV9</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="W120" t="n">
@@ -26594,135 +26602,131 @@
       </c>
       <c r="AA120" t="inlineStr"/>
       <c r="AB120" t="inlineStr"/>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
+      <c r="AC120" t="inlineStr"/>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>tUxUbLR2</t>
         </is>
       </c>
       <c r="AE120" t="n">
-        <v>25.18181818181818</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AF120" t="n">
-        <v>181.7272727272727</v>
+        <v>181.4444444444445</v>
       </c>
       <c r="AG120" t="n">
         <v>1</v>
       </c>
       <c r="AH120" t="n">
-        <v>69.36363636363636</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="AI120" t="n">
-        <v>2052727.272727273</v>
+        <v>2100000</v>
       </c>
       <c r="AJ120" t="n">
-        <v>73.27272727272727</v>
+        <v>74.33333333333333</v>
       </c>
       <c r="AK120" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="AL120" t="n">
-        <v>183.5</v>
+        <v>183</v>
       </c>
       <c r="AM120" t="n">
         <v>1</v>
       </c>
       <c r="AN120" t="n">
-        <v>71.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="AO120" t="n">
-        <v>4080000</v>
+        <v>1745000</v>
       </c>
       <c r="AP120" t="n">
-        <v>76.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="AQ120" t="n">
-        <v>24.91666666666667</v>
+        <v>24.71428571428572</v>
       </c>
       <c r="AR120" t="n">
-        <v>180.125</v>
+        <v>179.8571428571429</v>
       </c>
       <c r="AS120" t="n">
         <v>1</v>
       </c>
       <c r="AT120" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AU120" t="n">
-        <v>1540625</v>
+        <v>1400357.142857143</v>
       </c>
       <c r="AV120" t="n">
-        <v>72.29166666666667</v>
+        <v>72.28571428571429</v>
       </c>
       <c r="AW120" t="n">
-        <v>24.1875</v>
+        <v>25.2</v>
       </c>
       <c r="AX120" t="n">
-        <v>178.625</v>
+        <v>180.3333333333333</v>
       </c>
       <c r="AY120" t="n">
         <v>1</v>
       </c>
       <c r="AZ120" t="n">
-        <v>69.6875</v>
+        <v>66.73333333333333</v>
       </c>
       <c r="BA120" t="n">
-        <v>3064062.5</v>
+        <v>1391666.666666667</v>
       </c>
       <c r="BB120" t="n">
-        <v>75.6875</v>
+        <v>71.53333333333333</v>
       </c>
       <c r="BC120" t="n">
-        <v>26.66666666666667</v>
+        <v>25</v>
       </c>
       <c r="BD120" t="n">
-        <v>184.3333333333333</v>
+        <v>179</v>
       </c>
       <c r="BE120" t="n">
         <v>1</v>
       </c>
       <c r="BF120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BG120" t="n">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="BH120" t="n">
-        <v>2825000</v>
+        <v>2250000</v>
       </c>
       <c r="BI120" t="n">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="BJ120" t="n">
-        <v>26</v>
+        <v>26.8</v>
       </c>
       <c r="BK120" t="n">
-        <v>170</v>
+        <v>181.4</v>
       </c>
       <c r="BL120" t="n">
         <v>1</v>
       </c>
       <c r="BM120" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BN120" t="n">
-        <v>73</v>
+        <v>326</v>
       </c>
       <c r="BO120" t="n">
-        <v>3300000</v>
+        <v>4225000</v>
       </c>
       <c r="BP120" t="n">
-        <v>73</v>
+        <v>345</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>dU6KzVfr</t>
+          <t>YkKnUd7Q</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
@@ -26730,83 +26734,83 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">bramall t 
   eng </t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">st  andrew s stadium
+  birmingham </t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>30404</v>
+        <v>29409</v>
       </c>
       <c r="F121" t="n">
-        <v>29604</v>
+        <v>26811</v>
       </c>
       <c r="G121" t="n">
+        <v>3</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>SWk4muv7</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M121" t="n">
+        <v>29</v>
+      </c>
+      <c r="N121" t="n">
+        <v>71</v>
+      </c>
+      <c r="O121" t="n">
+        <v>15</v>
+      </c>
+      <c r="P121" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>4</v>
+      </c>
+      <c r="R121" t="n">
         <v>2</v>
       </c>
-      <c r="H121" t="n">
-        <v>2</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
-        </is>
-      </c>
-      <c r="K121" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="L121" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M121" t="n">
-        <v>46</v>
-      </c>
-      <c r="N121" t="n">
-        <v>54</v>
-      </c>
-      <c r="O121" t="n">
-        <v>18</v>
-      </c>
-      <c r="P121" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>9</v>
-      </c>
-      <c r="R121" t="n">
-        <v>4</v>
-      </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T121" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="W121" t="n">
         <v>48</v>
       </c>
       <c r="X121" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="Y121" t="n">
         <v>0</v>
@@ -26816,127 +26820,135 @@
       </c>
       <c r="AA121" t="inlineStr"/>
       <c r="AB121" t="inlineStr"/>
-      <c r="AC121" t="inlineStr"/>
-      <c r="AD121" t="inlineStr"/>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
       <c r="AE121" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>181.7272727272727</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>69.36363636363636</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>2052727.272727273</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AK121" t="n">
         <v>24.1</v>
       </c>
-      <c r="AF121" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="AG121" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH121" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="AI121" t="n">
-        <v>8990000</v>
-      </c>
-      <c r="AJ121" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="AK121" t="n">
-        <v>27.75</v>
-      </c>
       <c r="AL121" t="n">
-        <v>183.625</v>
+        <v>183.5</v>
       </c>
       <c r="AM121" t="n">
-        <v>1.625</v>
+        <v>1</v>
       </c>
       <c r="AN121" t="n">
-        <v>77.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AO121" t="n">
-        <v>13075000</v>
+        <v>4080000</v>
       </c>
       <c r="AP121" t="n">
-        <v>79.375</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AQ121" t="n">
-        <v>24.35</v>
+        <v>24.91666666666667</v>
       </c>
       <c r="AR121" t="n">
-        <v>184.8</v>
+        <v>180.125</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AT121" t="n">
-        <v>74.7</v>
+        <v>67</v>
       </c>
       <c r="AU121" t="n">
-        <v>9435000</v>
+        <v>1540625</v>
       </c>
       <c r="AV121" t="n">
-        <v>79.34999999999999</v>
+        <v>72.29166666666667</v>
       </c>
       <c r="AW121" t="n">
-        <v>23.42857142857143</v>
+        <v>24.1875</v>
       </c>
       <c r="AX121" t="n">
-        <v>181.4285714285714</v>
+        <v>178.625</v>
       </c>
       <c r="AY121" t="n">
-        <v>1.19047619047619</v>
+        <v>1</v>
       </c>
       <c r="AZ121" t="n">
-        <v>70.23809523809524</v>
+        <v>69.6875</v>
       </c>
       <c r="BA121" t="n">
-        <v>6565476.19047619</v>
+        <v>3064062.5</v>
       </c>
       <c r="BB121" t="n">
-        <v>78.28571428571429</v>
+        <v>75.6875</v>
       </c>
       <c r="BC121" t="n">
-        <v>28.5</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="BD121" t="n">
-        <v>192</v>
+        <v>184.3333333333333</v>
       </c>
       <c r="BE121" t="n">
         <v>1</v>
       </c>
       <c r="BF121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG121" t="n">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="BH121" t="n">
-        <v>18900000</v>
+        <v>2825000</v>
       </c>
       <c r="BI121" t="n">
-        <v>156</v>
+        <v>209</v>
       </c>
       <c r="BJ121" t="n">
-        <v>23.33333333333333</v>
+        <v>26</v>
       </c>
       <c r="BK121" t="n">
-        <v>174.6666666666667</v>
+        <v>170</v>
       </c>
       <c r="BL121" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BM121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN121" t="n">
-        <v>231</v>
+        <v>73</v>
       </c>
       <c r="BO121" t="n">
-        <v>49000000</v>
+        <v>3300000</v>
       </c>
       <c r="BP121" t="n">
-        <v>245</v>
+        <v>73</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>SbldtiXK</t>
+          <t>dU6KzVfr</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -26944,76 +26956,76 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>55097</v>
+        <v>30404</v>
       </c>
       <c r="F122" t="n">
-        <v>53449</v>
+        <v>29604</v>
       </c>
       <c r="G122" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>SlybbadF</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>3.34</v>
+        <v>1.94</v>
       </c>
       <c r="L122" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="M122" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="N122" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="O122" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="P122" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>9</v>
+      </c>
+      <c r="R122" t="n">
         <v>4</v>
       </c>
-      <c r="Q122" t="n">
-        <v>13</v>
-      </c>
-      <c r="R122" t="n">
-        <v>2</v>
-      </c>
       <c r="S122" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T122" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>MBpIn2MH</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="W122" t="n">
@@ -27030,121 +27042,127 @@
       </c>
       <c r="AA122" t="inlineStr"/>
       <c r="AB122" t="inlineStr"/>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
+      <c r="AC122" t="inlineStr"/>
+      <c r="AD122" t="inlineStr"/>
       <c r="AE122" t="n">
-        <v>24.72727272727273</v>
+        <v>24.1</v>
       </c>
       <c r="AF122" t="n">
-        <v>181.3636363636364</v>
+        <v>185.5</v>
       </c>
       <c r="AG122" t="n">
-        <v>2.909090909090909</v>
+        <v>1.3</v>
       </c>
       <c r="AH122" t="n">
-        <v>83.72727272727273</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AI122" t="n">
-        <v>63545454.54545455</v>
+        <v>8990000</v>
       </c>
       <c r="AJ122" t="n">
-        <v>87.36363636363636</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AK122" t="n">
-        <v>27.2</v>
+        <v>27.75</v>
       </c>
       <c r="AL122" t="n">
-        <v>183.4</v>
+        <v>183.625</v>
       </c>
       <c r="AM122" t="n">
-        <v>1.2</v>
+        <v>1.625</v>
       </c>
       <c r="AN122" t="n">
-        <v>72</v>
+        <v>77.5</v>
       </c>
       <c r="AO122" t="n">
-        <v>3150000</v>
+        <v>13075000</v>
       </c>
       <c r="AP122" t="n">
-        <v>73.8</v>
+        <v>79.375</v>
       </c>
       <c r="AQ122" t="n">
-        <v>24.64285714285714</v>
+        <v>24.35</v>
       </c>
       <c r="AR122" t="n">
-        <v>178.1428571428571</v>
+        <v>184.8</v>
       </c>
       <c r="AS122" t="n">
-        <v>2.357142857142857</v>
+        <v>1.35</v>
       </c>
       <c r="AT122" t="n">
-        <v>80</v>
+        <v>74.7</v>
       </c>
       <c r="AU122" t="n">
-        <v>52371428.57142857</v>
+        <v>9435000</v>
       </c>
       <c r="AV122" t="n">
-        <v>85.57142857142857</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="AW122" t="n">
-        <v>26.28571428571428</v>
+        <v>23.42857142857143</v>
       </c>
       <c r="AX122" t="n">
-        <v>180</v>
+        <v>181.4285714285714</v>
       </c>
       <c r="AY122" t="n">
-        <v>1.142857142857143</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="AZ122" t="n">
-        <v>66.64285714285714</v>
+        <v>70.23809523809524</v>
       </c>
       <c r="BA122" t="n">
-        <v>1291071.428571429</v>
+        <v>6565476.19047619</v>
       </c>
       <c r="BB122" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="BC122" t="inlineStr"/>
-      <c r="BD122" t="inlineStr"/>
-      <c r="BE122" t="inlineStr"/>
-      <c r="BF122" t="inlineStr"/>
-      <c r="BG122" t="inlineStr"/>
-      <c r="BH122" t="inlineStr"/>
-      <c r="BI122" t="inlineStr"/>
+        <v>78.28571428571429</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>192</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>153</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>18900000</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>156</v>
+      </c>
       <c r="BJ122" t="n">
-        <v>25.90909090909091</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="BK122" t="n">
-        <v>183.7272727272727</v>
+        <v>174.6666666666667</v>
       </c>
       <c r="BL122" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BM122" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BN122" t="n">
-        <v>792</v>
+        <v>231</v>
       </c>
       <c r="BO122" t="n">
-        <v>40500000</v>
+        <v>49000000</v>
       </c>
       <c r="BP122" t="n">
-        <v>823</v>
+        <v>245</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>IT65JTP7</t>
+          <t>SbldtiXK</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
@@ -27152,76 +27170,76 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">turf moor
-  burnley </t>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>22546</v>
+        <v>55097</v>
       </c>
       <c r="F123" t="n">
-        <v>20687</v>
+        <v>53449</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H123" t="n">
         <v>1</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>z3dmTMMO</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>SlybbadF</t>
         </is>
       </c>
       <c r="K123" t="n">
-        <v>1.74</v>
+        <v>3.34</v>
       </c>
       <c r="L123" t="n">
-        <v>1.03</v>
+        <v>0.7</v>
       </c>
       <c r="M123" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="N123" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="O123" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="P123" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Q123" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="R123" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S123" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="T123" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>6HLBNw1o</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="W123" t="n">
@@ -27240,133 +27258,119 @@
       <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="AE123" t="n">
-        <v>22.81818181818182</v>
+        <v>24.72727272727273</v>
       </c>
       <c r="AF123" t="n">
-        <v>185</v>
+        <v>181.3636363636364</v>
       </c>
       <c r="AG123" t="n">
-        <v>1</v>
+        <v>2.909090909090909</v>
       </c>
       <c r="AH123" t="n">
-        <v>72.54545454545455</v>
+        <v>83.72727272727273</v>
       </c>
       <c r="AI123" t="n">
-        <v>5172727.272727272</v>
+        <v>63545454.54545455</v>
       </c>
       <c r="AJ123" t="n">
-        <v>78.90909090909091</v>
+        <v>87.36363636363636</v>
       </c>
       <c r="AK123" t="n">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="AL123" t="n">
-        <v>183.8</v>
+        <v>183.4</v>
       </c>
       <c r="AM123" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AN123" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AO123" t="n">
-        <v>11200000</v>
+        <v>3150000</v>
       </c>
       <c r="AP123" t="n">
-        <v>80.3</v>
+        <v>73.8</v>
       </c>
       <c r="AQ123" t="n">
-        <v>26.15789473684211</v>
+        <v>24.64285714285714</v>
       </c>
       <c r="AR123" t="n">
-        <v>180.3157894736842</v>
+        <v>178.1428571428571</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.157894736842105</v>
+        <v>2.357142857142857</v>
       </c>
       <c r="AT123" t="n">
-        <v>73.89473684210526</v>
+        <v>80</v>
       </c>
       <c r="AU123" t="n">
-        <v>6489473.684210527</v>
+        <v>52371428.57142857</v>
       </c>
       <c r="AV123" t="n">
-        <v>77</v>
+        <v>85.57142857142857</v>
       </c>
       <c r="AW123" t="n">
-        <v>24.4375</v>
+        <v>26.28571428571428</v>
       </c>
       <c r="AX123" t="n">
-        <v>177.6875</v>
+        <v>180</v>
       </c>
       <c r="AY123" t="n">
-        <v>1.625</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AZ123" t="n">
-        <v>73.5625</v>
+        <v>66.64285714285714</v>
       </c>
       <c r="BA123" t="n">
-        <v>10643750</v>
+        <v>1291071.428571429</v>
       </c>
       <c r="BB123" t="n">
-        <v>80.4375</v>
-      </c>
-      <c r="BC123" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="BD123" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="BE123" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF123" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG123" t="n">
-        <v>363</v>
-      </c>
-      <c r="BH123" t="n">
-        <v>22300000</v>
-      </c>
-      <c r="BI123" t="n">
-        <v>393</v>
-      </c>
+        <v>71.5</v>
+      </c>
+      <c r="BC123" t="inlineStr"/>
+      <c r="BD123" t="inlineStr"/>
+      <c r="BE123" t="inlineStr"/>
+      <c r="BF123" t="inlineStr"/>
+      <c r="BG123" t="inlineStr"/>
+      <c r="BH123" t="inlineStr"/>
+      <c r="BI123" t="inlineStr"/>
       <c r="BJ123" t="n">
-        <v>23.75</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="BK123" t="n">
-        <v>177.125</v>
+        <v>183.7272727272727</v>
       </c>
       <c r="BL123" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
       <c r="BM123" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BN123" t="n">
-        <v>596</v>
+        <v>792</v>
       </c>
       <c r="BO123" t="n">
-        <v>75900000</v>
+        <v>40500000</v>
       </c>
       <c r="BP123" t="n">
-        <v>647</v>
+        <v>823</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>OI7kRTjn</t>
+          <t>vw81K9A1</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
@@ -27374,83 +27378,83 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">donohue m 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">the hawthorns
-  west bromwich </t>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>26688</v>
+        <v>17250</v>
       </c>
       <c r="F124" t="n">
-        <v>25366</v>
+        <v>17115</v>
       </c>
       <c r="G124" t="n">
+        <v>2</v>
+      </c>
+      <c r="H124" t="n">
         <v>0</v>
       </c>
-      <c r="H124" t="n">
-        <v>1</v>
-      </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>MeKPSerA</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>0.25</v>
+        <v>1.1</v>
       </c>
       <c r="L124" t="n">
-        <v>0.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M124" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N124" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O124" t="n">
+        <v>9</v>
+      </c>
+      <c r="P124" t="n">
         <v>8</v>
       </c>
-      <c r="P124" t="n">
-        <v>9</v>
-      </c>
       <c r="Q124" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T124" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>bPZzRChI</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="W124" t="n">
         <v>48</v>
       </c>
       <c r="X124" t="n">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
@@ -27461,130 +27465,126 @@
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="inlineStr"/>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
+      <c r="AD124" t="inlineStr"/>
       <c r="AE124" t="n">
-        <v>26.6</v>
+        <v>25.81818181818182</v>
       </c>
       <c r="AF124" t="n">
-        <v>184.7</v>
+        <v>182.2727272727273</v>
       </c>
       <c r="AG124" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AH124" t="n">
-        <v>70.40000000000001</v>
+        <v>75.90909090909091</v>
       </c>
       <c r="AI124" t="n">
-        <v>2030000</v>
+        <v>10281818.18181818</v>
       </c>
       <c r="AJ124" t="n">
-        <v>72.5</v>
+        <v>78.36363636363636</v>
       </c>
       <c r="AK124" t="n">
-        <v>22</v>
+        <v>24.2</v>
       </c>
       <c r="AL124" t="n">
-        <v>182.25</v>
+        <v>183</v>
       </c>
       <c r="AM124" t="n">
         <v>1</v>
       </c>
       <c r="AN124" t="n">
-        <v>69.875</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AO124" t="n">
-        <v>3375000</v>
+        <v>4240000</v>
       </c>
       <c r="AP124" t="n">
-        <v>78.25</v>
+        <v>77</v>
       </c>
       <c r="AQ124" t="n">
-        <v>29.26086956521739</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="AR124" t="n">
-        <v>185.7826086956522</v>
+        <v>180.9444444444445</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.043478260869565</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AT124" t="n">
-        <v>70.82608695652173</v>
+        <v>74.61111111111111</v>
       </c>
       <c r="AU124" t="n">
-        <v>2082608.695652174</v>
+        <v>9394444.444444444</v>
       </c>
       <c r="AV124" t="n">
-        <v>71.39130434782609</v>
+        <v>78.44444444444444</v>
       </c>
       <c r="AW124" t="n">
-        <v>21.9375</v>
+        <v>22.53846153846154</v>
       </c>
       <c r="AX124" t="n">
-        <v>181.0625</v>
+        <v>179.3076923076923</v>
       </c>
       <c r="AY124" t="n">
         <v>1</v>
       </c>
       <c r="AZ124" t="n">
-        <v>66.8125</v>
+        <v>70.15384615384616</v>
       </c>
       <c r="BA124" t="n">
-        <v>1914062.5</v>
+        <v>3205769.230769231</v>
       </c>
       <c r="BB124" t="n">
-        <v>74.375</v>
+        <v>77.30769230769231</v>
       </c>
       <c r="BC124" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BD124" t="n">
-        <v>182</v>
+        <v>180.5</v>
       </c>
       <c r="BE124" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BF124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BG124" t="n">
-        <v>140</v>
+        <v>307</v>
       </c>
       <c r="BH124" t="n">
-        <v>4700000</v>
+        <v>36000000</v>
       </c>
       <c r="BI124" t="n">
-        <v>151</v>
+        <v>314</v>
       </c>
       <c r="BJ124" t="n">
-        <v>23.83333333333333</v>
+        <v>26.57142857142857</v>
       </c>
       <c r="BK124" t="n">
-        <v>179.8333333333333</v>
+        <v>182.2857142857143</v>
       </c>
       <c r="BL124" t="n">
         <v>1</v>
       </c>
       <c r="BM124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN124" t="n">
-        <v>397</v>
+        <v>492</v>
       </c>
       <c r="BO124" t="n">
-        <v>9075000</v>
+        <v>14200000</v>
       </c>
       <c r="BP124" t="n">
-        <v>437</v>
+        <v>519</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bX3RMEa0</t>
+          <t>6km0uBnR</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -27592,55 +27592,55 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">bell j 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">elland road
-  leeds </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>37792</v>
+        <v>52305</v>
       </c>
       <c r="F125" t="n">
-        <v>36518</v>
+        <v>52206</v>
       </c>
       <c r="G125" t="n">
+        <v>4</v>
+      </c>
+      <c r="H125" t="n">
         <v>0</v>
       </c>
-      <c r="H125" t="n">
-        <v>1</v>
-      </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>tUxUbLR2</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>1.13</v>
+        <v>2.65</v>
       </c>
       <c r="L125" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M125" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="N125" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="O125" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P125" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q125" t="n">
         <v>5</v>
@@ -27649,26 +27649,26 @@
         <v>2</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T125" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="W125" t="n">
         <v>48</v>
       </c>
       <c r="X125" t="n">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
@@ -27680,133 +27680,133 @@
       <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>z3dmTMMO</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="AE125" t="n">
-        <v>22.8</v>
+        <v>26.54545454545455</v>
       </c>
       <c r="AF125" t="n">
-        <v>184.2</v>
+        <v>185.4545454545455</v>
       </c>
       <c r="AG125" t="n">
-        <v>1.2</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="AH125" t="n">
-        <v>74.40000000000001</v>
+        <v>78.36363636363636</v>
       </c>
       <c r="AI125" t="n">
-        <v>8880000</v>
+        <v>19563636.36363636</v>
       </c>
       <c r="AJ125" t="n">
-        <v>80.90000000000001</v>
+        <v>80.63636363636364</v>
       </c>
       <c r="AK125" t="n">
-        <v>24.90909090909091</v>
+        <v>25.55555555555556</v>
       </c>
       <c r="AL125" t="n">
-        <v>180.7272727272727</v>
+        <v>184.2222222222222</v>
       </c>
       <c r="AM125" t="n">
-        <v>1</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="AN125" t="n">
-        <v>70.18181818181819</v>
+        <v>82</v>
       </c>
       <c r="AO125" t="n">
-        <v>2327272.727272727</v>
+        <v>40388888.88888889</v>
       </c>
       <c r="AP125" t="n">
-        <v>73.09090909090909</v>
+        <v>84.88888888888889</v>
       </c>
       <c r="AQ125" t="n">
-        <v>25.82352941176471</v>
+        <v>25.38095238095238</v>
       </c>
       <c r="AR125" t="n">
-        <v>181</v>
+        <v>182.1428571428571</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.235294117647059</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="AT125" t="n">
-        <v>73.47058823529412</v>
+        <v>69.76190476190476</v>
       </c>
       <c r="AU125" t="n">
-        <v>4988235.294117647</v>
+        <v>6511904.761904762</v>
       </c>
       <c r="AV125" t="n">
-        <v>76.17647058823529</v>
+        <v>76.33333333333333</v>
       </c>
       <c r="AW125" t="n">
-        <v>25.13333333333333</v>
+        <v>24.72222222222222</v>
       </c>
       <c r="AX125" t="n">
-        <v>181.2</v>
+        <v>182.8888888888889</v>
       </c>
       <c r="AY125" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="AZ125" t="n">
-        <v>66.73333333333333</v>
+        <v>79.88888888888889</v>
       </c>
       <c r="BA125" t="n">
-        <v>1548333.333333333</v>
+        <v>31287500</v>
       </c>
       <c r="BB125" t="n">
-        <v>72.53333333333333</v>
+        <v>82.66666666666667</v>
       </c>
       <c r="BC125" t="n">
-        <v>21</v>
+        <v>26.8</v>
       </c>
       <c r="BD125" t="n">
-        <v>193</v>
+        <v>184.6</v>
       </c>
       <c r="BE125" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="BF125" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BG125" t="n">
-        <v>137</v>
+        <v>803</v>
       </c>
       <c r="BH125" t="n">
-        <v>7200000</v>
+        <v>288100000</v>
       </c>
       <c r="BI125" t="n">
-        <v>158</v>
+        <v>826</v>
       </c>
       <c r="BJ125" t="n">
-        <v>24</v>
+        <v>26.75</v>
       </c>
       <c r="BK125" t="n">
-        <v>177.6</v>
+        <v>183.25</v>
       </c>
       <c r="BL125" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="BM125" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN125" t="n">
-        <v>337</v>
+        <v>307</v>
       </c>
       <c r="BO125" t="n">
-        <v>8150000</v>
+        <v>56975000</v>
       </c>
       <c r="BP125" t="n">
-        <v>371</v>
+        <v>319</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>6km0uBnR</t>
+          <t>bX3RMEa0</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
@@ -27814,55 +27814,55 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinson t 
+          <t xml:space="preserve">bell j 
   eng </t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">elland road
+  leeds </t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>52305</v>
+        <v>37792</v>
       </c>
       <c r="F126" t="n">
-        <v>52206</v>
+        <v>36518</v>
       </c>
       <c r="G126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>tUxUbLR2</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>2.65</v>
+        <v>1.13</v>
       </c>
       <c r="L126" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="M126" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="N126" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="O126" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P126" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q126" t="n">
         <v>5</v>
@@ -27871,26 +27871,26 @@
         <v>2</v>
       </c>
       <c r="S126" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T126" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="W126" t="n">
         <v>48</v>
       </c>
       <c r="X126" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="Y126" t="n">
         <v>0</v>
@@ -27902,127 +27902,127 @@
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>z3dmTMMO</t>
         </is>
       </c>
       <c r="AE126" t="n">
-        <v>26.54545454545455</v>
+        <v>22.8</v>
       </c>
       <c r="AF126" t="n">
-        <v>185.4545454545455</v>
+        <v>184.2</v>
       </c>
       <c r="AG126" t="n">
-        <v>1.545454545454545</v>
+        <v>1.2</v>
       </c>
       <c r="AH126" t="n">
-        <v>78.36363636363636</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AI126" t="n">
-        <v>19563636.36363636</v>
+        <v>8880000</v>
       </c>
       <c r="AJ126" t="n">
-        <v>80.63636363636364</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AK126" t="n">
-        <v>25.55555555555556</v>
+        <v>24.90909090909091</v>
       </c>
       <c r="AL126" t="n">
-        <v>184.2222222222222</v>
+        <v>180.7272727272727</v>
       </c>
       <c r="AM126" t="n">
-        <v>2.222222222222222</v>
+        <v>1</v>
       </c>
       <c r="AN126" t="n">
-        <v>82</v>
+        <v>70.18181818181819</v>
       </c>
       <c r="AO126" t="n">
-        <v>40388888.88888889</v>
+        <v>2327272.727272727</v>
       </c>
       <c r="AP126" t="n">
-        <v>84.88888888888889</v>
+        <v>73.09090909090909</v>
       </c>
       <c r="AQ126" t="n">
-        <v>25.38095238095238</v>
+        <v>25.82352941176471</v>
       </c>
       <c r="AR126" t="n">
-        <v>182.1428571428571</v>
+        <v>181</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.19047619047619</v>
+        <v>1.235294117647059</v>
       </c>
       <c r="AT126" t="n">
-        <v>69.76190476190476</v>
+        <v>73.47058823529412</v>
       </c>
       <c r="AU126" t="n">
-        <v>6511904.761904762</v>
+        <v>4988235.294117647</v>
       </c>
       <c r="AV126" t="n">
-        <v>76.33333333333333</v>
+        <v>76.17647058823529</v>
       </c>
       <c r="AW126" t="n">
-        <v>24.72222222222222</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="AX126" t="n">
-        <v>182.8888888888889</v>
+        <v>181.2</v>
       </c>
       <c r="AY126" t="n">
-        <v>1.833333333333333</v>
+        <v>1</v>
       </c>
       <c r="AZ126" t="n">
-        <v>79.88888888888889</v>
+        <v>66.73333333333333</v>
       </c>
       <c r="BA126" t="n">
-        <v>31287500</v>
+        <v>1548333.333333333</v>
       </c>
       <c r="BB126" t="n">
-        <v>82.66666666666667</v>
+        <v>72.53333333333333</v>
       </c>
       <c r="BC126" t="n">
-        <v>26.8</v>
+        <v>21</v>
       </c>
       <c r="BD126" t="n">
-        <v>184.6</v>
+        <v>193</v>
       </c>
       <c r="BE126" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="BF126" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BG126" t="n">
-        <v>803</v>
+        <v>137</v>
       </c>
       <c r="BH126" t="n">
-        <v>288100000</v>
+        <v>7200000</v>
       </c>
       <c r="BI126" t="n">
-        <v>826</v>
+        <v>158</v>
       </c>
       <c r="BJ126" t="n">
-        <v>26.75</v>
+        <v>24</v>
       </c>
       <c r="BK126" t="n">
-        <v>183.25</v>
+        <v>177.6</v>
       </c>
       <c r="BL126" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="BM126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN126" t="n">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="BO126" t="n">
-        <v>56975000</v>
+        <v>8150000</v>
       </c>
       <c r="BP126" t="n">
-        <v>319</v>
+        <v>371</v>
       </c>
     </row>
     <row r="127">
@@ -28229,1322 +28229,6 @@
         <v>79</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="1" t="inlineStr">
-        <is>
-          <t>AXtmgbcg</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="n">
-        <v>45392.66666666666</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stroud k 
-  eng </t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
-        </is>
-      </c>
-      <c r="E128" t="n">
-        <v>21088</v>
-      </c>
-      <c r="F128" t="n">
-        <v>14692</v>
-      </c>
-      <c r="G128" t="n">
-        <v>3</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>hSUajdSS</t>
-        </is>
-      </c>
-      <c r="K128" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="M128" t="n">
-        <v>51</v>
-      </c>
-      <c r="N128" t="n">
-        <v>49</v>
-      </c>
-      <c r="O128" t="n">
-        <v>12</v>
-      </c>
-      <c r="P128" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>4</v>
-      </c>
-      <c r="R128" t="n">
-        <v>1</v>
-      </c>
-      <c r="S128" t="n">
-        <v>15</v>
-      </c>
-      <c r="T128" t="n">
-        <v>16</v>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="W128" t="n">
-        <v>48</v>
-      </c>
-      <c r="X128" t="n">
-        <v>485</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="AA128" t="inlineStr"/>
-      <c r="AB128" t="inlineStr"/>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr"/>
-      <c r="AE128" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="AF128" t="n">
-        <v>179.875</v>
-      </c>
-      <c r="AG128" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH128" t="n">
-        <v>69.125</v>
-      </c>
-      <c r="AI128" t="n">
-        <v>1937500</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>73.75</v>
-      </c>
-      <c r="AK128" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="AL128" t="n">
-        <v>185.3</v>
-      </c>
-      <c r="AM128" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN128" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="AO128" t="n">
-        <v>2727500</v>
-      </c>
-      <c r="AP128" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="AQ128" t="n">
-        <v>23.76190476190476</v>
-      </c>
-      <c r="AR128" t="n">
-        <v>180.7619047619048</v>
-      </c>
-      <c r="AS128" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT128" t="n">
-        <v>66.9047619047619</v>
-      </c>
-      <c r="AU128" t="n">
-        <v>1608333.333333333</v>
-      </c>
-      <c r="AV128" t="n">
-        <v>73.85714285714286</v>
-      </c>
-      <c r="AW128" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="AX128" t="n">
-        <v>180.3</v>
-      </c>
-      <c r="AY128" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ128" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="BA128" t="n">
-        <v>2072500</v>
-      </c>
-      <c r="BB128" t="n">
-        <v>73</v>
-      </c>
-      <c r="BC128" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="BD128" t="n">
-        <v>175.25</v>
-      </c>
-      <c r="BE128" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF128" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG128" t="n">
-        <v>269</v>
-      </c>
-      <c r="BH128" t="n">
-        <v>3900000</v>
-      </c>
-      <c r="BI128" t="n">
-        <v>281</v>
-      </c>
-      <c r="BJ128" t="n">
-        <v>27</v>
-      </c>
-      <c r="BK128" t="n">
-        <v>177.3333333333333</v>
-      </c>
-      <c r="BL128" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM128" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN128" t="n">
-        <v>206</v>
-      </c>
-      <c r="BO128" t="n">
-        <v>4125000</v>
-      </c>
-      <c r="BP128" t="n">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="inlineStr">
-        <is>
-          <t>jRUsVxhK</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="n">
-        <v>45392.66666666666</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the hawthorns
-  west bromwich </t>
-        </is>
-      </c>
-      <c r="E129" t="n">
-        <v>26688</v>
-      </c>
-      <c r="F129" t="n">
-        <v>22331</v>
-      </c>
-      <c r="G129" t="n">
-        <v>2</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>CCBWpzjj</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>KMfM7P4b</t>
-        </is>
-      </c>
-      <c r="K129" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="L129" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M129" t="n">
-        <v>68</v>
-      </c>
-      <c r="N129" t="n">
-        <v>32</v>
-      </c>
-      <c r="O129" t="n">
-        <v>11</v>
-      </c>
-      <c r="P129" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>4</v>
-      </c>
-      <c r="R129" t="n">
-        <v>1</v>
-      </c>
-      <c r="S129" t="n">
-        <v>4</v>
-      </c>
-      <c r="T129" t="n">
-        <v>9</v>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>GKEUt35A</t>
-        </is>
-      </c>
-      <c r="W129" t="n">
-        <v>48</v>
-      </c>
-      <c r="X129" t="n">
-        <v>485</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="AA129" t="inlineStr"/>
-      <c r="AB129" t="inlineStr"/>
-      <c r="AC129" t="inlineStr"/>
-      <c r="AD129" t="inlineStr"/>
-      <c r="AE129" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="AF129" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="AG129" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH129" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="AI129" t="n">
-        <v>2480000</v>
-      </c>
-      <c r="AJ129" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="AK129" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="AL129" t="n">
-        <v>181.4</v>
-      </c>
-      <c r="AM129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN129" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="AO129" t="n">
-        <v>1110000</v>
-      </c>
-      <c r="AP129" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="AQ129" t="n">
-        <v>27.08695652173913</v>
-      </c>
-      <c r="AR129" t="n">
-        <v>184.9565217391304</v>
-      </c>
-      <c r="AS129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT129" t="n">
-        <v>70.26086956521739</v>
-      </c>
-      <c r="AU129" t="n">
-        <v>2156521.739130435</v>
-      </c>
-      <c r="AV129" t="n">
-        <v>72.43478260869566</v>
-      </c>
-      <c r="AW129" t="n">
-        <v>27.26315789473684</v>
-      </c>
-      <c r="AX129" t="n">
-        <v>181.3684210526316</v>
-      </c>
-      <c r="AY129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ129" t="n">
-        <v>64.94736842105263</v>
-      </c>
-      <c r="BA129" t="n">
-        <v>814473.6842105263</v>
-      </c>
-      <c r="BB129" t="n">
-        <v>68.31578947368421</v>
-      </c>
-      <c r="BC129" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD129" t="n">
-        <v>182</v>
-      </c>
-      <c r="BE129" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF129" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG129" t="n">
-        <v>140</v>
-      </c>
-      <c r="BH129" t="n">
-        <v>4700000</v>
-      </c>
-      <c r="BI129" t="n">
-        <v>151</v>
-      </c>
-      <c r="BJ129" t="n">
-        <v>27.85714285714286</v>
-      </c>
-      <c r="BK129" t="n">
-        <v>185.5714285714286</v>
-      </c>
-      <c r="BL129" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM129" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN129" t="n">
-        <v>470</v>
-      </c>
-      <c r="BO129" t="n">
-        <v>7850000</v>
-      </c>
-      <c r="BP129" t="n">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="inlineStr">
-        <is>
-          <t>GAsqfvrm</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="n">
-        <v>45392.65625</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allison s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  andrew s stadium
-  birmingham </t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>29409</v>
-      </c>
-      <c r="F130" t="n">
-        <v>20894</v>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>1</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>SWk4muv7</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="K130" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="L130" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="M130" t="n">
-        <v>56</v>
-      </c>
-      <c r="N130" t="n">
-        <v>44</v>
-      </c>
-      <c r="O130" t="n">
-        <v>12</v>
-      </c>
-      <c r="P130" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>1</v>
-      </c>
-      <c r="R130" t="n">
-        <v>4</v>
-      </c>
-      <c r="S130" t="n">
-        <v>15</v>
-      </c>
-      <c r="T130" t="n">
-        <v>10</v>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>neBDmKpm</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>OEy2L7Zo</t>
-        </is>
-      </c>
-      <c r="W130" t="n">
-        <v>48</v>
-      </c>
-      <c r="X130" t="n">
-        <v>485</v>
-      </c>
-      <c r="Y130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="AA130" t="inlineStr"/>
-      <c r="AB130" t="inlineStr"/>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="AE130" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF130" t="n">
-        <v>181.5454545454545</v>
-      </c>
-      <c r="AG130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH130" t="n">
-        <v>68.90909090909091</v>
-      </c>
-      <c r="AI130" t="n">
-        <v>2170909.090909091</v>
-      </c>
-      <c r="AJ130" t="n">
-        <v>74.72727272727273</v>
-      </c>
-      <c r="AK130" t="n">
-        <v>26.54545454545455</v>
-      </c>
-      <c r="AL130" t="n">
-        <v>182.4545454545455</v>
-      </c>
-      <c r="AM130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN130" t="n">
-        <v>70.90909090909091</v>
-      </c>
-      <c r="AO130" t="n">
-        <v>2281818.181818182</v>
-      </c>
-      <c r="AP130" t="n">
-        <v>72.90909090909091</v>
-      </c>
-      <c r="AQ130" t="n">
-        <v>26.91666666666667</v>
-      </c>
-      <c r="AR130" t="n">
-        <v>180.0833333333333</v>
-      </c>
-      <c r="AS130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT130" t="n">
-        <v>67.95833333333333</v>
-      </c>
-      <c r="AU130" t="n">
-        <v>1582291.666666667</v>
-      </c>
-      <c r="AV130" t="n">
-        <v>70.54166666666667</v>
-      </c>
-      <c r="AW130" t="n">
-        <v>23.42105263157895</v>
-      </c>
-      <c r="AX130" t="n">
-        <v>184.9473684210526</v>
-      </c>
-      <c r="AY130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ130" t="n">
-        <v>64.84210526315789</v>
-      </c>
-      <c r="BA130" t="n">
-        <v>1519210.526315789</v>
-      </c>
-      <c r="BB130" t="n">
-        <v>71.21052631578948</v>
-      </c>
-      <c r="BC130" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD130" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="BE130" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF130" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG130" t="n">
-        <v>129</v>
-      </c>
-      <c r="BH130" t="n">
-        <v>1525000</v>
-      </c>
-      <c r="BI130" t="n">
-        <v>141</v>
-      </c>
-      <c r="BJ130" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="BK130" t="n">
-        <v>187.2</v>
-      </c>
-      <c r="BL130" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM130" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN130" t="n">
-        <v>339</v>
-      </c>
-      <c r="BO130" t="n">
-        <v>7775000</v>
-      </c>
-      <c r="BP130" t="n">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="inlineStr">
-        <is>
-          <t>pUwh8Fp7</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="n">
-        <v>45392.65625</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley r 
-  eng </t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
-        </is>
-      </c>
-      <c r="E131" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F131" t="n">
-        <v>19672</v>
-      </c>
-      <c r="G131" t="n">
-        <v>5</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>MahqU27I</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>6Nl8nagD</t>
-        </is>
-      </c>
-      <c r="K131" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="L131" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M131" t="n">
-        <v>45</v>
-      </c>
-      <c r="N131" t="n">
-        <v>55</v>
-      </c>
-      <c r="O131" t="n">
-        <v>15</v>
-      </c>
-      <c r="P131" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>7</v>
-      </c>
-      <c r="R131" t="n">
-        <v>4</v>
-      </c>
-      <c r="S131" t="n">
-        <v>7</v>
-      </c>
-      <c r="T131" t="n">
-        <v>15</v>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>UwJevjpg</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
-      <c r="W131" t="n">
-        <v>48</v>
-      </c>
-      <c r="X131" t="n">
-        <v>485</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="AA131" t="inlineStr"/>
-      <c r="AB131" t="inlineStr"/>
-      <c r="AC131" t="inlineStr"/>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>z3dmTMMO</t>
-        </is>
-      </c>
-      <c r="AE131" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AF131" t="n">
-        <v>182</v>
-      </c>
-      <c r="AG131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH131" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="AI131" t="n">
-        <v>2050000</v>
-      </c>
-      <c r="AJ131" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="AK131" t="n">
-        <v>24.72727272727273</v>
-      </c>
-      <c r="AL131" t="n">
-        <v>179.5454545454545</v>
-      </c>
-      <c r="AM131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN131" t="n">
-        <v>69.72727272727273</v>
-      </c>
-      <c r="AO131" t="n">
-        <v>2272727.272727273</v>
-      </c>
-      <c r="AP131" t="n">
-        <v>72.90909090909091</v>
-      </c>
-      <c r="AQ131" t="n">
-        <v>25.61904761904762</v>
-      </c>
-      <c r="AR131" t="n">
-        <v>181.3809523809524</v>
-      </c>
-      <c r="AS131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT131" t="n">
-        <v>65.23809523809524</v>
-      </c>
-      <c r="AU131" t="n">
-        <v>1268809.523809524</v>
-      </c>
-      <c r="AV131" t="n">
-        <v>71.19047619047619</v>
-      </c>
-      <c r="AW131" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="AX131" t="n">
-        <v>179.35</v>
-      </c>
-      <c r="AY131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ131" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="BA131" t="n">
-        <v>1727500</v>
-      </c>
-      <c r="BB131" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="BC131" t="n">
-        <v>23.66666666666667</v>
-      </c>
-      <c r="BD131" t="n">
-        <v>178.6666666666667</v>
-      </c>
-      <c r="BE131" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF131" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG131" t="n">
-        <v>201</v>
-      </c>
-      <c r="BH131" t="n">
-        <v>4950000</v>
-      </c>
-      <c r="BI131" t="n">
-        <v>225</v>
-      </c>
-      <c r="BJ131" t="n">
-        <v>24</v>
-      </c>
-      <c r="BK131" t="n">
-        <v>177.6</v>
-      </c>
-      <c r="BL131" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM131" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN131" t="n">
-        <v>337</v>
-      </c>
-      <c r="BO131" t="n">
-        <v>8150000</v>
-      </c>
-      <c r="BP131" t="n">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="inlineStr">
-        <is>
-          <t>OKxd7ZaD</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="n">
-        <v>45392.65625</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
-        </is>
-      </c>
-      <c r="E132" t="n">
-        <v>25586</v>
-      </c>
-      <c r="F132" t="n">
-        <v>21934</v>
-      </c>
-      <c r="G132" t="n">
-        <v>2</v>
-      </c>
-      <c r="H132" t="n">
-        <v>2</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>S66R0t75</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>6F0lvLNC</t>
-        </is>
-      </c>
-      <c r="K132" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="L132" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M132" t="n">
-        <v>61</v>
-      </c>
-      <c r="N132" t="n">
-        <v>39</v>
-      </c>
-      <c r="O132" t="n">
-        <v>18</v>
-      </c>
-      <c r="P132" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>7</v>
-      </c>
-      <c r="R132" t="n">
-        <v>6</v>
-      </c>
-      <c r="S132" t="n">
-        <v>8</v>
-      </c>
-      <c r="T132" t="n">
-        <v>7</v>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
-      <c r="W132" t="n">
-        <v>48</v>
-      </c>
-      <c r="X132" t="n">
-        <v>485</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="AA132" t="inlineStr"/>
-      <c r="AB132" t="inlineStr"/>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="AD132" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="AE132" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AF132" t="n">
-        <v>179.4</v>
-      </c>
-      <c r="AG132" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH132" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="AI132" t="n">
-        <v>3235000</v>
-      </c>
-      <c r="AJ132" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="AK132" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="AL132" t="n">
-        <v>182.1</v>
-      </c>
-      <c r="AM132" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN132" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="AO132" t="n">
-        <v>2560000</v>
-      </c>
-      <c r="AP132" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="AQ132" t="n">
-        <v>27.17647058823529</v>
-      </c>
-      <c r="AR132" t="n">
-        <v>179.7058823529412</v>
-      </c>
-      <c r="AS132" t="n">
-        <v>1.058823529411765</v>
-      </c>
-      <c r="AT132" t="n">
-        <v>70.47058823529412</v>
-      </c>
-      <c r="AU132" t="n">
-        <v>2677941.176470588</v>
-      </c>
-      <c r="AV132" t="n">
-        <v>73.41176470588235</v>
-      </c>
-      <c r="AW132" t="n">
-        <v>21.92857142857143</v>
-      </c>
-      <c r="AX132" t="n">
-        <v>178.1428571428571</v>
-      </c>
-      <c r="AY132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ132" t="n">
-        <v>66</v>
-      </c>
-      <c r="BA132" t="n">
-        <v>2023571.428571429</v>
-      </c>
-      <c r="BB132" t="n">
-        <v>74.14285714285714</v>
-      </c>
-      <c r="BC132" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD132" t="n">
-        <v>186</v>
-      </c>
-      <c r="BE132" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF132" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG132" t="n">
-        <v>71</v>
-      </c>
-      <c r="BH132" t="n">
-        <v>4100000</v>
-      </c>
-      <c r="BI132" t="n">
-        <v>82</v>
-      </c>
-      <c r="BJ132" t="n">
-        <v>24.42857142857143</v>
-      </c>
-      <c r="BK132" t="n">
-        <v>184.7142857142857</v>
-      </c>
-      <c r="BL132" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM132" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN132" t="n">
-        <v>497</v>
-      </c>
-      <c r="BO132" t="n">
-        <v>21100000</v>
-      </c>
-      <c r="BP132" t="n">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="inlineStr">
-        <is>
-          <t>CzWwWIxE</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="n">
-        <v>45392.65625</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>29673</v>
-      </c>
-      <c r="F133" t="n">
-        <v>28589</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
-      <c r="K133" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L133" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="M133" t="n">
-        <v>57</v>
-      </c>
-      <c r="N133" t="n">
-        <v>43</v>
-      </c>
-      <c r="O133" t="n">
-        <v>15</v>
-      </c>
-      <c r="P133" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>4</v>
-      </c>
-      <c r="R133" t="n">
-        <v>3</v>
-      </c>
-      <c r="S133" t="n">
-        <v>13</v>
-      </c>
-      <c r="T133" t="n">
-        <v>16</v>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>n94TZqsm</t>
-        </is>
-      </c>
-      <c r="W133" t="n">
-        <v>48</v>
-      </c>
-      <c r="X133" t="n">
-        <v>485</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="AA133" t="inlineStr"/>
-      <c r="AB133" t="inlineStr"/>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
-      <c r="AE133" t="n">
-        <v>26.18181818181818</v>
-      </c>
-      <c r="AF133" t="n">
-        <v>183.6363636363636</v>
-      </c>
-      <c r="AG133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>69.63636363636364</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>2318181.818181818</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>73.45454545454545</v>
-      </c>
-      <c r="AK133" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="AL133" t="n">
-        <v>183.3</v>
-      </c>
-      <c r="AM133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN133" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="AO133" t="n">
-        <v>2070000</v>
-      </c>
-      <c r="AP133" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="AQ133" t="n">
-        <v>25.16666666666667</v>
-      </c>
-      <c r="AR133" t="n">
-        <v>182.5416666666667</v>
-      </c>
-      <c r="AS133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT133" t="n">
-        <v>69.70833333333333</v>
-      </c>
-      <c r="AU133" t="n">
-        <v>2479166.666666667</v>
-      </c>
-      <c r="AV133" t="n">
-        <v>73.875</v>
-      </c>
-      <c r="AW133" t="n">
-        <v>25.33333333333333</v>
-      </c>
-      <c r="AX133" t="n">
-        <v>182.1666666666667</v>
-      </c>
-      <c r="AY133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ133" t="n">
-        <v>70.22222222222223</v>
-      </c>
-      <c r="BA133" t="n">
-        <v>3130555.555555556</v>
-      </c>
-      <c r="BB133" t="n">
-        <v>74.72222222222223</v>
-      </c>
-      <c r="BC133" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="BD133" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="BE133" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF133" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG133" t="n">
-        <v>281</v>
-      </c>
-      <c r="BH133" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="BI133" t="n">
-        <v>291</v>
-      </c>
-      <c r="BJ133" t="n">
-        <v>23.66666666666667</v>
-      </c>
-      <c r="BK133" t="n">
-        <v>180.3333333333333</v>
-      </c>
-      <c r="BL133" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM133" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN133" t="n">
-        <v>199</v>
-      </c>
-      <c r="BO133" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="BP133" t="n">
-        <v>217</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/england/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14042,7 +14042,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>t0DBiZhl</t>
+          <t>z51uktXk</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -14050,76 +14050,76 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">bramall lane
-  sheffield </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>32050</v>
+        <v>31876</v>
       </c>
       <c r="F76" t="n">
-        <v>29116</v>
+        <v>31662</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M76" t="n">
+        <v>56</v>
+      </c>
+      <c r="N76" t="n">
+        <v>44</v>
+      </c>
+      <c r="O76" t="n">
+        <v>17</v>
+      </c>
+      <c r="P76" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q76" t="n">
         <v>3</v>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>MeKPSerA</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L76" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M76" t="n">
-        <v>23</v>
-      </c>
-      <c r="N76" t="n">
-        <v>77</v>
-      </c>
-      <c r="O76" t="n">
-        <v>6</v>
-      </c>
-      <c r="P76" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1</v>
-      </c>
       <c r="R76" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T76" t="n">
         <v>9</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="W76" t="n">
@@ -14136,131 +14136,135 @@
       </c>
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr"/>
-      <c r="AC76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="AE76" t="n">
-        <v>24.6</v>
+        <v>26.77777777777778</v>
       </c>
       <c r="AF76" t="n">
-        <v>181.1</v>
+        <v>181.8888888888889</v>
       </c>
       <c r="AG76" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AH76" t="n">
-        <v>72.2</v>
+        <v>74.77777777777777</v>
       </c>
       <c r="AI76" t="n">
-        <v>4020000</v>
+        <v>7044444.444444444</v>
       </c>
       <c r="AJ76" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AK76" t="n">
-        <v>24.44444444444444</v>
+        <v>24.9</v>
       </c>
       <c r="AL76" t="n">
-        <v>185.1111111111111</v>
+        <v>183.8</v>
       </c>
       <c r="AM76" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AN76" t="n">
-        <v>81.88888888888889</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AO76" t="n">
-        <v>41777777.77777778</v>
+        <v>32100000</v>
       </c>
       <c r="AP76" t="n">
-        <v>85.55555555555556</v>
+        <v>84.5</v>
       </c>
       <c r="AQ76" t="n">
-        <v>22.15789473684211</v>
+        <v>20.95</v>
       </c>
       <c r="AR76" t="n">
-        <v>181.6315789473684</v>
+        <v>173.05</v>
       </c>
       <c r="AS76" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="AT76" t="n">
-        <v>67.94736842105263</v>
+        <v>72.25</v>
       </c>
       <c r="AU76" t="n">
-        <v>2677631.578947369</v>
+        <v>9223750</v>
       </c>
       <c r="AV76" t="n">
-        <v>76.15789473684211</v>
+        <v>81.3</v>
       </c>
       <c r="AW76" t="n">
-        <v>23.17647058823529</v>
+        <v>26.52380952380953</v>
       </c>
       <c r="AX76" t="n">
-        <v>181.5882352941177</v>
+        <v>186.1904761904762</v>
       </c>
       <c r="AY76" t="n">
-        <v>1.470588235294118</v>
+        <v>2.190476190476191</v>
       </c>
       <c r="AZ76" t="n">
-        <v>74.47058823529412</v>
+        <v>78.04761904761905</v>
       </c>
       <c r="BA76" t="n">
-        <v>21061764.70588235</v>
+        <v>25060714.28571429</v>
       </c>
       <c r="BB76" t="n">
-        <v>80.64705882352941</v>
+        <v>82.19047619047619</v>
       </c>
       <c r="BC76" t="n">
-        <v>29.5</v>
+        <v>26.125</v>
       </c>
       <c r="BD76" t="n">
-        <v>182.75</v>
+        <v>181.875</v>
       </c>
       <c r="BE76" t="n">
-        <v>1</v>
+        <v>1.625</v>
       </c>
       <c r="BF76" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BG76" t="n">
-        <v>286</v>
+        <v>612</v>
       </c>
       <c r="BH76" t="n">
-        <v>7000000</v>
+        <v>108900000</v>
       </c>
       <c r="BI76" t="n">
-        <v>290</v>
+        <v>648</v>
       </c>
       <c r="BJ76" t="n">
-        <v>26.66666666666667</v>
+        <v>25.8</v>
       </c>
       <c r="BK76" t="n">
-        <v>182.5</v>
+        <v>180.4</v>
       </c>
       <c r="BL76" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BM76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN76" t="n">
-        <v>467</v>
+        <v>395</v>
       </c>
       <c r="BO76" t="n">
-        <v>104475000</v>
+        <v>101000000</v>
       </c>
       <c r="BP76" t="n">
-        <v>482</v>
+        <v>404</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>z51uktXk</t>
+          <t>nu5ql0nd</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -14268,76 +14272,76 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">scott g 
   eng </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">turf moor
+  burnley </t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>31876</v>
+        <v>22546</v>
       </c>
       <c r="F77" t="n">
-        <v>31662</v>
+        <v>21109</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>2</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>z3dmTMMO</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>1.76</v>
+        <v>1.1</v>
       </c>
       <c r="L77" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M77" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="N77" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="O77" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q77" t="n">
         <v>3</v>
       </c>
       <c r="R77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T77" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="W77" t="n">
@@ -14356,133 +14360,129 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="n">
-        <v>26.77777777777778</v>
+        <v>23.7</v>
       </c>
       <c r="AF77" t="n">
-        <v>181.8888888888889</v>
+        <v>186.4</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AH77" t="n">
-        <v>74.77777777777777</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AI77" t="n">
-        <v>7044444.444444444</v>
+        <v>5210000</v>
       </c>
       <c r="AJ77" t="n">
-        <v>79</v>
+        <v>78.2</v>
       </c>
       <c r="AK77" t="n">
-        <v>24.9</v>
+        <v>25.8</v>
       </c>
       <c r="AL77" t="n">
-        <v>183.8</v>
+        <v>184.4</v>
       </c>
       <c r="AM77" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="AN77" t="n">
-        <v>80.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="AO77" t="n">
-        <v>32100000</v>
+        <v>8590000</v>
       </c>
       <c r="AP77" t="n">
-        <v>84.5</v>
+        <v>78.7</v>
       </c>
       <c r="AQ77" t="n">
-        <v>20.95</v>
+        <v>26.95</v>
       </c>
       <c r="AR77" t="n">
-        <v>173.05</v>
+        <v>181.6</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AT77" t="n">
-        <v>72.25</v>
+        <v>72.95</v>
       </c>
       <c r="AU77" t="n">
-        <v>9223750</v>
+        <v>3750000</v>
       </c>
       <c r="AV77" t="n">
-        <v>81.3</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="AW77" t="n">
-        <v>26.52380952380953</v>
+        <v>25.26086956521739</v>
       </c>
       <c r="AX77" t="n">
-        <v>186.1904761904762</v>
+        <v>188.1304347826087</v>
       </c>
       <c r="AY77" t="n">
-        <v>2.190476190476191</v>
+        <v>1.652173913043478</v>
       </c>
       <c r="AZ77" t="n">
-        <v>78.04761904761905</v>
+        <v>75.30434782608695</v>
       </c>
       <c r="BA77" t="n">
-        <v>25060714.28571429</v>
+        <v>11013043.47826087</v>
       </c>
       <c r="BB77" t="n">
-        <v>82.19047619047619</v>
+        <v>79.95652173913044</v>
       </c>
       <c r="BC77" t="n">
-        <v>26.125</v>
+        <v>25</v>
       </c>
       <c r="BD77" t="n">
-        <v>181.875</v>
+        <v>179.5</v>
       </c>
       <c r="BE77" t="n">
-        <v>1.625</v>
+        <v>1.75</v>
       </c>
       <c r="BF77" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BG77" t="n">
-        <v>612</v>
+        <v>291</v>
       </c>
       <c r="BH77" t="n">
-        <v>108900000</v>
+        <v>18900000</v>
       </c>
       <c r="BI77" t="n">
-        <v>648</v>
+        <v>315</v>
       </c>
       <c r="BJ77" t="n">
-        <v>25.8</v>
+        <v>23.5</v>
       </c>
       <c r="BK77" t="n">
-        <v>180.4</v>
+        <v>181</v>
       </c>
       <c r="BL77" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="BM77" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BN77" t="n">
-        <v>395</v>
+        <v>151</v>
       </c>
       <c r="BO77" t="n">
-        <v>101000000</v>
+        <v>20500000</v>
       </c>
       <c r="BP77" t="n">
-        <v>404</v>
+        <v>162</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>nu5ql0nd</t>
+          <t>0rgRCqPd</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -14490,76 +14490,76 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">scott g 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">turf moor
-  burnley </t>
+          <t xml:space="preserve">stamford bridge
+  london </t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>22546</v>
+        <v>40341</v>
       </c>
       <c r="F78" t="n">
-        <v>21109</v>
+        <v>39724</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>z3dmTMMO</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="L78" t="n">
-        <v>1.45</v>
+        <v>2.34</v>
       </c>
       <c r="M78" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="N78" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="O78" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P78" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q78" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S78" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T78" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="W78" t="n">
@@ -14578,105 +14578,109 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr"/>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
       <c r="AE78" t="n">
-        <v>23.7</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="AF78" t="n">
-        <v>186.4</v>
+        <v>183</v>
       </c>
       <c r="AG78" t="n">
-        <v>1</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="AH78" t="n">
-        <v>72.90000000000001</v>
+        <v>78.88888888888889</v>
       </c>
       <c r="AI78" t="n">
-        <v>5210000</v>
+        <v>20111111.11111111</v>
       </c>
       <c r="AJ78" t="n">
-        <v>78.2</v>
+        <v>82.88888888888889</v>
       </c>
       <c r="AK78" t="n">
-        <v>25.8</v>
+        <v>24.9</v>
       </c>
       <c r="AL78" t="n">
-        <v>184.4</v>
+        <v>180.6</v>
       </c>
       <c r="AM78" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AN78" t="n">
-        <v>75.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AO78" t="n">
-        <v>8590000</v>
+        <v>10660000</v>
       </c>
       <c r="AP78" t="n">
-        <v>78.7</v>
+        <v>79.3</v>
       </c>
       <c r="AQ78" t="n">
-        <v>26.95</v>
+        <v>22.29411764705882</v>
       </c>
       <c r="AR78" t="n">
-        <v>181.6</v>
+        <v>182.8235294117647</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.3</v>
+        <v>1.647058823529412</v>
       </c>
       <c r="AT78" t="n">
-        <v>72.95</v>
+        <v>75.35294117647059</v>
       </c>
       <c r="AU78" t="n">
-        <v>3750000</v>
+        <v>23738235.29411765</v>
       </c>
       <c r="AV78" t="n">
-        <v>76.34999999999999</v>
+        <v>82.88235294117646</v>
       </c>
       <c r="AW78" t="n">
-        <v>25.26086956521739</v>
+        <v>23.5</v>
       </c>
       <c r="AX78" t="n">
-        <v>188.1304347826087</v>
+        <v>184.8181818181818</v>
       </c>
       <c r="AY78" t="n">
-        <v>1.652173913043478</v>
+        <v>1.136363636363636</v>
       </c>
       <c r="AZ78" t="n">
-        <v>75.30434782608695</v>
+        <v>74.77272727272727</v>
       </c>
       <c r="BA78" t="n">
-        <v>11013043.47826087</v>
+        <v>9631818.181818182</v>
       </c>
       <c r="BB78" t="n">
-        <v>79.95652173913044</v>
+        <v>79.72727272727273</v>
       </c>
       <c r="BC78" t="n">
-        <v>25</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="BD78" t="n">
-        <v>179.5</v>
+        <v>181.5</v>
       </c>
       <c r="BE78" t="n">
-        <v>1.75</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BF78" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BG78" t="n">
-        <v>291</v>
+        <v>456</v>
       </c>
       <c r="BH78" t="n">
-        <v>18900000</v>
+        <v>120250000</v>
       </c>
       <c r="BI78" t="n">
-        <v>315</v>
+        <v>490</v>
       </c>
       <c r="BJ78" t="n">
-        <v>23.5</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="BK78" t="n">
         <v>181</v>
@@ -14685,22 +14689,22 @@
         <v>1</v>
       </c>
       <c r="BM78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN78" t="n">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="BO78" t="n">
-        <v>20500000</v>
+        <v>24800000</v>
       </c>
       <c r="BP78" t="n">
-        <v>162</v>
+        <v>229</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>0rgRCqPd</t>
+          <t>vZiVB3v3</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -14708,76 +14712,76 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
+          <t xml:space="preserve">selhurst park
   london </t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>40341</v>
+        <v>25486</v>
       </c>
       <c r="F79" t="n">
-        <v>39724</v>
+        <v>25191</v>
       </c>
       <c r="G79" t="n">
+        <v>5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M79" t="n">
+        <v>53</v>
+      </c>
+      <c r="N79" t="n">
+        <v>47</v>
+      </c>
+      <c r="O79" t="n">
+        <v>15</v>
+      </c>
+      <c r="P79" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>9</v>
+      </c>
+      <c r="R79" t="n">
         <v>2</v>
       </c>
-      <c r="H79" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L79" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="M79" t="n">
-        <v>63</v>
-      </c>
-      <c r="N79" t="n">
-        <v>37</v>
-      </c>
-      <c r="O79" t="n">
-        <v>16</v>
-      </c>
-      <c r="P79" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>6</v>
-      </c>
-      <c r="R79" t="n">
-        <v>5</v>
-      </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>zuJM7XDg</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="W79" t="n">
@@ -14796,133 +14800,129 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="AD79" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="n">
-        <v>24.66666666666667</v>
+        <v>24.63636363636364</v>
       </c>
       <c r="AF79" t="n">
-        <v>183</v>
+        <v>183.3636363636364</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.111111111111111</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AH79" t="n">
-        <v>78.88888888888889</v>
+        <v>77</v>
       </c>
       <c r="AI79" t="n">
-        <v>20111111.11111111</v>
+        <v>17009090.90909091</v>
       </c>
       <c r="AJ79" t="n">
-        <v>82.88888888888889</v>
+        <v>81.36363636363636</v>
       </c>
       <c r="AK79" t="n">
-        <v>24.9</v>
+        <v>26.81818181818182</v>
       </c>
       <c r="AL79" t="n">
-        <v>180.6</v>
+        <v>182.1818181818182</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.3</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="AN79" t="n">
-        <v>75.90000000000001</v>
+        <v>78.18181818181819</v>
       </c>
       <c r="AO79" t="n">
-        <v>10660000</v>
+        <v>19663636.36363636</v>
       </c>
       <c r="AP79" t="n">
-        <v>79.3</v>
+        <v>80.09090909090909</v>
       </c>
       <c r="AQ79" t="n">
-        <v>22.29411764705882</v>
+        <v>27.54166666666667</v>
       </c>
       <c r="AR79" t="n">
-        <v>182.8235294117647</v>
+        <v>185</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.647058823529412</v>
+        <v>1.208333333333333</v>
       </c>
       <c r="AT79" t="n">
-        <v>75.35294117647059</v>
+        <v>73.70833333333333</v>
       </c>
       <c r="AU79" t="n">
-        <v>23738235.29411765</v>
+        <v>7292708.333333333</v>
       </c>
       <c r="AV79" t="n">
-        <v>82.88235294117646</v>
+        <v>76.16666666666667</v>
       </c>
       <c r="AW79" t="n">
-        <v>23.5</v>
+        <v>21.375</v>
       </c>
       <c r="AX79" t="n">
-        <v>184.8181818181818</v>
+        <v>182.4375</v>
       </c>
       <c r="AY79" t="n">
-        <v>1.136363636363636</v>
+        <v>1.4375</v>
       </c>
       <c r="AZ79" t="n">
-        <v>74.77272727272727</v>
+        <v>69.4375</v>
       </c>
       <c r="BA79" t="n">
-        <v>9631818.181818182</v>
+        <v>9957812.5</v>
       </c>
       <c r="BB79" t="n">
-        <v>79.72727272727273</v>
+        <v>78.375</v>
       </c>
       <c r="BC79" t="n">
-        <v>23.16666666666667</v>
+        <v>25.8</v>
       </c>
       <c r="BD79" t="n">
-        <v>181.5</v>
+        <v>186</v>
       </c>
       <c r="BE79" t="n">
-        <v>1.333333333333333</v>
+        <v>1.2</v>
       </c>
       <c r="BF79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BG79" t="n">
-        <v>456</v>
+        <v>376</v>
       </c>
       <c r="BH79" t="n">
-        <v>120250000</v>
+        <v>47300000</v>
       </c>
       <c r="BI79" t="n">
-        <v>490</v>
+        <v>390</v>
       </c>
       <c r="BJ79" t="n">
-        <v>26.33333333333333</v>
+        <v>24.375</v>
       </c>
       <c r="BK79" t="n">
-        <v>181</v>
+        <v>183.875</v>
       </c>
       <c r="BL79" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="BM79" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BN79" t="n">
-        <v>222</v>
+        <v>626</v>
       </c>
       <c r="BO79" t="n">
-        <v>24800000</v>
+        <v>166100000</v>
       </c>
       <c r="BP79" t="n">
-        <v>229</v>
+        <v>648</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>vZiVB3v3</t>
+          <t>dAnzBNg9</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -14930,76 +14930,76 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>25486</v>
+        <v>61276</v>
       </c>
       <c r="F80" t="n">
-        <v>25191</v>
+        <v>60059</v>
       </c>
       <c r="G80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>2.31</v>
+        <v>4.46</v>
       </c>
       <c r="L80" t="n">
-        <v>1.2</v>
+        <v>0.62</v>
       </c>
       <c r="M80" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="N80" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="O80" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="P80" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q80" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S80" t="n">
+        <v>14</v>
+      </c>
+      <c r="T80" t="n">
         <v>10</v>
       </c>
-      <c r="T80" t="n">
-        <v>8</v>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="W80" t="n">
@@ -15018,129 +15018,129 @@
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
       <c r="AE80" t="n">
-        <v>24.63636363636364</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="AF80" t="n">
-        <v>183.3636363636364</v>
+        <v>181.8181818181818</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.363636363636364</v>
+        <v>2.818181818181818</v>
       </c>
       <c r="AH80" t="n">
-        <v>77</v>
+        <v>83.45454545454545</v>
       </c>
       <c r="AI80" t="n">
-        <v>17009090.90909091</v>
+        <v>50436363.63636363</v>
       </c>
       <c r="AJ80" t="n">
-        <v>81.36363636363636</v>
+        <v>85.81818181818181</v>
       </c>
       <c r="AK80" t="n">
-        <v>26.81818181818182</v>
+        <v>26</v>
       </c>
       <c r="AL80" t="n">
-        <v>182.1818181818182</v>
+        <v>182.4444444444445</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.909090909090909</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="AN80" t="n">
-        <v>78.18181818181819</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="AO80" t="n">
-        <v>19663636.36363636</v>
+        <v>14666666.66666667</v>
       </c>
       <c r="AP80" t="n">
-        <v>80.09090909090909</v>
+        <v>80.44444444444444</v>
       </c>
       <c r="AQ80" t="n">
-        <v>27.54166666666667</v>
+        <v>22.43478260869565</v>
       </c>
       <c r="AR80" t="n">
-        <v>185</v>
+        <v>184.7826086956522</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.208333333333333</v>
+        <v>1.739130434782609</v>
       </c>
       <c r="AT80" t="n">
-        <v>73.70833333333333</v>
+        <v>80.08695652173913</v>
       </c>
       <c r="AU80" t="n">
-        <v>7292708.333333333</v>
+        <v>36260869.56521739</v>
       </c>
       <c r="AV80" t="n">
-        <v>76.16666666666667</v>
+        <v>85.21739130434783</v>
       </c>
       <c r="AW80" t="n">
-        <v>21.375</v>
+        <v>23.65</v>
       </c>
       <c r="AX80" t="n">
-        <v>182.4375</v>
+        <v>180.35</v>
       </c>
       <c r="AY80" t="n">
-        <v>1.4375</v>
+        <v>1.1</v>
       </c>
       <c r="AZ80" t="n">
-        <v>69.4375</v>
+        <v>73.2</v>
       </c>
       <c r="BA80" t="n">
-        <v>9957812.5</v>
+        <v>9796250</v>
       </c>
       <c r="BB80" t="n">
-        <v>78.375</v>
+        <v>79.3</v>
       </c>
       <c r="BC80" t="n">
-        <v>25.8</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="BD80" t="n">
-        <v>186</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="BE80" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="BF80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BG80" t="n">
-        <v>376</v>
+        <v>226</v>
       </c>
       <c r="BH80" t="n">
-        <v>47300000</v>
+        <v>40300000</v>
       </c>
       <c r="BI80" t="n">
-        <v>390</v>
+        <v>247</v>
       </c>
       <c r="BJ80" t="n">
-        <v>24.375</v>
+        <v>32</v>
       </c>
       <c r="BK80" t="n">
-        <v>183.875</v>
+        <v>181</v>
       </c>
       <c r="BL80" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BM80" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BN80" t="n">
-        <v>626</v>
+        <v>154</v>
       </c>
       <c r="BO80" t="n">
-        <v>166100000</v>
+        <v>13500000</v>
       </c>
       <c r="BP80" t="n">
-        <v>648</v>
+        <v>154</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>dAnzBNg9</t>
+          <t>z1ovAs9F</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -15148,76 +15148,76 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">donohue m 
   eng </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
+          <t xml:space="preserve">kenilworth road
+  luton </t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>61276</v>
+        <v>12300</v>
       </c>
       <c r="F81" t="n">
-        <v>60059</v>
+        <v>12027</v>
       </c>
       <c r="G81" t="n">
         <v>2</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>SlybbadF</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>4.46</v>
+        <v>2</v>
       </c>
       <c r="L81" t="n">
-        <v>0.62</v>
+        <v>1.02</v>
       </c>
       <c r="M81" t="n">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="N81" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="O81" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="P81" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q81" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R81" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S81" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>x6CvOHH9</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="W81" t="n">
@@ -15236,129 +15236,129 @@
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr"/>
       <c r="AE81" t="n">
-        <v>26.27272727272727</v>
+        <v>25</v>
       </c>
       <c r="AF81" t="n">
-        <v>181.8181818181818</v>
+        <v>184.1818181818182</v>
       </c>
       <c r="AG81" t="n">
-        <v>2.818181818181818</v>
+        <v>1</v>
       </c>
       <c r="AH81" t="n">
-        <v>83.45454545454545</v>
+        <v>72.27272727272727</v>
       </c>
       <c r="AI81" t="n">
-        <v>50436363.63636363</v>
+        <v>3754545.454545455</v>
       </c>
       <c r="AJ81" t="n">
-        <v>85.81818181818181</v>
+        <v>76</v>
       </c>
       <c r="AK81" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>183</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>11520000</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>28.11764705882353</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>181.5294117647059</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>1.235294117647059</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>70.76470588235294</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>2341176.470588235</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>72.58823529411765</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>27.45833333333333</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>1.208333333333333</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>74.95833333333333</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>7537500</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>647</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>30900000</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>666</v>
+      </c>
+      <c r="BJ81" t="n">
         <v>26</v>
       </c>
-      <c r="AL81" t="n">
-        <v>182.4444444444445</v>
-      </c>
-      <c r="AM81" t="n">
-        <v>1.555555555555556</v>
-      </c>
-      <c r="AN81" t="n">
-        <v>77.66666666666667</v>
-      </c>
-      <c r="AO81" t="n">
-        <v>14666666.66666667</v>
-      </c>
-      <c r="AP81" t="n">
-        <v>80.44444444444444</v>
-      </c>
-      <c r="AQ81" t="n">
-        <v>22.43478260869565</v>
-      </c>
-      <c r="AR81" t="n">
-        <v>184.7826086956522</v>
-      </c>
-      <c r="AS81" t="n">
-        <v>1.739130434782609</v>
-      </c>
-      <c r="AT81" t="n">
-        <v>80.08695652173913</v>
-      </c>
-      <c r="AU81" t="n">
-        <v>36260869.56521739</v>
-      </c>
-      <c r="AV81" t="n">
-        <v>85.21739130434783</v>
-      </c>
-      <c r="AW81" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="AX81" t="n">
-        <v>180.35</v>
-      </c>
-      <c r="AY81" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AZ81" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="BA81" t="n">
-        <v>9796250</v>
-      </c>
-      <c r="BB81" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="BC81" t="n">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="BD81" t="n">
-        <v>181.3333333333333</v>
-      </c>
-      <c r="BE81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF81" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG81" t="n">
-        <v>226</v>
-      </c>
-      <c r="BH81" t="n">
-        <v>40300000</v>
-      </c>
-      <c r="BI81" t="n">
-        <v>247</v>
-      </c>
-      <c r="BJ81" t="n">
-        <v>32</v>
-      </c>
       <c r="BK81" t="n">
-        <v>181</v>
+        <v>188.5</v>
       </c>
       <c r="BL81" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BM81" t="n">
         <v>2</v>
       </c>
       <c r="BN81" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BO81" t="n">
-        <v>13500000</v>
+        <v>20500000</v>
       </c>
       <c r="BP81" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>z1ovAs9F</t>
+          <t>Sd97hFwr</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -15366,76 +15366,76 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">donohue m 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">kenilworth road
-  luton </t>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>12300</v>
+        <v>55097</v>
       </c>
       <c r="F82" t="n">
-        <v>12027</v>
+        <v>55097</v>
       </c>
       <c r="G82" t="n">
+        <v>3</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M82" t="n">
+        <v>70</v>
+      </c>
+      <c r="N82" t="n">
+        <v>30</v>
+      </c>
+      <c r="O82" t="n">
+        <v>28</v>
+      </c>
+      <c r="P82" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>12</v>
+      </c>
+      <c r="R82" t="n">
         <v>2</v>
       </c>
-      <c r="H82" t="n">
-        <v>4</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
-        <v>2</v>
-      </c>
-      <c r="L82" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="M82" t="n">
-        <v>37</v>
-      </c>
-      <c r="N82" t="n">
-        <v>63</v>
-      </c>
-      <c r="O82" t="n">
-        <v>15</v>
-      </c>
-      <c r="P82" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>6</v>
-      </c>
-      <c r="R82" t="n">
-        <v>8</v>
-      </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T82" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>MBpIn2MH</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="W82" t="n">
@@ -15454,129 +15454,133 @@
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
-      <c r="AD82" t="inlineStr"/>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
       <c r="AE82" t="n">
-        <v>25</v>
+        <v>26.36363636363636</v>
       </c>
       <c r="AF82" t="n">
-        <v>184.1818181818182</v>
+        <v>182.8181818181818</v>
       </c>
       <c r="AG82" t="n">
-        <v>1</v>
+        <v>3.272727272727273</v>
       </c>
       <c r="AH82" t="n">
-        <v>72.27272727272727</v>
+        <v>85.54545454545455</v>
       </c>
       <c r="AI82" t="n">
-        <v>3754545.454545455</v>
+        <v>78272727.27272727</v>
       </c>
       <c r="AJ82" t="n">
-        <v>76</v>
+        <v>87.81818181818181</v>
       </c>
       <c r="AK82" t="n">
-        <v>28.2</v>
+        <v>27.81818181818182</v>
       </c>
       <c r="AL82" t="n">
-        <v>183</v>
+        <v>182.9090909090909</v>
       </c>
       <c r="AM82" t="n">
-        <v>1.6</v>
+        <v>2.090909090909091</v>
       </c>
       <c r="AN82" t="n">
-        <v>76.5</v>
+        <v>78.72727272727273</v>
       </c>
       <c r="AO82" t="n">
-        <v>11520000</v>
+        <v>17536363.63636364</v>
       </c>
       <c r="AP82" t="n">
-        <v>77.5</v>
+        <v>80.18181818181819</v>
       </c>
       <c r="AQ82" t="n">
-        <v>28.11764705882353</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="AR82" t="n">
-        <v>181.5294117647059</v>
+        <v>178.4166666666667</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.235294117647059</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="AT82" t="n">
-        <v>70.76470588235294</v>
+        <v>79.5</v>
       </c>
       <c r="AU82" t="n">
-        <v>2341176.470588235</v>
+        <v>34748333.33333334</v>
       </c>
       <c r="AV82" t="n">
-        <v>72.58823529411765</v>
+        <v>82.83333333333333</v>
       </c>
       <c r="AW82" t="n">
-        <v>27.45833333333333</v>
+        <v>25.64705882352941</v>
       </c>
       <c r="AX82" t="n">
-        <v>182.25</v>
+        <v>182.2352941176471</v>
       </c>
       <c r="AY82" t="n">
-        <v>1.208333333333333</v>
+        <v>1.705882352941176</v>
       </c>
       <c r="AZ82" t="n">
-        <v>74.95833333333333</v>
+        <v>72.52941176470588</v>
       </c>
       <c r="BA82" t="n">
-        <v>7537500</v>
+        <v>11302941.17647059</v>
       </c>
       <c r="BB82" t="n">
-        <v>76.75</v>
+        <v>78.29411764705883</v>
       </c>
       <c r="BC82" t="n">
-        <v>26.88888888888889</v>
+        <v>29</v>
       </c>
       <c r="BD82" t="n">
-        <v>183.7777777777778</v>
+        <v>188</v>
       </c>
       <c r="BE82" t="n">
-        <v>1.111111111111111</v>
+        <v>3</v>
       </c>
       <c r="BF82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BG82" t="n">
-        <v>647</v>
+        <v>88</v>
       </c>
       <c r="BH82" t="n">
-        <v>30900000</v>
+        <v>70000000</v>
       </c>
       <c r="BI82" t="n">
-        <v>666</v>
+        <v>89</v>
       </c>
       <c r="BJ82" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BK82" t="n">
-        <v>188.5</v>
+        <v>178</v>
       </c>
       <c r="BL82" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BM82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BN82" t="n">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="BO82" t="n">
-        <v>20500000</v>
+        <v>11000000</v>
       </c>
       <c r="BP82" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>Sd97hFwr</t>
+          <t>t0DBiZhl</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -15584,76 +15588,76 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">bramall lane
+  sheffield </t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>55097</v>
+        <v>32050</v>
       </c>
       <c r="F83" t="n">
-        <v>55097</v>
+        <v>29116</v>
       </c>
       <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
         <v>3</v>
       </c>
-      <c r="H83" t="n">
-        <v>1</v>
-      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>MeKPSerA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="L83" t="n">
-        <v>0.37</v>
+        <v>3.4</v>
       </c>
       <c r="M83" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="N83" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="O83" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="P83" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q83" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T83" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>hUGEt9yf</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="W83" t="n">
@@ -15670,129 +15674,125 @@
       </c>
       <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr"/>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
+      <c r="AC83" t="inlineStr"/>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="AE83" t="n">
-        <v>26.36363636363636</v>
+        <v>24.6</v>
       </c>
       <c r="AF83" t="n">
-        <v>182.8181818181818</v>
+        <v>181.1</v>
       </c>
       <c r="AG83" t="n">
-        <v>3.272727272727273</v>
+        <v>1</v>
       </c>
       <c r="AH83" t="n">
-        <v>85.54545454545455</v>
+        <v>72.2</v>
       </c>
       <c r="AI83" t="n">
-        <v>78272727.27272727</v>
+        <v>4020000</v>
       </c>
       <c r="AJ83" t="n">
-        <v>87.81818181818181</v>
+        <v>77</v>
       </c>
       <c r="AK83" t="n">
-        <v>27.81818181818182</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="AL83" t="n">
-        <v>182.9090909090909</v>
+        <v>185.1111111111111</v>
       </c>
       <c r="AM83" t="n">
-        <v>2.090909090909091</v>
+        <v>2</v>
       </c>
       <c r="AN83" t="n">
-        <v>78.72727272727273</v>
+        <v>81.88888888888889</v>
       </c>
       <c r="AO83" t="n">
-        <v>17536363.63636364</v>
+        <v>41777777.77777778</v>
       </c>
       <c r="AP83" t="n">
-        <v>80.18181818181819</v>
+        <v>85.55555555555556</v>
       </c>
       <c r="AQ83" t="n">
-        <v>26.16666666666667</v>
+        <v>22.15789473684211</v>
       </c>
       <c r="AR83" t="n">
-        <v>178.4166666666667</v>
+        <v>181.6315789473684</v>
       </c>
       <c r="AS83" t="n">
-        <v>2.083333333333333</v>
+        <v>1</v>
       </c>
       <c r="AT83" t="n">
-        <v>79.5</v>
+        <v>67.94736842105263</v>
       </c>
       <c r="AU83" t="n">
-        <v>34748333.33333334</v>
+        <v>2677631.578947369</v>
       </c>
       <c r="AV83" t="n">
-        <v>82.83333333333333</v>
+        <v>76.15789473684211</v>
       </c>
       <c r="AW83" t="n">
-        <v>25.64705882352941</v>
+        <v>23.17647058823529</v>
       </c>
       <c r="AX83" t="n">
-        <v>182.2352941176471</v>
+        <v>181.5882352941177</v>
       </c>
       <c r="AY83" t="n">
-        <v>1.705882352941176</v>
+        <v>1.470588235294118</v>
       </c>
       <c r="AZ83" t="n">
-        <v>72.52941176470588</v>
+        <v>74.47058823529412</v>
       </c>
       <c r="BA83" t="n">
-        <v>11302941.17647059</v>
+        <v>21061764.70588235</v>
       </c>
       <c r="BB83" t="n">
-        <v>78.29411764705883</v>
+        <v>80.64705882352941</v>
       </c>
       <c r="BC83" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="BD83" t="n">
-        <v>188</v>
+        <v>182.75</v>
       </c>
       <c r="BE83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BF83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BG83" t="n">
-        <v>88</v>
+        <v>286</v>
       </c>
       <c r="BH83" t="n">
-        <v>70000000</v>
+        <v>7000000</v>
       </c>
       <c r="BI83" t="n">
-        <v>89</v>
+        <v>290</v>
       </c>
       <c r="BJ83" t="n">
-        <v>27</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="BK83" t="n">
-        <v>178</v>
+        <v>182.5</v>
       </c>
       <c r="BL83" t="n">
         <v>2</v>
       </c>
       <c r="BM83" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BN83" t="n">
-        <v>77</v>
+        <v>467</v>
       </c>
       <c r="BO83" t="n">
-        <v>11000000</v>
+        <v>104475000</v>
       </c>
       <c r="BP83" t="n">
-        <v>78</v>
+        <v>482</v>
       </c>
     </row>
     <row r="84">
@@ -17978,7 +17978,7 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>McL4erfM</t>
+          <t>2XnybGbN</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -17986,76 +17986,76 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">bramall t 
+          <t xml:space="preserve">donohue m 
   eng </t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>31750</v>
+        <v>11307</v>
       </c>
       <c r="F94" t="n">
-        <v>31424</v>
+        <v>11154</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>1.16</v>
+        <v>0.59</v>
       </c>
       <c r="L94" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="M94" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="N94" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O94" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P94" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q94" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S94" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T94" t="n">
         <v>12</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="W94" t="n">
@@ -18072,131 +18072,131 @@
       </c>
       <c r="AA94" t="inlineStr"/>
       <c r="AB94" t="inlineStr"/>
-      <c r="AC94" t="inlineStr"/>
-      <c r="AD94" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr"/>
       <c r="AE94" t="n">
-        <v>26.22222222222222</v>
+        <v>24.1</v>
       </c>
       <c r="AF94" t="n">
-        <v>182.3333333333333</v>
+        <v>182.1</v>
       </c>
       <c r="AG94" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>7550000</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>25.54545454545455</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>185</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>76.81818181818181</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>12772727.27272727</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>80</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>23.78947368421053</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>180.421052631579</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>1.526315789473684</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>74.84210526315789</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>11950000</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>79.68421052631579</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>182.55</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>7115000</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>297</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>36300000</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>314</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="BL94" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="AH94" t="n">
-        <v>76</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>11788888.88888889</v>
-      </c>
-      <c r="AJ94" t="n">
-        <v>78.88888888888889</v>
-      </c>
-      <c r="AK94" t="n">
-        <v>25.18181818181818</v>
-      </c>
-      <c r="AL94" t="n">
-        <v>183.6363636363636</v>
-      </c>
-      <c r="AM94" t="n">
-        <v>1.272727272727273</v>
-      </c>
-      <c r="AN94" t="n">
-        <v>76.63636363636364</v>
-      </c>
-      <c r="AO94" t="n">
-        <v>15527272.72727273</v>
-      </c>
-      <c r="AP94" t="n">
-        <v>80.45454545454545</v>
-      </c>
-      <c r="AQ94" t="n">
-        <v>24.78571428571428</v>
-      </c>
-      <c r="AR94" t="n">
-        <v>179</v>
-      </c>
-      <c r="AS94" t="n">
-        <v>1.428571428571429</v>
-      </c>
-      <c r="AT94" t="n">
-        <v>72.92857142857143</v>
-      </c>
-      <c r="AU94" t="n">
-        <v>7523214.285714285</v>
-      </c>
-      <c r="AV94" t="n">
-        <v>78.92857142857143</v>
-      </c>
-      <c r="AW94" t="n">
-        <v>25.58333333333333</v>
-      </c>
-      <c r="AX94" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="AY94" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AZ94" t="n">
-        <v>73.45833333333333</v>
-      </c>
-      <c r="BA94" t="n">
-        <v>9106250</v>
-      </c>
-      <c r="BB94" t="n">
-        <v>77.58333333333333</v>
-      </c>
-      <c r="BC94" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD94" t="n">
-        <v>180</v>
-      </c>
-      <c r="BE94" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF94" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG94" t="n">
-        <v>156</v>
-      </c>
-      <c r="BH94" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="BI94" t="n">
-        <v>160</v>
-      </c>
-      <c r="BJ94" t="n">
-        <v>27</v>
-      </c>
-      <c r="BK94" t="n">
-        <v>185.25</v>
-      </c>
-      <c r="BL94" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BM94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN94" t="n">
-        <v>310</v>
+        <v>231</v>
       </c>
       <c r="BO94" t="n">
-        <v>52000000</v>
+        <v>29500000</v>
       </c>
       <c r="BP94" t="n">
-        <v>316</v>
+        <v>238</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>2XnybGbN</t>
+          <t>YFw7hfMp</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -18204,76 +18204,76 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">donohue m 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>11307</v>
+        <v>39572</v>
       </c>
       <c r="F95" t="n">
-        <v>11154</v>
+        <v>39221</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
       </c>
       <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
         <v>2</v>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>0.59</v>
-      </c>
       <c r="L95" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="M95" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="N95" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="O95" t="n">
+        <v>15</v>
+      </c>
+      <c r="P95" t="n">
         <v>13</v>
       </c>
-      <c r="P95" t="n">
+      <c r="Q95" t="n">
+        <v>6</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="n">
+        <v>6</v>
+      </c>
+      <c r="T95" t="n">
         <v>11</v>
       </c>
-      <c r="Q95" t="n">
-        <v>4</v>
-      </c>
-      <c r="R95" t="n">
-        <v>5</v>
-      </c>
-      <c r="S95" t="n">
-        <v>16</v>
-      </c>
-      <c r="T95" t="n">
-        <v>12</v>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="W95" t="n">
@@ -18292,129 +18292,129 @@
       <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr"/>
       <c r="AE95" t="n">
-        <v>24.1</v>
+        <v>27.81818181818182</v>
       </c>
       <c r="AF95" t="n">
-        <v>182.1</v>
+        <v>183.8181818181818</v>
       </c>
       <c r="AG95" t="n">
-        <v>1.1</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="AH95" t="n">
-        <v>74.5</v>
+        <v>76.72727272727273</v>
       </c>
       <c r="AI95" t="n">
-        <v>7550000</v>
+        <v>11156818.18181818</v>
       </c>
       <c r="AJ95" t="n">
-        <v>78.2</v>
+        <v>79.27272727272727</v>
       </c>
       <c r="AK95" t="n">
-        <v>25.54545454545455</v>
+        <v>23.22222222222222</v>
       </c>
       <c r="AL95" t="n">
-        <v>185</v>
+        <v>180.1111111111111</v>
       </c>
       <c r="AM95" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AN95" t="n">
-        <v>76.81818181818181</v>
+        <v>70.22222222222223</v>
       </c>
       <c r="AO95" t="n">
-        <v>12772727.27272727</v>
+        <v>3591666.666666667</v>
       </c>
       <c r="AP95" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AQ95" t="n">
-        <v>23.78947368421053</v>
+        <v>23.75</v>
       </c>
       <c r="AR95" t="n">
-        <v>180.421052631579</v>
+        <v>185.5</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.526315789473684</v>
+        <v>1.4</v>
       </c>
       <c r="AT95" t="n">
-        <v>74.84210526315789</v>
+        <v>71.2</v>
       </c>
       <c r="AU95" t="n">
-        <v>11950000</v>
+        <v>5290000</v>
       </c>
       <c r="AV95" t="n">
-        <v>79.68421052631579</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AW95" t="n">
-        <v>25.35</v>
+        <v>22.375</v>
       </c>
       <c r="AX95" t="n">
-        <v>182.55</v>
+        <v>180</v>
       </c>
       <c r="AY95" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AZ95" t="n">
-        <v>74.2</v>
+        <v>68</v>
       </c>
       <c r="BA95" t="n">
-        <v>7115000</v>
+        <v>2398437.5</v>
       </c>
       <c r="BB95" t="n">
-        <v>77.55</v>
+        <v>76.5625</v>
       </c>
       <c r="BC95" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="BD95" t="n">
-        <v>179.75</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="BE95" t="n">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="BF95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BG95" t="n">
-        <v>297</v>
+        <v>222</v>
       </c>
       <c r="BH95" t="n">
-        <v>36300000</v>
+        <v>19500000</v>
       </c>
       <c r="BI95" t="n">
-        <v>314</v>
+        <v>236</v>
       </c>
       <c r="BJ95" t="n">
-        <v>26.33333333333333</v>
+        <v>26.71428571428572</v>
       </c>
       <c r="BK95" t="n">
-        <v>178.3333333333333</v>
+        <v>185.7142857142857</v>
       </c>
       <c r="BL95" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BM95" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BN95" t="n">
-        <v>231</v>
+        <v>500</v>
       </c>
       <c r="BO95" t="n">
-        <v>29500000</v>
+        <v>19400000</v>
       </c>
       <c r="BP95" t="n">
-        <v>238</v>
+        <v>524</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>YFw7hfMp</t>
+          <t>hITmaQfc</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -18422,76 +18422,76 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">england d 
   eng </t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>39572</v>
+        <v>52305</v>
       </c>
       <c r="F96" t="n">
-        <v>39221</v>
+        <v>51997</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>MeKPSerA</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="L96" t="n">
-        <v>0.62</v>
+        <v>1.5</v>
       </c>
       <c r="M96" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N96" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O96" t="n">
+        <v>18</v>
+      </c>
+      <c r="P96" t="n">
         <v>15</v>
       </c>
-      <c r="P96" t="n">
-        <v>13</v>
-      </c>
       <c r="Q96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T96" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="W96" t="n">
@@ -18510,129 +18510,133 @@
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="AD96" t="inlineStr"/>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
       <c r="AE96" t="n">
-        <v>27.81818181818182</v>
+        <v>25.4</v>
       </c>
       <c r="AF96" t="n">
-        <v>183.8181818181818</v>
+        <v>184.6</v>
       </c>
       <c r="AG96" t="n">
-        <v>1.636363636363636</v>
+        <v>1.4</v>
       </c>
       <c r="AH96" t="n">
-        <v>76.72727272727273</v>
+        <v>76.7</v>
       </c>
       <c r="AI96" t="n">
-        <v>11156818.18181818</v>
+        <v>17150000</v>
       </c>
       <c r="AJ96" t="n">
-        <v>79.27272727272727</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AK96" t="n">
-        <v>23.22222222222222</v>
+        <v>25.4</v>
       </c>
       <c r="AL96" t="n">
-        <v>180.1111111111111</v>
+        <v>182</v>
       </c>
       <c r="AM96" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AN96" t="n">
-        <v>70.22222222222223</v>
+        <v>75.5</v>
       </c>
       <c r="AO96" t="n">
-        <v>3591666.666666667</v>
+        <v>9380000</v>
       </c>
       <c r="AP96" t="n">
-        <v>77</v>
+        <v>80.3</v>
       </c>
       <c r="AQ96" t="n">
-        <v>23.75</v>
+        <v>26.85714285714286</v>
       </c>
       <c r="AR96" t="n">
-        <v>185.5</v>
+        <v>181.5238095238095</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.4</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AT96" t="n">
-        <v>71.2</v>
+        <v>77.80952380952381</v>
       </c>
       <c r="AU96" t="n">
-        <v>5290000</v>
+        <v>21455952.38095238</v>
       </c>
       <c r="AV96" t="n">
-        <v>76.59999999999999</v>
+        <v>80.66666666666667</v>
       </c>
       <c r="AW96" t="n">
-        <v>22.375</v>
+        <v>22.5</v>
       </c>
       <c r="AX96" t="n">
-        <v>180</v>
+        <v>175.15</v>
       </c>
       <c r="AY96" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AZ96" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="BA96" t="n">
-        <v>2398437.5</v>
+        <v>5936250</v>
       </c>
       <c r="BB96" t="n">
-        <v>76.5625</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="BC96" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD96" t="n">
-        <v>183.6666666666667</v>
+        <v>187</v>
       </c>
       <c r="BE96" t="n">
-        <v>1.666666666666667</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="BF96" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BG96" t="n">
-        <v>222</v>
+        <v>472</v>
       </c>
       <c r="BH96" t="n">
-        <v>19500000</v>
+        <v>167600000</v>
       </c>
       <c r="BI96" t="n">
-        <v>236</v>
+        <v>494</v>
       </c>
       <c r="BJ96" t="n">
-        <v>26.71428571428572</v>
+        <v>24.5</v>
       </c>
       <c r="BK96" t="n">
-        <v>185.7142857142857</v>
+        <v>179.8333333333333</v>
       </c>
       <c r="BL96" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BM96" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN96" t="n">
-        <v>500</v>
+        <v>453</v>
       </c>
       <c r="BO96" t="n">
-        <v>19400000</v>
+        <v>81400000</v>
       </c>
       <c r="BP96" t="n">
-        <v>524</v>
+        <v>489</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hITmaQfc</t>
+          <t>0rXec4P9</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -18640,76 +18644,76 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">england d 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>52305</v>
+        <v>62850</v>
       </c>
       <c r="F97" t="n">
-        <v>51997</v>
+        <v>61148</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" t="n">
         <v>1</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>z3dmTMMO</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>2.21</v>
+        <v>2.58</v>
       </c>
       <c r="L97" t="n">
-        <v>1.5</v>
+        <v>0.71</v>
       </c>
       <c r="M97" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="N97" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O97" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P97" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q97" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T97" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="W97" t="n">
@@ -18728,133 +18732,133 @@
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="AE97" t="n">
-        <v>25.4</v>
+        <v>24.2</v>
       </c>
       <c r="AF97" t="n">
-        <v>184.6</v>
+        <v>183.6</v>
       </c>
       <c r="AG97" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AH97" t="n">
-        <v>76.7</v>
+        <v>81.2</v>
       </c>
       <c r="AI97" t="n">
-        <v>17150000</v>
+        <v>37650000</v>
       </c>
       <c r="AJ97" t="n">
-        <v>80.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="AK97" t="n">
-        <v>25.4</v>
+        <v>23.63636363636364</v>
       </c>
       <c r="AL97" t="n">
-        <v>182</v>
+        <v>185.3636363636364</v>
       </c>
       <c r="AM97" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AN97" t="n">
-        <v>75.5</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="AO97" t="n">
-        <v>9380000</v>
+        <v>5063636.363636363</v>
       </c>
       <c r="AP97" t="n">
-        <v>80.3</v>
+        <v>78.18181818181819</v>
       </c>
       <c r="AQ97" t="n">
-        <v>26.85714285714286</v>
+        <v>24.21052631578947</v>
       </c>
       <c r="AR97" t="n">
-        <v>181.5238095238095</v>
+        <v>181.8421052631579</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.666666666666667</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="AT97" t="n">
-        <v>77.80952380952381</v>
+        <v>77.15789473684211</v>
       </c>
       <c r="AU97" t="n">
-        <v>21455952.38095238</v>
+        <v>24440789.47368421</v>
       </c>
       <c r="AV97" t="n">
-        <v>80.66666666666667</v>
+        <v>81.52631578947368</v>
       </c>
       <c r="AW97" t="n">
-        <v>22.5</v>
+        <v>24.11764705882353</v>
       </c>
       <c r="AX97" t="n">
-        <v>175.15</v>
+        <v>177.6470588235294</v>
       </c>
       <c r="AY97" t="n">
-        <v>1.2</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="AZ97" t="n">
-        <v>71</v>
+        <v>73.52941176470588</v>
       </c>
       <c r="BA97" t="n">
-        <v>5936250</v>
+        <v>7088235.294117647</v>
       </c>
       <c r="BB97" t="n">
-        <v>79.09999999999999</v>
+        <v>78.35294117647059</v>
       </c>
       <c r="BC97" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>387</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>79475000</v>
+      </c>
+      <c r="BI97" t="n">
+        <v>399</v>
+      </c>
+      <c r="BJ97" t="n">
         <v>25</v>
       </c>
-      <c r="BD97" t="n">
-        <v>187</v>
-      </c>
-      <c r="BE97" t="n">
-        <v>1.833333333333333</v>
-      </c>
-      <c r="BF97" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG97" t="n">
-        <v>472</v>
-      </c>
-      <c r="BH97" t="n">
-        <v>167600000</v>
-      </c>
-      <c r="BI97" t="n">
-        <v>494</v>
-      </c>
-      <c r="BJ97" t="n">
-        <v>24.5</v>
-      </c>
       <c r="BK97" t="n">
-        <v>179.8333333333333</v>
+        <v>179.5</v>
       </c>
       <c r="BL97" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="BM97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BN97" t="n">
-        <v>453</v>
+        <v>291</v>
       </c>
       <c r="BO97" t="n">
-        <v>81400000</v>
+        <v>18900000</v>
       </c>
       <c r="BP97" t="n">
-        <v>489</v>
+        <v>315</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>0rXec4P9</t>
+          <t>McL4erfM</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -18862,76 +18866,76 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">bramall t 
+  eng </t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>62850</v>
+        <v>31750</v>
       </c>
       <c r="F98" t="n">
-        <v>61148</v>
+        <v>31424</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>z3dmTMMO</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>2.58</v>
+        <v>1.16</v>
       </c>
       <c r="L98" t="n">
-        <v>0.71</v>
+        <v>3</v>
       </c>
       <c r="M98" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N98" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O98" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="P98" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R98" t="n">
         <v>3</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T98" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="W98" t="n">
@@ -18948,129 +18952,125 @@
       </c>
       <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr"/>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
+      <c r="AC98" t="inlineStr"/>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="AE98" t="n">
-        <v>24.2</v>
+        <v>26.22222222222222</v>
       </c>
       <c r="AF98" t="n">
-        <v>183.6</v>
+        <v>182.3333333333333</v>
       </c>
       <c r="AG98" t="n">
-        <v>1.9</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AH98" t="n">
-        <v>81.2</v>
+        <v>76</v>
       </c>
       <c r="AI98" t="n">
-        <v>37650000</v>
+        <v>11788888.88888889</v>
       </c>
       <c r="AJ98" t="n">
-        <v>85</v>
+        <v>78.88888888888889</v>
       </c>
       <c r="AK98" t="n">
-        <v>23.63636363636364</v>
+        <v>25.18181818181818</v>
       </c>
       <c r="AL98" t="n">
-        <v>185.3636363636364</v>
+        <v>183.6363636363636</v>
       </c>
       <c r="AM98" t="n">
-        <v>1</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="AN98" t="n">
-        <v>72.72727272727273</v>
+        <v>76.63636363636364</v>
       </c>
       <c r="AO98" t="n">
-        <v>5063636.363636363</v>
+        <v>15527272.72727273</v>
       </c>
       <c r="AP98" t="n">
-        <v>78.18181818181819</v>
+        <v>80.45454545454545</v>
       </c>
       <c r="AQ98" t="n">
-        <v>24.21052631578947</v>
+        <v>24.78571428571428</v>
       </c>
       <c r="AR98" t="n">
-        <v>181.8421052631579</v>
+        <v>179</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.631578947368421</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AT98" t="n">
-        <v>77.15789473684211</v>
+        <v>72.92857142857143</v>
       </c>
       <c r="AU98" t="n">
-        <v>24440789.47368421</v>
+        <v>7523214.285714285</v>
       </c>
       <c r="AV98" t="n">
-        <v>81.52631578947368</v>
+        <v>78.92857142857143</v>
       </c>
       <c r="AW98" t="n">
-        <v>24.11764705882353</v>
+        <v>25.58333333333333</v>
       </c>
       <c r="AX98" t="n">
-        <v>177.6470588235294</v>
+        <v>183.75</v>
       </c>
       <c r="AY98" t="n">
-        <v>1.058823529411765</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AZ98" t="n">
-        <v>73.52941176470588</v>
+        <v>73.45833333333333</v>
       </c>
       <c r="BA98" t="n">
-        <v>7088235.294117647</v>
+        <v>9106250</v>
       </c>
       <c r="BB98" t="n">
-        <v>78.35294117647059</v>
+        <v>77.58333333333333</v>
       </c>
       <c r="BC98" t="n">
-        <v>26.8</v>
+        <v>28</v>
       </c>
       <c r="BD98" t="n">
-        <v>182.6</v>
+        <v>180</v>
       </c>
       <c r="BE98" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF98" t="n">
         <v>2</v>
       </c>
-      <c r="BF98" t="n">
-        <v>5</v>
-      </c>
       <c r="BG98" t="n">
-        <v>387</v>
+        <v>156</v>
       </c>
       <c r="BH98" t="n">
-        <v>79475000</v>
+        <v>30000000</v>
       </c>
       <c r="BI98" t="n">
-        <v>399</v>
+        <v>160</v>
       </c>
       <c r="BJ98" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BK98" t="n">
-        <v>179.5</v>
+        <v>185.25</v>
       </c>
       <c r="BL98" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="BM98" t="n">
         <v>4</v>
       </c>
       <c r="BN98" t="n">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="BO98" t="n">
-        <v>18900000</v>
+        <v>52000000</v>
       </c>
       <c r="BP98" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="99">
@@ -19960,7 +19960,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrmC3KUo</t>
+          <t>xWC2qHqU</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -19968,76 +19968,76 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>40341</v>
+        <v>31876</v>
       </c>
       <c r="F103" t="n">
-        <v>39295</v>
+        <v>31596</v>
       </c>
       <c r="G103" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>4.31</v>
+        <v>2.47</v>
       </c>
       <c r="L103" t="n">
-        <v>0.93</v>
+        <v>0.06</v>
       </c>
       <c r="M103" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="N103" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="O103" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="P103" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>8</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" t="n">
         <v>13</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>14</v>
-      </c>
-      <c r="R103" t="n">
-        <v>2</v>
-      </c>
-      <c r="S103" t="n">
-        <v>12</v>
       </c>
       <c r="T103" t="n">
         <v>10</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>zuJM7XDg</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>hUGEt9yf</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="W103" t="n">
@@ -20056,133 +20056,129 @@
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr"/>
       <c r="AE103" t="n">
-        <v>24</v>
+        <v>26.11111111111111</v>
       </c>
       <c r="AF103" t="n">
-        <v>183.5555555555555</v>
+        <v>182.8888888888889</v>
       </c>
       <c r="AG103" t="n">
-        <v>1.777777777777778</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AH103" t="n">
-        <v>78.33333333333333</v>
+        <v>76</v>
       </c>
       <c r="AI103" t="n">
-        <v>19111111.11111111</v>
+        <v>9977777.777777778</v>
       </c>
       <c r="AJ103" t="n">
-        <v>83.11111111111111</v>
+        <v>80.11111111111111</v>
       </c>
       <c r="AK103" t="n">
-        <v>27.81818181818182</v>
+        <v>26.45454545454545</v>
       </c>
       <c r="AL103" t="n">
-        <v>183.9090909090909</v>
+        <v>182.3636363636364</v>
       </c>
       <c r="AM103" t="n">
-        <v>2.181818181818182</v>
+        <v>2.090909090909091</v>
       </c>
       <c r="AN103" t="n">
-        <v>79.18181818181819</v>
+        <v>79.54545454545455</v>
       </c>
       <c r="AO103" t="n">
-        <v>19545454.54545455</v>
+        <v>25127272.72727273</v>
       </c>
       <c r="AP103" t="n">
-        <v>80.54545454545455</v>
+        <v>81.45454545454545</v>
       </c>
       <c r="AQ103" t="n">
-        <v>22.95652173913043</v>
+        <v>21.31578947368421</v>
       </c>
       <c r="AR103" t="n">
-        <v>183.8260869565217</v>
+        <v>177.8421052631579</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.652173913043478</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="AT103" t="n">
-        <v>74.82608695652173</v>
+        <v>71.57894736842105</v>
       </c>
       <c r="AU103" t="n">
-        <v>19750000</v>
+        <v>6010526.315789473</v>
       </c>
       <c r="AV103" t="n">
-        <v>82.56521739130434</v>
+        <v>80.73684210526316</v>
       </c>
       <c r="AW103" t="n">
-        <v>27.88235294117647</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AX103" t="n">
-        <v>178.8235294117647</v>
+        <v>183.9444444444445</v>
       </c>
       <c r="AY103" t="n">
-        <v>1.705882352941176</v>
+        <v>1.611111111111111</v>
       </c>
       <c r="AZ103" t="n">
-        <v>74.41176470588235</v>
+        <v>72.94444444444444</v>
       </c>
       <c r="BA103" t="n">
-        <v>10511764.70588235</v>
+        <v>10123611.11111111</v>
       </c>
       <c r="BB103" t="n">
-        <v>77.82352941176471</v>
+        <v>78.88888888888889</v>
       </c>
       <c r="BC103" t="n">
-        <v>22.66666666666667</v>
+        <v>25.5</v>
       </c>
       <c r="BD103" t="n">
-        <v>183.6666666666667</v>
+        <v>177.5</v>
       </c>
       <c r="BE103" t="n">
-        <v>1.333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="BF103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BG103" t="n">
-        <v>448</v>
+        <v>604</v>
       </c>
       <c r="BH103" t="n">
-        <v>102050000</v>
+        <v>92500000</v>
       </c>
       <c r="BI103" t="n">
-        <v>488</v>
+        <v>645</v>
       </c>
       <c r="BJ103" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="BK103" t="n">
-        <v>186</v>
+        <v>183.8333333333333</v>
       </c>
       <c r="BL103" t="n">
         <v>2</v>
       </c>
       <c r="BM103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BN103" t="n">
-        <v>155</v>
+        <v>485</v>
       </c>
       <c r="BO103" t="n">
-        <v>28500000</v>
+        <v>167500000</v>
       </c>
       <c r="BP103" t="n">
-        <v>160</v>
+        <v>494</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>xWC2qHqU</t>
+          <t>hrmC3KUo</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -20190,76 +20186,76 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">stamford bridge
+  london </t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>31876</v>
+        <v>40341</v>
       </c>
       <c r="F104" t="n">
-        <v>31596</v>
+        <v>39295</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>2.47</v>
+        <v>4.31</v>
       </c>
       <c r="L104" t="n">
-        <v>0.06</v>
+        <v>0.93</v>
       </c>
       <c r="M104" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="N104" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="O104" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="P104" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>14</v>
+      </c>
+      <c r="R104" t="n">
         <v>2</v>
       </c>
-      <c r="Q104" t="n">
-        <v>8</v>
-      </c>
-      <c r="R104" t="n">
-        <v>1</v>
-      </c>
       <c r="S104" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T104" t="n">
         <v>10</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="W104" t="n">
@@ -20278,123 +20274,127 @@
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr"/>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
       <c r="AE104" t="n">
-        <v>26.11111111111111</v>
+        <v>24</v>
       </c>
       <c r="AF104" t="n">
-        <v>182.8888888888889</v>
+        <v>183.5555555555555</v>
       </c>
       <c r="AG104" t="n">
-        <v>1.444444444444444</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AH104" t="n">
-        <v>76</v>
+        <v>78.33333333333333</v>
       </c>
       <c r="AI104" t="n">
-        <v>9977777.777777778</v>
+        <v>19111111.11111111</v>
       </c>
       <c r="AJ104" t="n">
-        <v>80.11111111111111</v>
+        <v>83.11111111111111</v>
       </c>
       <c r="AK104" t="n">
-        <v>26.45454545454545</v>
+        <v>27.81818181818182</v>
       </c>
       <c r="AL104" t="n">
-        <v>182.3636363636364</v>
+        <v>183.9090909090909</v>
       </c>
       <c r="AM104" t="n">
-        <v>2.090909090909091</v>
+        <v>2.181818181818182</v>
       </c>
       <c r="AN104" t="n">
-        <v>79.54545454545455</v>
+        <v>79.18181818181819</v>
       </c>
       <c r="AO104" t="n">
-        <v>25127272.72727273</v>
+        <v>19545454.54545455</v>
       </c>
       <c r="AP104" t="n">
-        <v>81.45454545454545</v>
+        <v>80.54545454545455</v>
       </c>
       <c r="AQ104" t="n">
-        <v>21.31578947368421</v>
+        <v>22.95652173913043</v>
       </c>
       <c r="AR104" t="n">
-        <v>177.8421052631579</v>
+        <v>183.8260869565217</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.157894736842105</v>
+        <v>1.652173913043478</v>
       </c>
       <c r="AT104" t="n">
-        <v>71.57894736842105</v>
+        <v>74.82608695652173</v>
       </c>
       <c r="AU104" t="n">
-        <v>6010526.315789473</v>
+        <v>19750000</v>
       </c>
       <c r="AV104" t="n">
-        <v>80.73684210526316</v>
+        <v>82.56521739130434</v>
       </c>
       <c r="AW104" t="n">
-        <v>23.33333333333333</v>
+        <v>27.88235294117647</v>
       </c>
       <c r="AX104" t="n">
-        <v>183.9444444444445</v>
+        <v>178.8235294117647</v>
       </c>
       <c r="AY104" t="n">
-        <v>1.611111111111111</v>
+        <v>1.705882352941176</v>
       </c>
       <c r="AZ104" t="n">
-        <v>72.94444444444444</v>
+        <v>74.41176470588235</v>
       </c>
       <c r="BA104" t="n">
-        <v>10123611.11111111</v>
+        <v>10511764.70588235</v>
       </c>
       <c r="BB104" t="n">
-        <v>78.88888888888889</v>
+        <v>77.82352941176471</v>
       </c>
       <c r="BC104" t="n">
-        <v>25.5</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="BD104" t="n">
-        <v>177.5</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="BE104" t="n">
-        <v>1.5</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BF104" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BG104" t="n">
-        <v>604</v>
+        <v>448</v>
       </c>
       <c r="BH104" t="n">
-        <v>92500000</v>
+        <v>102050000</v>
       </c>
       <c r="BI104" t="n">
-        <v>645</v>
+        <v>488</v>
       </c>
       <c r="BJ104" t="n">
-        <v>26.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="BK104" t="n">
-        <v>183.8333333333333</v>
+        <v>186</v>
       </c>
       <c r="BL104" t="n">
         <v>2</v>
       </c>
       <c r="BM104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BN104" t="n">
-        <v>485</v>
+        <v>155</v>
       </c>
       <c r="BO104" t="n">
-        <v>167500000</v>
+        <v>28500000</v>
       </c>
       <c r="BP104" t="n">
-        <v>494</v>
+        <v>160</v>
       </c>
     </row>
     <row r="105">
@@ -21252,7 +21252,7 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>zkqE7cCn</t>
+          <t>ry0m3N33</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -21260,76 +21260,76 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">eltringham g 
+          <t xml:space="preserve">martin s 
   eng </t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
+          <t xml:space="preserve">the hawthorns
+  west bromwich </t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>21088</v>
+        <v>26688</v>
       </c>
       <c r="F109" t="n">
-        <v>17661</v>
+        <v>25386</v>
       </c>
       <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="n">
         <v>0</v>
       </c>
-      <c r="H109" t="n">
-        <v>1</v>
-      </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>1.63</v>
+        <v>2.39</v>
       </c>
       <c r="L109" t="n">
-        <v>0.57</v>
+        <v>0.14</v>
       </c>
       <c r="M109" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="N109" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O109" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P109" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q109" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S109" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T109" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>tMUvLt7h</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>MsDWbjnD</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="W109" t="n">
@@ -21346,129 +21346,121 @@
       </c>
       <c r="AA109" t="inlineStr"/>
       <c r="AB109" t="inlineStr"/>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
+      <c r="AC109" t="inlineStr"/>
+      <c r="AD109" t="inlineStr"/>
       <c r="AE109" t="n">
-        <v>23.125</v>
+        <v>26.7</v>
       </c>
       <c r="AF109" t="n">
-        <v>179.625</v>
+        <v>185.3</v>
       </c>
       <c r="AG109" t="n">
         <v>1</v>
       </c>
       <c r="AH109" t="n">
-        <v>68.125</v>
+        <v>70.8</v>
       </c>
       <c r="AI109" t="n">
-        <v>2037500</v>
+        <v>2250000</v>
       </c>
       <c r="AJ109" t="n">
-        <v>76</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AK109" t="n">
-        <v>24.6</v>
+        <v>26.22222222222222</v>
       </c>
       <c r="AL109" t="n">
-        <v>180.5</v>
+        <v>184.5555555555555</v>
       </c>
       <c r="AM109" t="n">
         <v>1</v>
       </c>
       <c r="AN109" t="n">
-        <v>69.2</v>
+        <v>70.55555555555556</v>
       </c>
       <c r="AO109" t="n">
-        <v>2452500</v>
+        <v>2188888.888888889</v>
       </c>
       <c r="AP109" t="n">
-        <v>74.40000000000001</v>
+        <v>72.55555555555556</v>
       </c>
       <c r="AQ109" t="n">
-        <v>24.52941176470588</v>
+        <v>28</v>
       </c>
       <c r="AR109" t="n">
-        <v>180.1176470588235</v>
+        <v>183.3478260869565</v>
       </c>
       <c r="AS109" t="n">
-        <v>1</v>
+        <v>1.130434782608696</v>
       </c>
       <c r="AT109" t="n">
-        <v>66.94117647058823</v>
+        <v>71.65217391304348</v>
       </c>
       <c r="AU109" t="n">
-        <v>1445588.235294118</v>
+        <v>2821739.130434783</v>
       </c>
       <c r="AV109" t="n">
-        <v>72</v>
+        <v>73.52173913043478</v>
       </c>
       <c r="AW109" t="n">
-        <v>26.25</v>
+        <v>22.21052631578947</v>
       </c>
       <c r="AX109" t="n">
-        <v>180.1666666666667</v>
+        <v>181.6842105263158</v>
       </c>
       <c r="AY109" t="n">
         <v>1</v>
       </c>
       <c r="AZ109" t="n">
-        <v>68.16666666666667</v>
+        <v>65.42105263157895</v>
       </c>
       <c r="BA109" t="n">
-        <v>1618750</v>
+        <v>1511842.105263158</v>
       </c>
       <c r="BB109" t="n">
-        <v>72.54166666666667</v>
+        <v>74.15789473684211</v>
       </c>
       <c r="BC109" t="n">
-        <v>28.5</v>
+        <v>23</v>
       </c>
       <c r="BD109" t="n">
-        <v>175.25</v>
+        <v>182</v>
       </c>
       <c r="BE109" t="n">
         <v>1</v>
       </c>
       <c r="BF109" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BG109" t="n">
-        <v>269</v>
+        <v>140</v>
       </c>
       <c r="BH109" t="n">
-        <v>3900000</v>
+        <v>4700000</v>
       </c>
       <c r="BI109" t="n">
-        <v>281</v>
+        <v>151</v>
       </c>
       <c r="BJ109" t="n">
-        <v>29.5</v>
+        <v>26.5</v>
       </c>
       <c r="BK109" t="n">
-        <v>180.5</v>
+        <v>186.5</v>
       </c>
       <c r="BL109" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BM109" t="n">
         <v>2</v>
       </c>
       <c r="BN109" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="BO109" t="n">
-        <v>2700000</v>
+        <v>36400000</v>
       </c>
       <c r="BP109" t="n">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110">
@@ -21914,7 +21906,7 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>ry0m3N33</t>
+          <t>4WLAk4Z3</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -21922,76 +21914,76 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">martin s 
+          <t xml:space="preserve">langford o 
   eng </t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">the hawthorns
-  west bromwich </t>
+          <t xml:space="preserve">st  andrew s stadium
+  birmingham </t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>26688</v>
+        <v>29409</v>
       </c>
       <c r="F112" t="n">
-        <v>25386</v>
+        <v>27680</v>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>2.39</v>
+        <v>1.31</v>
       </c>
       <c r="L112" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="M112" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="N112" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="O112" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P112" t="n">
         <v>5</v>
       </c>
       <c r="Q112" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="n">
         <v>8</v>
       </c>
-      <c r="T112" t="n">
-        <v>15</v>
-      </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>6wEAqBAE</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="W112" t="n">
@@ -22008,85 +22000,93 @@
       </c>
       <c r="AA112" t="inlineStr"/>
       <c r="AB112" t="inlineStr"/>
-      <c r="AC112" t="inlineStr"/>
-      <c r="AD112" t="inlineStr"/>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
       <c r="AE112" t="n">
-        <v>26.7</v>
+        <v>24.63636363636364</v>
       </c>
       <c r="AF112" t="n">
-        <v>185.3</v>
+        <v>181.5454545454545</v>
       </c>
       <c r="AG112" t="n">
         <v>1</v>
       </c>
       <c r="AH112" t="n">
-        <v>70.8</v>
+        <v>69.09090909090909</v>
       </c>
       <c r="AI112" t="n">
-        <v>2250000</v>
+        <v>2061818.181818182</v>
       </c>
       <c r="AJ112" t="n">
-        <v>72.90000000000001</v>
+        <v>73.81818181818181</v>
       </c>
       <c r="AK112" t="n">
-        <v>26.22222222222222</v>
+        <v>25.5</v>
       </c>
       <c r="AL112" t="n">
-        <v>184.5555555555555</v>
+        <v>182.4</v>
       </c>
       <c r="AM112" t="n">
         <v>1</v>
       </c>
       <c r="AN112" t="n">
-        <v>70.55555555555556</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AO112" t="n">
-        <v>2188888.888888889</v>
+        <v>3230000</v>
       </c>
       <c r="AP112" t="n">
-        <v>72.55555555555556</v>
+        <v>74.8</v>
       </c>
       <c r="AQ112" t="n">
-        <v>28</v>
+        <v>26.25</v>
       </c>
       <c r="AR112" t="n">
-        <v>183.3478260869565</v>
+        <v>178.8</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.130434782608696</v>
+        <v>1</v>
       </c>
       <c r="AT112" t="n">
-        <v>71.65217391304348</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="AU112" t="n">
-        <v>2821739.130434783</v>
+        <v>1647500</v>
       </c>
       <c r="AV112" t="n">
-        <v>73.52173913043478</v>
+        <v>72.5</v>
       </c>
       <c r="AW112" t="n">
-        <v>22.21052631578947</v>
+        <v>25.60869565217391</v>
       </c>
       <c r="AX112" t="n">
-        <v>181.6842105263158</v>
+        <v>183.9130434782609</v>
       </c>
       <c r="AY112" t="n">
         <v>1</v>
       </c>
       <c r="AZ112" t="n">
-        <v>65.42105263157895</v>
+        <v>68.26086956521739</v>
       </c>
       <c r="BA112" t="n">
-        <v>1511842.105263158</v>
+        <v>2070434.782608696</v>
       </c>
       <c r="BB112" t="n">
-        <v>74.15789473684211</v>
+        <v>72.82608695652173</v>
       </c>
       <c r="BC112" t="n">
         <v>23</v>
       </c>
       <c r="BD112" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="BE112" t="n">
         <v>1</v>
@@ -22095,40 +22095,40 @@
         <v>2</v>
       </c>
       <c r="BG112" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="BH112" t="n">
-        <v>4700000</v>
+        <v>2400000</v>
       </c>
       <c r="BI112" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="BJ112" t="n">
-        <v>26.5</v>
+        <v>25</v>
       </c>
       <c r="BK112" t="n">
-        <v>186.5</v>
+        <v>175</v>
       </c>
       <c r="BL112" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BM112" t="n">
         <v>2</v>
       </c>
       <c r="BN112" t="n">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="BO112" t="n">
-        <v>36400000</v>
+        <v>3700000</v>
       </c>
       <c r="BP112" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>4WLAk4Z3</t>
+          <t>zkqE7cCn</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -22136,76 +22136,76 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">langford o 
+          <t xml:space="preserve">eltringham g 
   eng </t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  andrew s stadium
-  birmingham </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>29409</v>
+        <v>21088</v>
       </c>
       <c r="F113" t="n">
-        <v>27680</v>
+        <v>17661</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="K113" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="L113" t="n">
-        <v>0.1</v>
+        <v>0.57</v>
       </c>
       <c r="M113" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="N113" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="O113" t="n">
+        <v>9</v>
+      </c>
+      <c r="P113" t="n">
         <v>12</v>
       </c>
-      <c r="P113" t="n">
-        <v>5</v>
-      </c>
       <c r="Q113" t="n">
+        <v>2</v>
+      </c>
+      <c r="R113" t="n">
+        <v>4</v>
+      </c>
+      <c r="S113" t="n">
         <v>3</v>
       </c>
-      <c r="R113" t="n">
-        <v>2</v>
-      </c>
-      <c r="S113" t="n">
-        <v>10</v>
-      </c>
       <c r="T113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>neBDmKpm</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>OS3AwgCU</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="W113" t="n">
@@ -22224,112 +22224,112 @@
       <c r="AB113" t="inlineStr"/>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="AE113" t="n">
-        <v>24.63636363636364</v>
+        <v>23.125</v>
       </c>
       <c r="AF113" t="n">
-        <v>181.5454545454545</v>
+        <v>179.625</v>
       </c>
       <c r="AG113" t="n">
         <v>1</v>
       </c>
       <c r="AH113" t="n">
-        <v>69.09090909090909</v>
+        <v>68.125</v>
       </c>
       <c r="AI113" t="n">
-        <v>2061818.181818182</v>
+        <v>2037500</v>
       </c>
       <c r="AJ113" t="n">
-        <v>73.81818181818181</v>
+        <v>76</v>
       </c>
       <c r="AK113" t="n">
-        <v>25.5</v>
+        <v>24.6</v>
       </c>
       <c r="AL113" t="n">
-        <v>182.4</v>
+        <v>180.5</v>
       </c>
       <c r="AM113" t="n">
         <v>1</v>
       </c>
       <c r="AN113" t="n">
-        <v>71.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="AO113" t="n">
-        <v>3230000</v>
+        <v>2452500</v>
       </c>
       <c r="AP113" t="n">
-        <v>74.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AQ113" t="n">
+        <v>24.52941176470588</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>180.1176470588235</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>66.94117647058823</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>1445588.235294118</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>72</v>
+      </c>
+      <c r="AW113" t="n">
         <v>26.25</v>
       </c>
-      <c r="AR113" t="n">
-        <v>178.8</v>
-      </c>
-      <c r="AS113" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT113" t="n">
-        <v>68.15000000000001</v>
-      </c>
-      <c r="AU113" t="n">
-        <v>1647500</v>
-      </c>
-      <c r="AV113" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="AW113" t="n">
-        <v>25.60869565217391</v>
-      </c>
       <c r="AX113" t="n">
-        <v>183.9130434782609</v>
+        <v>180.1666666666667</v>
       </c>
       <c r="AY113" t="n">
         <v>1</v>
       </c>
       <c r="AZ113" t="n">
-        <v>68.26086956521739</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="BA113" t="n">
-        <v>2070434.782608696</v>
+        <v>1618750</v>
       </c>
       <c r="BB113" t="n">
-        <v>72.82608695652173</v>
+        <v>72.54166666666667</v>
       </c>
       <c r="BC113" t="n">
-        <v>23</v>
+        <v>28.5</v>
       </c>
       <c r="BD113" t="n">
-        <v>184</v>
+        <v>175.25</v>
       </c>
       <c r="BE113" t="n">
         <v>1</v>
       </c>
       <c r="BF113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BG113" t="n">
-        <v>131</v>
+        <v>269</v>
       </c>
       <c r="BH113" t="n">
-        <v>2400000</v>
+        <v>3900000</v>
       </c>
       <c r="BI113" t="n">
-        <v>143</v>
+        <v>281</v>
       </c>
       <c r="BJ113" t="n">
-        <v>25</v>
+        <v>29.5</v>
       </c>
       <c r="BK113" t="n">
-        <v>175</v>
+        <v>180.5</v>
       </c>
       <c r="BL113" t="n">
         <v>1</v>
@@ -22338,19 +22338,19 @@
         <v>2</v>
       </c>
       <c r="BN113" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="BO113" t="n">
-        <v>3700000</v>
+        <v>2700000</v>
       </c>
       <c r="BP113" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>4p1q43lc</t>
+          <t>0bFJmr4G</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -22358,76 +22358,76 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward g 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium of light
-  sunderland </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>48707</v>
+        <v>29673</v>
       </c>
       <c r="F114" t="n">
-        <v>41222</v>
+        <v>29011</v>
       </c>
       <c r="G114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" t="n">
         <v>0</v>
       </c>
-      <c r="H114" t="n">
-        <v>2</v>
-      </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>llcCvIcG</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="L114" t="n">
-        <v>1.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M114" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N114" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O114" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="P114" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R114" t="n">
         <v>2</v>
       </c>
       <c r="S114" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T114" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>bPZzRChI</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>Y39YvFx6</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="W114" t="n">
@@ -22446,129 +22446,121 @@
       <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr"/>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
       <c r="AE114" t="n">
-        <v>22.4</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="AF114" t="n">
-        <v>181.3</v>
+        <v>182.1818181818182</v>
       </c>
       <c r="AG114" t="n">
         <v>1</v>
       </c>
       <c r="AH114" t="n">
-        <v>68.90000000000001</v>
+        <v>71.18181818181819</v>
       </c>
       <c r="AI114" t="n">
-        <v>2735000</v>
+        <v>2827272.727272727</v>
       </c>
       <c r="AJ114" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="AK114" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="AL114" t="n">
-        <v>182.1</v>
-      </c>
-      <c r="AM114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN114" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="AO114" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="AP114" t="n">
-        <v>70.3</v>
-      </c>
+        <v>74.63636363636364</v>
+      </c>
+      <c r="AK114" t="inlineStr"/>
+      <c r="AL114" t="inlineStr"/>
+      <c r="AM114" t="inlineStr"/>
+      <c r="AN114" t="inlineStr"/>
+      <c r="AO114" t="inlineStr"/>
+      <c r="AP114" t="inlineStr"/>
       <c r="AQ114" t="n">
-        <v>23.17647058823529</v>
+        <v>26.375</v>
       </c>
       <c r="AR114" t="n">
-        <v>182.0588235294118</v>
+        <v>185</v>
       </c>
       <c r="AS114" t="n">
         <v>1</v>
       </c>
       <c r="AT114" t="n">
-        <v>66</v>
+        <v>69.20833333333333</v>
       </c>
       <c r="AU114" t="n">
-        <v>1720588.235294118</v>
+        <v>2037500</v>
       </c>
       <c r="AV114" t="n">
-        <v>73.41176470588235</v>
+        <v>72.83333333333333</v>
       </c>
       <c r="AW114" t="n">
-        <v>26.08333333333333</v>
+        <v>21.95</v>
       </c>
       <c r="AX114" t="n">
-        <v>185.4166666666667</v>
+        <v>183.5</v>
       </c>
       <c r="AY114" t="n">
         <v>1</v>
       </c>
       <c r="AZ114" t="n">
-        <v>66.33333333333333</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="BA114" t="n">
-        <v>1110416.666666667</v>
+        <v>1255000</v>
       </c>
       <c r="BB114" t="n">
-        <v>69.83333333333333</v>
+        <v>74.5</v>
       </c>
       <c r="BC114" t="n">
-        <v>22.16666666666667</v>
+        <v>25.5</v>
       </c>
       <c r="BD114" t="n">
-        <v>179</v>
+        <v>182.5</v>
       </c>
       <c r="BE114" t="n">
         <v>1</v>
       </c>
       <c r="BF114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>140</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>145</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>182</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM114" t="n">
         <v>6</v>
       </c>
-      <c r="BG114" t="n">
-        <v>396</v>
-      </c>
-      <c r="BH114" t="n">
-        <v>9900000</v>
-      </c>
-      <c r="BI114" t="n">
-        <v>443</v>
-      </c>
-      <c r="BJ114" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="BK114" t="n">
-        <v>172</v>
-      </c>
-      <c r="BL114" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM114" t="n">
-        <v>2</v>
-      </c>
       <c r="BN114" t="n">
-        <v>137</v>
+        <v>393</v>
       </c>
       <c r="BO114" t="n">
-        <v>3100000</v>
+        <v>4875000</v>
       </c>
       <c r="BP114" t="n">
-        <v>142</v>
+        <v>412</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>AX4gstsp</t>
+          <t>4p1q43lc</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -22576,76 +22568,76 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">bell j 
+          <t xml:space="preserve">ward g 
   eng </t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">riverside stadium
-  middlesbrough </t>
+          <t xml:space="preserve">stadium of light
+  sunderland </t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>34742</v>
+        <v>48707</v>
       </c>
       <c r="F115" t="n">
-        <v>28289</v>
+        <v>41222</v>
       </c>
       <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M115" t="n">
+        <v>65</v>
+      </c>
+      <c r="N115" t="n">
+        <v>35</v>
+      </c>
+      <c r="O115" t="n">
+        <v>18</v>
+      </c>
+      <c r="P115" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q115" t="n">
         <v>3</v>
       </c>
-      <c r="H115" t="n">
-        <v>1</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>6F0lvLNC</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
-      <c r="K115" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="L115" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="M115" t="n">
-        <v>55</v>
-      </c>
-      <c r="N115" t="n">
-        <v>45</v>
-      </c>
-      <c r="O115" t="n">
-        <v>12</v>
-      </c>
-      <c r="P115" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>6</v>
-      </c>
       <c r="R115" t="n">
+        <v>2</v>
+      </c>
+      <c r="S115" t="n">
         <v>4</v>
       </c>
-      <c r="S115" t="n">
-        <v>9</v>
-      </c>
       <c r="T115" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>phM8NElP</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>n94TZqsm</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="W115" t="n">
@@ -22667,88 +22659,84 @@
           <t>p6ahwuwJ</t>
         </is>
       </c>
-      <c r="AD115" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
+      <c r="AD115" t="inlineStr"/>
       <c r="AE115" t="n">
-        <v>23.3</v>
+        <v>22.4</v>
       </c>
       <c r="AF115" t="n">
-        <v>182.3</v>
+        <v>181.3</v>
       </c>
       <c r="AG115" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AH115" t="n">
-        <v>67.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AI115" t="n">
-        <v>2225000</v>
+        <v>2735000</v>
       </c>
       <c r="AJ115" t="n">
-        <v>75.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AK115" t="n">
-        <v>24.09090909090909</v>
+        <v>27.2</v>
       </c>
       <c r="AL115" t="n">
-        <v>184.6363636363636</v>
+        <v>182.1</v>
       </c>
       <c r="AM115" t="n">
         <v>1</v>
       </c>
       <c r="AN115" t="n">
-        <v>69.54545454545455</v>
+        <v>67.7</v>
       </c>
       <c r="AO115" t="n">
-        <v>2200000</v>
+        <v>1260000</v>
       </c>
       <c r="AP115" t="n">
-        <v>74.09090909090909</v>
+        <v>70.3</v>
       </c>
       <c r="AQ115" t="n">
-        <v>23.21052631578947</v>
+        <v>23.17647058823529</v>
       </c>
       <c r="AR115" t="n">
-        <v>180.3684210526316</v>
+        <v>182.0588235294118</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.052631578947368</v>
+        <v>1</v>
       </c>
       <c r="AT115" t="n">
-        <v>68.26315789473684</v>
+        <v>66</v>
       </c>
       <c r="AU115" t="n">
-        <v>2239473.684210526</v>
+        <v>1720588.235294118</v>
       </c>
       <c r="AV115" t="n">
-        <v>74.94736842105263</v>
+        <v>73.41176470588235</v>
       </c>
       <c r="AW115" t="n">
-        <v>22</v>
+        <v>26.08333333333333</v>
       </c>
       <c r="AX115" t="n">
-        <v>181.75</v>
+        <v>185.4166666666667</v>
       </c>
       <c r="AY115" t="n">
         <v>1</v>
       </c>
       <c r="AZ115" t="n">
-        <v>64.875</v>
+        <v>66.33333333333333</v>
       </c>
       <c r="BA115" t="n">
-        <v>1591875</v>
+        <v>1110416.666666667</v>
       </c>
       <c r="BB115" t="n">
-        <v>73.75</v>
+        <v>69.83333333333333</v>
       </c>
       <c r="BC115" t="n">
-        <v>25.16666666666667</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="BD115" t="n">
-        <v>183.3333333333333</v>
+        <v>179</v>
       </c>
       <c r="BE115" t="n">
         <v>1</v>
@@ -22757,34 +22745,34 @@
         <v>6</v>
       </c>
       <c r="BG115" t="n">
-        <v>432</v>
+        <v>396</v>
       </c>
       <c r="BH115" t="n">
-        <v>19500000</v>
+        <v>9900000</v>
       </c>
       <c r="BI115" t="n">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="BJ115" t="n">
-        <v>21.66666666666667</v>
+        <v>26.5</v>
       </c>
       <c r="BK115" t="n">
-        <v>181.3333333333333</v>
+        <v>172</v>
       </c>
       <c r="BL115" t="n">
         <v>1</v>
       </c>
       <c r="BM115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN115" t="n">
-        <v>198</v>
+        <v>137</v>
       </c>
       <c r="BO115" t="n">
-        <v>4700000</v>
+        <v>3100000</v>
       </c>
       <c r="BP115" t="n">
-        <v>221</v>
+        <v>142</v>
       </c>
     </row>
     <row r="116">
@@ -23004,7 +22992,7 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>6FvA8wct</t>
+          <t>vkENn2JM</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -23012,76 +23000,76 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">davies a 
+          <t xml:space="preserve">donohue m 
   eng </t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">elland road
+  leeds </t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>12021</v>
+        <v>37792</v>
       </c>
       <c r="F117" t="n">
-        <v>10547</v>
+        <v>36766</v>
       </c>
       <c r="G117" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
         <v>2</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>tUxUbLR2</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="K117" t="n">
-        <v>3.21</v>
+        <v>0.83</v>
       </c>
       <c r="L117" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M117" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="N117" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="O117" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P117" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Q117" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S117" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T117" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>OEy2L7Zo</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="W117" t="n">
@@ -23098,131 +23086,131 @@
       </c>
       <c r="AA117" t="inlineStr"/>
       <c r="AB117" t="inlineStr"/>
-      <c r="AC117" t="inlineStr"/>
-      <c r="AD117" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr"/>
       <c r="AE117" t="n">
-        <v>26.9</v>
+        <v>23.44444444444444</v>
       </c>
       <c r="AF117" t="n">
-        <v>181.7</v>
+        <v>184.4444444444445</v>
       </c>
       <c r="AG117" t="n">
-        <v>1</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AH117" t="n">
-        <v>66.09999999999999</v>
+        <v>74.55555555555556</v>
       </c>
       <c r="AI117" t="n">
-        <v>972500</v>
+        <v>9033333.333333334</v>
       </c>
       <c r="AJ117" t="n">
-        <v>69</v>
+        <v>80.11111111111111</v>
       </c>
       <c r="AK117" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="AL117" t="n">
-        <v>182.9</v>
+        <v>179.5</v>
       </c>
       <c r="AM117" t="n">
         <v>1</v>
       </c>
       <c r="AN117" t="n">
-        <v>69</v>
+        <v>73.2</v>
       </c>
       <c r="AO117" t="n">
-        <v>1900000</v>
+        <v>4620000</v>
       </c>
       <c r="AP117" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AQ117" t="n">
-        <v>26.9375</v>
+        <v>23.21052631578947</v>
       </c>
       <c r="AR117" t="n">
-        <v>182.8125</v>
+        <v>181.421052631579</v>
       </c>
       <c r="AS117" t="n">
         <v>1</v>
       </c>
       <c r="AT117" t="n">
-        <v>66</v>
+        <v>72.52631578947368</v>
       </c>
       <c r="AU117" t="n">
-        <v>948437.5</v>
+        <v>4952631.578947368</v>
       </c>
       <c r="AV117" t="n">
-        <v>69.4375</v>
+        <v>78.78947368421052</v>
       </c>
       <c r="AW117" t="n">
-        <v>23</v>
+        <v>25.95238095238095</v>
       </c>
       <c r="AX117" t="n">
-        <v>184.3809523809524</v>
+        <v>178.3809523809524</v>
       </c>
       <c r="AY117" t="n">
         <v>1</v>
       </c>
       <c r="AZ117" t="n">
-        <v>63.80952380952381</v>
+        <v>71.61904761904762</v>
       </c>
       <c r="BA117" t="n">
-        <v>1308809.523809524</v>
+        <v>3061904.761904762</v>
       </c>
       <c r="BB117" t="n">
-        <v>70.0952380952381</v>
+        <v>74.04761904761905</v>
       </c>
       <c r="BC117" t="n">
-        <v>27.16666666666667</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="BD117" t="n">
-        <v>185</v>
+        <v>185.6666666666667</v>
       </c>
       <c r="BE117" t="n">
         <v>1</v>
       </c>
       <c r="BF117" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BG117" t="n">
-        <v>402</v>
+        <v>212</v>
       </c>
       <c r="BH117" t="n">
-        <v>7000000</v>
+        <v>13700000</v>
       </c>
       <c r="BI117" t="n">
-        <v>415</v>
+        <v>234</v>
       </c>
       <c r="BJ117" t="n">
-        <v>24.75</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="BK117" t="n">
-        <v>184.125</v>
+        <v>180.6666666666667</v>
       </c>
       <c r="BL117" t="n">
         <v>1</v>
       </c>
       <c r="BM117" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BN117" t="n">
-        <v>553</v>
+        <v>205</v>
       </c>
       <c r="BO117" t="n">
-        <v>16475000</v>
+        <v>7700000</v>
       </c>
       <c r="BP117" t="n">
-        <v>586</v>
+        <v>232</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>0bFJmr4G</t>
+          <t>8OIRoMYS</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
@@ -23230,76 +23218,76 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">kitchen a 
   eng </t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>29673</v>
+        <v>32261</v>
       </c>
       <c r="F118" t="n">
-        <v>29011</v>
+        <v>32117</v>
       </c>
       <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
         <v>2</v>
       </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="K118" t="n">
-        <v>1.43</v>
+        <v>1.06</v>
       </c>
       <c r="L118" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.93</v>
       </c>
       <c r="M118" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N118" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="O118" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="P118" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q118" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R118" t="n">
         <v>2</v>
       </c>
       <c r="S118" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T118" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>lhUKMQZu</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="W118" t="n">
@@ -23318,121 +23306,119 @@
       <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>tUxUbLR2</t>
+          <t>z3dmTMMO</t>
         </is>
       </c>
       <c r="AE118" t="n">
-        <v>26.27272727272727</v>
+        <v>27</v>
       </c>
       <c r="AF118" t="n">
-        <v>182.1818181818182</v>
+        <v>182.7</v>
       </c>
       <c r="AG118" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AH118" t="n">
-        <v>71.18181818181819</v>
+        <v>76</v>
       </c>
       <c r="AI118" t="n">
-        <v>2827272.727272727</v>
+        <v>8840000</v>
       </c>
       <c r="AJ118" t="n">
-        <v>74.63636363636364</v>
-      </c>
-      <c r="AK118" t="inlineStr"/>
-      <c r="AL118" t="inlineStr"/>
-      <c r="AM118" t="inlineStr"/>
-      <c r="AN118" t="inlineStr"/>
-      <c r="AO118" t="inlineStr"/>
-      <c r="AP118" t="inlineStr"/>
+        <v>77.8</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>2215000</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>73</v>
+      </c>
       <c r="AQ118" t="n">
-        <v>26.375</v>
+        <v>25.89473684210526</v>
       </c>
       <c r="AR118" t="n">
-        <v>185</v>
+        <v>179.4736842105263</v>
       </c>
       <c r="AS118" t="n">
-        <v>1</v>
+        <v>1.315789473684211</v>
       </c>
       <c r="AT118" t="n">
-        <v>69.20833333333333</v>
+        <v>72.15789473684211</v>
       </c>
       <c r="AU118" t="n">
-        <v>2037500</v>
+        <v>4396052.631578947</v>
       </c>
       <c r="AV118" t="n">
-        <v>72.83333333333333</v>
+        <v>75.31578947368421</v>
       </c>
       <c r="AW118" t="n">
-        <v>21.95</v>
+        <v>21.23529411764706</v>
       </c>
       <c r="AX118" t="n">
-        <v>183.5</v>
+        <v>177.8235294117647</v>
       </c>
       <c r="AY118" t="n">
         <v>1</v>
       </c>
       <c r="AZ118" t="n">
-        <v>64.34999999999999</v>
+        <v>65.94117647058823</v>
       </c>
       <c r="BA118" t="n">
-        <v>1255000</v>
+        <v>1877941.176470588</v>
       </c>
       <c r="BB118" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="BC118" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BD118" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="BE118" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF118" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG118" t="n">
-        <v>140</v>
-      </c>
-      <c r="BH118" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="BI118" t="n">
-        <v>145</v>
-      </c>
+        <v>75.47058823529412</v>
+      </c>
+      <c r="BC118" t="inlineStr"/>
+      <c r="BD118" t="inlineStr"/>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr"/>
+      <c r="BG118" t="inlineStr"/>
+      <c r="BH118" t="inlineStr"/>
+      <c r="BI118" t="inlineStr"/>
       <c r="BJ118" t="n">
-        <v>27.66666666666667</v>
+        <v>25.2</v>
       </c>
       <c r="BK118" t="n">
-        <v>182</v>
+        <v>179.6</v>
       </c>
       <c r="BL118" t="n">
         <v>1</v>
       </c>
       <c r="BM118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN118" t="n">
-        <v>393</v>
+        <v>345</v>
       </c>
       <c r="BO118" t="n">
-        <v>4875000</v>
+        <v>8800000</v>
       </c>
       <c r="BP118" t="n">
-        <v>412</v>
+        <v>364</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>vkENn2JM</t>
+          <t>AX4gstsp</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
@@ -23440,76 +23426,76 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">donohue m 
+          <t xml:space="preserve">bell j 
   eng </t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">elland road
-  leeds </t>
+          <t xml:space="preserve">riverside stadium
+  middlesbrough </t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>37792</v>
+        <v>34742</v>
       </c>
       <c r="F119" t="n">
-        <v>36766</v>
+        <v>28289</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>tUxUbLR2</t>
+          <t>6F0lvLNC</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>0.83</v>
+        <v>1.76</v>
       </c>
       <c r="L119" t="n">
-        <v>1.02</v>
+        <v>0.82</v>
       </c>
       <c r="M119" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N119" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O119" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P119" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q119" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R119" t="n">
         <v>4</v>
       </c>
       <c r="S119" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T119" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="W119" t="n">
@@ -23528,108 +23514,112 @@
       <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr"/>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
       <c r="AE119" t="n">
-        <v>23.44444444444444</v>
+        <v>23.3</v>
       </c>
       <c r="AF119" t="n">
-        <v>184.4444444444445</v>
+        <v>182.3</v>
       </c>
       <c r="AG119" t="n">
-        <v>1.222222222222222</v>
+        <v>1.1</v>
       </c>
       <c r="AH119" t="n">
-        <v>74.55555555555556</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AI119" t="n">
-        <v>9033333.333333334</v>
+        <v>2225000</v>
       </c>
       <c r="AJ119" t="n">
-        <v>80.11111111111111</v>
+        <v>75.5</v>
       </c>
       <c r="AK119" t="n">
-        <v>25.9</v>
+        <v>24.09090909090909</v>
       </c>
       <c r="AL119" t="n">
-        <v>179.5</v>
+        <v>184.6363636363636</v>
       </c>
       <c r="AM119" t="n">
         <v>1</v>
       </c>
       <c r="AN119" t="n">
-        <v>73.2</v>
+        <v>69.54545454545455</v>
       </c>
       <c r="AO119" t="n">
-        <v>4620000</v>
+        <v>2200000</v>
       </c>
       <c r="AP119" t="n">
-        <v>76</v>
+        <v>74.09090909090909</v>
       </c>
       <c r="AQ119" t="n">
         <v>23.21052631578947</v>
       </c>
       <c r="AR119" t="n">
-        <v>181.421052631579</v>
+        <v>180.3684210526316</v>
       </c>
       <c r="AS119" t="n">
-        <v>1</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AT119" t="n">
-        <v>72.52631578947368</v>
+        <v>68.26315789473684</v>
       </c>
       <c r="AU119" t="n">
-        <v>4952631.578947368</v>
+        <v>2239473.684210526</v>
       </c>
       <c r="AV119" t="n">
-        <v>78.78947368421052</v>
+        <v>74.94736842105263</v>
       </c>
       <c r="AW119" t="n">
-        <v>25.95238095238095</v>
+        <v>22</v>
       </c>
       <c r="AX119" t="n">
-        <v>178.3809523809524</v>
+        <v>181.75</v>
       </c>
       <c r="AY119" t="n">
         <v>1</v>
       </c>
       <c r="AZ119" t="n">
-        <v>71.61904761904762</v>
+        <v>64.875</v>
       </c>
       <c r="BA119" t="n">
-        <v>3061904.761904762</v>
+        <v>1591875</v>
       </c>
       <c r="BB119" t="n">
-        <v>74.04761904761905</v>
+        <v>73.75</v>
       </c>
       <c r="BC119" t="n">
-        <v>22.33333333333333</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="BD119" t="n">
-        <v>185.6666666666667</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="BE119" t="n">
         <v>1</v>
       </c>
       <c r="BF119" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BG119" t="n">
-        <v>212</v>
+        <v>432</v>
       </c>
       <c r="BH119" t="n">
-        <v>13700000</v>
+        <v>19500000</v>
       </c>
       <c r="BI119" t="n">
-        <v>234</v>
+        <v>458</v>
       </c>
       <c r="BJ119" t="n">
-        <v>23.66666666666667</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="BK119" t="n">
-        <v>180.6666666666667</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="BL119" t="n">
         <v>1</v>
@@ -23638,19 +23628,19 @@
         <v>3</v>
       </c>
       <c r="BN119" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="BO119" t="n">
-        <v>7700000</v>
+        <v>4700000</v>
       </c>
       <c r="BP119" t="n">
-        <v>232</v>
+        <v>221</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>8OIRoMYS</t>
+          <t>hdfbt0dj</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
@@ -23658,76 +23648,76 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
+          <t xml:space="preserve">home park
+  plymouth </t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>32261</v>
+        <v>17000</v>
       </c>
       <c r="F120" t="n">
-        <v>32117</v>
+        <v>16881</v>
       </c>
       <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
         <v>0</v>
       </c>
-      <c r="H120" t="n">
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M120" t="n">
+        <v>34</v>
+      </c>
+      <c r="N120" t="n">
+        <v>66</v>
+      </c>
+      <c r="O120" t="n">
+        <v>11</v>
+      </c>
+      <c r="P120" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q120" t="n">
         <v>2</v>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>6Nl8nagD</t>
-        </is>
-      </c>
-      <c r="K120" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L120" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="M120" t="n">
-        <v>75</v>
-      </c>
-      <c r="N120" t="n">
-        <v>25</v>
-      </c>
-      <c r="O120" t="n">
-        <v>14</v>
-      </c>
-      <c r="P120" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>7</v>
-      </c>
       <c r="R120" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T120" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="W120" t="n">
@@ -23744,121 +23734,131 @@
       </c>
       <c r="AA120" t="inlineStr"/>
       <c r="AB120" t="inlineStr"/>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
+      <c r="AC120" t="inlineStr"/>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>z3dmTMMO</t>
+          <t>tUxUbLR2</t>
         </is>
       </c>
       <c r="AE120" t="n">
+        <v>23.45454545454545</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>181.8181818181818</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>68.18181818181819</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>2320454.545454545</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>75.45454545454545</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>181.0909090909091</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>3056818.181818182</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>180.85</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>66.84999999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1476250</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>25.38095238095238</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>179.2857142857143</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>69.57142857142857</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>2659523.80952381</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>74.23809523809524</v>
+      </c>
+      <c r="BC120" t="n">
         <v>27</v>
       </c>
-      <c r="AF120" t="n">
-        <v>182.7</v>
-      </c>
-      <c r="AG120" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH120" t="n">
-        <v>76</v>
-      </c>
-      <c r="AI120" t="n">
-        <v>8840000</v>
-      </c>
-      <c r="AJ120" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="AK120" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AL120" t="n">
-        <v>180.3</v>
-      </c>
-      <c r="AM120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN120" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO120" t="n">
-        <v>2215000</v>
-      </c>
-      <c r="AP120" t="n">
-        <v>73</v>
-      </c>
-      <c r="AQ120" t="n">
-        <v>25.89473684210526</v>
-      </c>
-      <c r="AR120" t="n">
-        <v>179.4736842105263</v>
-      </c>
-      <c r="AS120" t="n">
-        <v>1.315789473684211</v>
-      </c>
-      <c r="AT120" t="n">
-        <v>72.15789473684211</v>
-      </c>
-      <c r="AU120" t="n">
-        <v>4396052.631578947</v>
-      </c>
-      <c r="AV120" t="n">
-        <v>75.31578947368421</v>
-      </c>
-      <c r="AW120" t="n">
-        <v>21.23529411764706</v>
-      </c>
-      <c r="AX120" t="n">
-        <v>177.8235294117647</v>
-      </c>
-      <c r="AY120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ120" t="n">
-        <v>65.94117647058823</v>
-      </c>
-      <c r="BA120" t="n">
-        <v>1877941.176470588</v>
-      </c>
-      <c r="BB120" t="n">
-        <v>75.47058823529412</v>
-      </c>
-      <c r="BC120" t="inlineStr"/>
-      <c r="BD120" t="inlineStr"/>
-      <c r="BE120" t="inlineStr"/>
-      <c r="BF120" t="inlineStr"/>
-      <c r="BG120" t="inlineStr"/>
-      <c r="BH120" t="inlineStr"/>
-      <c r="BI120" t="inlineStr"/>
+      <c r="BD120" t="n">
+        <v>173</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>700000</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>65</v>
+      </c>
       <c r="BJ120" t="n">
-        <v>25.2</v>
+        <v>22</v>
       </c>
       <c r="BK120" t="n">
-        <v>179.6</v>
+        <v>178</v>
       </c>
       <c r="BL120" t="n">
         <v>1</v>
       </c>
       <c r="BM120" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BN120" t="n">
-        <v>345</v>
+        <v>74</v>
       </c>
       <c r="BO120" t="n">
-        <v>8800000</v>
+        <v>9500000</v>
       </c>
       <c r="BP120" t="n">
-        <v>364</v>
+        <v>83</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hdfbt0dj</t>
+          <t>6FvA8wct</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
@@ -23866,76 +23866,76 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">davies a 
   eng </t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">home park
-  plymouth </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>17000</v>
+        <v>12021</v>
       </c>
       <c r="F121" t="n">
-        <v>16881</v>
+        <v>10547</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>WpGM6ELj</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>S66R0t75</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="K121" t="n">
-        <v>0.46</v>
+        <v>3.21</v>
       </c>
       <c r="L121" t="n">
-        <v>0.5</v>
+        <v>1.01</v>
       </c>
       <c r="M121" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N121" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O121" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P121" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Q121" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S121" t="n">
+        <v>9</v>
+      </c>
+      <c r="T121" t="n">
         <v>6</v>
       </c>
-      <c r="T121" t="n">
-        <v>8</v>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>8tPSZqtA</t>
+          <t>zNcAe8Sa</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="W121" t="n">
@@ -23955,122 +23955,122 @@
       <c r="AC121" t="inlineStr"/>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>tUxUbLR2</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="AE121" t="n">
-        <v>23.45454545454545</v>
+        <v>26.9</v>
       </c>
       <c r="AF121" t="n">
-        <v>181.8181818181818</v>
+        <v>181.7</v>
       </c>
       <c r="AG121" t="n">
         <v>1</v>
       </c>
       <c r="AH121" t="n">
-        <v>68.18181818181819</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AI121" t="n">
-        <v>2320454.545454545</v>
+        <v>972500</v>
       </c>
       <c r="AJ121" t="n">
-        <v>75.45454545454545</v>
+        <v>69</v>
       </c>
       <c r="AK121" t="n">
-        <v>23.90909090909091</v>
+        <v>26</v>
       </c>
       <c r="AL121" t="n">
-        <v>181.0909090909091</v>
+        <v>182.9</v>
       </c>
       <c r="AM121" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AN121" t="n">
-        <v>69.63636363636364</v>
+        <v>69</v>
       </c>
       <c r="AO121" t="n">
-        <v>3056818.181818182</v>
+        <v>1900000</v>
       </c>
       <c r="AP121" t="n">
-        <v>75.27272727272727</v>
+        <v>72</v>
       </c>
       <c r="AQ121" t="n">
-        <v>25</v>
+        <v>26.9375</v>
       </c>
       <c r="AR121" t="n">
-        <v>180.85</v>
+        <v>182.8125</v>
       </c>
       <c r="AS121" t="n">
         <v>1</v>
       </c>
       <c r="AT121" t="n">
-        <v>66.84999999999999</v>
+        <v>66</v>
       </c>
       <c r="AU121" t="n">
-        <v>1476250</v>
+        <v>948437.5</v>
       </c>
       <c r="AV121" t="n">
-        <v>71.90000000000001</v>
+        <v>69.4375</v>
       </c>
       <c r="AW121" t="n">
-        <v>25.38095238095238</v>
+        <v>23</v>
       </c>
       <c r="AX121" t="n">
-        <v>179.2857142857143</v>
+        <v>184.3809523809524</v>
       </c>
       <c r="AY121" t="n">
         <v>1</v>
       </c>
       <c r="AZ121" t="n">
-        <v>69.57142857142857</v>
+        <v>63.80952380952381</v>
       </c>
       <c r="BA121" t="n">
-        <v>2659523.80952381</v>
+        <v>1308809.523809524</v>
       </c>
       <c r="BB121" t="n">
-        <v>74.23809523809524</v>
+        <v>70.0952380952381</v>
       </c>
       <c r="BC121" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="BD121" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="BE121" t="n">
         <v>1</v>
       </c>
       <c r="BF121" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BG121" t="n">
-        <v>65</v>
+        <v>402</v>
       </c>
       <c r="BH121" t="n">
-        <v>700000</v>
+        <v>7000000</v>
       </c>
       <c r="BI121" t="n">
-        <v>65</v>
+        <v>415</v>
       </c>
       <c r="BJ121" t="n">
-        <v>22</v>
+        <v>24.75</v>
       </c>
       <c r="BK121" t="n">
-        <v>178</v>
+        <v>184.125</v>
       </c>
       <c r="BL121" t="n">
         <v>1</v>
       </c>
       <c r="BM121" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BN121" t="n">
-        <v>74</v>
+        <v>553</v>
       </c>
       <c r="BO121" t="n">
-        <v>9500000</v>
+        <v>16475000</v>
       </c>
       <c r="BP121" t="n">
-        <v>83</v>
+        <v>586</v>
       </c>
     </row>
     <row r="122">
@@ -27122,7 +27122,7 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>46hrDJlP</t>
+          <t>21EalzCO</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
@@ -27130,76 +27130,76 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">linington j 
+          <t xml:space="preserve">simpson j 
   eng </t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>27137</v>
+        <v>33280</v>
       </c>
       <c r="F136" t="n">
-        <v>26429</v>
+        <v>22999</v>
       </c>
       <c r="G136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>6F0lvLNC</t>
         </is>
       </c>
       <c r="K136" t="n">
-        <v>2.99</v>
+        <v>1.74</v>
       </c>
       <c r="L136" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M136" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N136" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="O136" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="P136" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q136" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S136" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T136" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>OS3AwgCU</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>tMUvLt7h</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="W136" t="n">
@@ -27218,133 +27218,133 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="AE136" t="n">
-        <v>25.9</v>
+        <v>26.3</v>
       </c>
       <c r="AF136" t="n">
-        <v>182.5</v>
+        <v>182.7</v>
       </c>
       <c r="AG136" t="n">
         <v>1</v>
       </c>
       <c r="AH136" t="n">
-        <v>72.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="AI136" t="n">
-        <v>3470000</v>
+        <v>1870000</v>
       </c>
       <c r="AJ136" t="n">
-        <v>75</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AK136" t="n">
-        <v>24.75</v>
+        <v>24.2</v>
       </c>
       <c r="AL136" t="n">
-        <v>179.875</v>
+        <v>183.4</v>
       </c>
       <c r="AM136" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AN136" t="n">
-        <v>69.125</v>
+        <v>69.5</v>
       </c>
       <c r="AO136" t="n">
-        <v>1937500</v>
+        <v>2385000</v>
       </c>
       <c r="AP136" t="n">
-        <v>73.75</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AQ136" t="n">
-        <v>27.05882352941176</v>
+        <v>24.55555555555556</v>
       </c>
       <c r="AR136" t="n">
-        <v>185.3529411764706</v>
+        <v>179.8333333333333</v>
       </c>
       <c r="AS136" t="n">
         <v>1</v>
       </c>
       <c r="AT136" t="n">
-        <v>69.94117647058823</v>
+        <v>63.22222222222222</v>
       </c>
       <c r="AU136" t="n">
-        <v>2207352.94117647</v>
+        <v>1038055.555555556</v>
       </c>
       <c r="AV136" t="n">
-        <v>73.11764705882354</v>
+        <v>68.77777777777777</v>
       </c>
       <c r="AW136" t="n">
-        <v>24.66666666666667</v>
+        <v>21.875</v>
       </c>
       <c r="AX136" t="n">
-        <v>180.2777777777778</v>
+        <v>178</v>
       </c>
       <c r="AY136" t="n">
         <v>1</v>
       </c>
       <c r="AZ136" t="n">
-        <v>67.88888888888889</v>
+        <v>65.125</v>
       </c>
       <c r="BA136" t="n">
-        <v>1637500</v>
+        <v>1709375</v>
       </c>
       <c r="BB136" t="n">
-        <v>72.55555555555556</v>
+        <v>74.25</v>
       </c>
       <c r="BC136" t="n">
-        <v>25.66666666666667</v>
+        <v>24.8</v>
       </c>
       <c r="BD136" t="n">
-        <v>176</v>
+        <v>184.7</v>
       </c>
       <c r="BE136" t="n">
         <v>1</v>
       </c>
       <c r="BF136" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BG136" t="n">
-        <v>209</v>
+        <v>692</v>
       </c>
       <c r="BH136" t="n">
-        <v>6000000</v>
+        <v>19875000</v>
       </c>
       <c r="BI136" t="n">
-        <v>219</v>
+        <v>729</v>
       </c>
       <c r="BJ136" t="n">
-        <v>28.5</v>
+        <v>24.42857142857143</v>
       </c>
       <c r="BK136" t="n">
-        <v>175.25</v>
+        <v>184.7142857142857</v>
       </c>
       <c r="BL136" t="n">
         <v>1</v>
       </c>
       <c r="BM136" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BN136" t="n">
-        <v>269</v>
+        <v>497</v>
       </c>
       <c r="BO136" t="n">
-        <v>3900000</v>
+        <v>21100000</v>
       </c>
       <c r="BP136" t="n">
-        <v>281</v>
+        <v>534</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>21EalzCO</t>
+          <t>WQHRStSj</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
@@ -27352,76 +27352,76 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">simpson j 
+          <t xml:space="preserve">scott g 
   eng </t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">hillsborough
+  sheffield </t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>33280</v>
+        <v>39732</v>
       </c>
       <c r="F137" t="n">
-        <v>22999</v>
+        <v>33295</v>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H137" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>llcCvIcG</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>6F0lvLNC</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="K137" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="L137" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="M137" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="N137" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="O137" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P137" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q137" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S137" t="n">
         <v>7</v>
       </c>
       <c r="T137" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>OEy2L7Zo</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>phM8NElP</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="W137" t="n">
@@ -27438,129 +27438,121 @@
       </c>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr"/>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
+      <c r="AC137" t="inlineStr"/>
+      <c r="AD137" t="inlineStr"/>
       <c r="AE137" t="n">
-        <v>26.3</v>
+        <v>27.2</v>
       </c>
       <c r="AF137" t="n">
-        <v>182.7</v>
+        <v>182.1</v>
       </c>
       <c r="AG137" t="n">
         <v>1</v>
       </c>
       <c r="AH137" t="n">
-        <v>69</v>
+        <v>67.7</v>
       </c>
       <c r="AI137" t="n">
-        <v>1870000</v>
+        <v>1260000</v>
       </c>
       <c r="AJ137" t="n">
-        <v>71.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="AK137" t="n">
-        <v>24.2</v>
+        <v>28.9</v>
       </c>
       <c r="AL137" t="n">
-        <v>183.4</v>
+        <v>185.8</v>
       </c>
       <c r="AM137" t="n">
         <v>1.1</v>
       </c>
       <c r="AN137" t="n">
-        <v>69.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AO137" t="n">
-        <v>2385000</v>
+        <v>2550000</v>
       </c>
       <c r="AP137" t="n">
-        <v>75.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="AQ137" t="n">
-        <v>24.55555555555556</v>
+        <v>25.56521739130435</v>
       </c>
       <c r="AR137" t="n">
-        <v>179.8333333333333</v>
+        <v>185.5652173913043</v>
       </c>
       <c r="AS137" t="n">
         <v>1</v>
       </c>
       <c r="AT137" t="n">
-        <v>63.22222222222222</v>
+        <v>66.65217391304348</v>
       </c>
       <c r="AU137" t="n">
-        <v>1038055.555555556</v>
+        <v>1218478.260869565</v>
       </c>
       <c r="AV137" t="n">
-        <v>68.77777777777777</v>
+        <v>70.69565217391305</v>
       </c>
       <c r="AW137" t="n">
-        <v>21.875</v>
+        <v>26.78260869565218</v>
       </c>
       <c r="AX137" t="n">
-        <v>178</v>
+        <v>182.8695652173913</v>
       </c>
       <c r="AY137" t="n">
-        <v>1</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AZ137" t="n">
-        <v>65.125</v>
+        <v>70.08695652173913</v>
       </c>
       <c r="BA137" t="n">
-        <v>1709375</v>
+        <v>2165217.391304348</v>
       </c>
       <c r="BB137" t="n">
-        <v>74.25</v>
+        <v>72.69565217391305</v>
       </c>
       <c r="BC137" t="n">
-        <v>24.8</v>
+        <v>26.5</v>
       </c>
       <c r="BD137" t="n">
-        <v>184.7</v>
+        <v>172</v>
       </c>
       <c r="BE137" t="n">
         <v>1</v>
       </c>
       <c r="BF137" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BG137" t="n">
-        <v>692</v>
+        <v>137</v>
       </c>
       <c r="BH137" t="n">
-        <v>19875000</v>
+        <v>3100000</v>
       </c>
       <c r="BI137" t="n">
-        <v>729</v>
+        <v>142</v>
       </c>
       <c r="BJ137" t="n">
-        <v>24.42857142857143</v>
+        <v>23</v>
       </c>
       <c r="BK137" t="n">
-        <v>184.7142857142857</v>
+        <v>182</v>
       </c>
       <c r="BL137" t="n">
         <v>1</v>
       </c>
       <c r="BM137" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BN137" t="n">
-        <v>497</v>
+        <v>140</v>
       </c>
       <c r="BO137" t="n">
-        <v>21100000</v>
+        <v>4700000</v>
       </c>
       <c r="BP137" t="n">
-        <v>534</v>
+        <v>151</v>
       </c>
     </row>
     <row r="138">
@@ -28438,7 +28430,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>nsKknJaB</t>
+          <t>46hrDJlP</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
@@ -28446,83 +28438,83 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">linington j 
   eng </t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>31750</v>
+        <v>27137</v>
       </c>
       <c r="F142" t="n">
-        <v>31531</v>
+        <v>26429</v>
       </c>
       <c r="G142" t="n">
         <v>2</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>SlybbadF</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>1.17</v>
+        <v>2.99</v>
       </c>
       <c r="L142" t="n">
-        <v>0.45</v>
+        <v>1.56</v>
       </c>
       <c r="M142" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="N142" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="O142" t="n">
+        <v>27</v>
+      </c>
+      <c r="P142" t="n">
         <v>13</v>
       </c>
-      <c r="P142" t="n">
-        <v>9</v>
-      </c>
       <c r="Q142" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R142" t="n">
         <v>6</v>
       </c>
       <c r="S142" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T142" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>MBpIn2MH</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="W142" t="n">
         <v>48</v>
       </c>
       <c r="X142" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="Y142" t="n">
         <v>0</v>
@@ -28532,131 +28524,135 @@
       </c>
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr"/>
-      <c r="AC142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="AE142" t="n">
-        <v>26.33333333333333</v>
+        <v>25.9</v>
       </c>
       <c r="AF142" t="n">
-        <v>182.7777777777778</v>
+        <v>182.5</v>
       </c>
       <c r="AG142" t="n">
-        <v>1.444444444444444</v>
+        <v>1</v>
       </c>
       <c r="AH142" t="n">
-        <v>76.77777777777777</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AI142" t="n">
-        <v>12888888.88888889</v>
+        <v>3470000</v>
       </c>
       <c r="AJ142" t="n">
-        <v>79.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="AK142" t="n">
-        <v>25.36363636363636</v>
+        <v>24.75</v>
       </c>
       <c r="AL142" t="n">
-        <v>184.2727272727273</v>
+        <v>179.875</v>
       </c>
       <c r="AM142" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AN142" t="n">
-        <v>72.27272727272727</v>
+        <v>69.125</v>
       </c>
       <c r="AO142" t="n">
-        <v>3927272.727272727</v>
+        <v>1937500</v>
       </c>
       <c r="AP142" t="n">
-        <v>76</v>
+        <v>73.75</v>
       </c>
       <c r="AQ142" t="n">
-        <v>24.09090909090909</v>
+        <v>27.05882352941176</v>
       </c>
       <c r="AR142" t="n">
-        <v>179.9090909090909</v>
+        <v>185.3529411764706</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.363636363636364</v>
+        <v>1</v>
       </c>
       <c r="AT142" t="n">
-        <v>72.36363636363636</v>
+        <v>69.94117647058823</v>
       </c>
       <c r="AU142" t="n">
-        <v>8129545.454545454</v>
+        <v>2207352.94117647</v>
       </c>
       <c r="AV142" t="n">
-        <v>78.81818181818181</v>
+        <v>73.11764705882354</v>
       </c>
       <c r="AW142" t="n">
-        <v>28.0625</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="AX142" t="n">
-        <v>183.3125</v>
+        <v>180.2777777777778</v>
       </c>
       <c r="AY142" t="n">
-        <v>1.1875</v>
+        <v>1</v>
       </c>
       <c r="AZ142" t="n">
-        <v>71.125</v>
+        <v>67.88888888888889</v>
       </c>
       <c r="BA142" t="n">
-        <v>2609375</v>
+        <v>1637500</v>
       </c>
       <c r="BB142" t="n">
-        <v>72.3125</v>
+        <v>72.55555555555556</v>
       </c>
       <c r="BC142" t="n">
-        <v>26.25</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="BD142" t="n">
-        <v>180.5</v>
+        <v>176</v>
       </c>
       <c r="BE142" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BF142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>209</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>219</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>175.25</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM142" t="n">
         <v>4</v>
       </c>
-      <c r="BG142" t="n">
-        <v>308</v>
-      </c>
-      <c r="BH142" t="n">
-        <v>52500000</v>
-      </c>
-      <c r="BI142" t="n">
-        <v>321</v>
-      </c>
-      <c r="BJ142" t="n">
-        <v>26.625</v>
-      </c>
-      <c r="BK142" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="BL142" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM142" t="n">
-        <v>8</v>
-      </c>
       <c r="BN142" t="n">
-        <v>574</v>
+        <v>269</v>
       </c>
       <c r="BO142" t="n">
-        <v>24900000</v>
+        <v>3900000</v>
       </c>
       <c r="BP142" t="n">
-        <v>590</v>
+        <v>281</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>4bSYk10n</t>
+          <t>nsKknJaB</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
@@ -28664,76 +28660,76 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>52305</v>
+        <v>31750</v>
       </c>
       <c r="F143" t="n">
-        <v>52196</v>
+        <v>31531</v>
       </c>
       <c r="G143" t="n">
+        <v>2</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M143" t="n">
+        <v>58</v>
+      </c>
+      <c r="N143" t="n">
+        <v>42</v>
+      </c>
+      <c r="O143" t="n">
+        <v>13</v>
+      </c>
+      <c r="P143" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q143" t="n">
         <v>5</v>
       </c>
-      <c r="H143" t="n">
-        <v>1</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>MeKPSerA</t>
-        </is>
-      </c>
-      <c r="K143" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="L143" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M143" t="n">
-        <v>59</v>
-      </c>
-      <c r="N143" t="n">
-        <v>41</v>
-      </c>
-      <c r="O143" t="n">
-        <v>20</v>
-      </c>
-      <c r="P143" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>7</v>
-      </c>
       <c r="R143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S143" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T143" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="W143" t="n">
@@ -28750,110 +28746,110 @@
       </c>
       <c r="AA143" t="inlineStr"/>
       <c r="AB143" t="inlineStr"/>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
       <c r="AE143" t="n">
-        <v>25.7</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AF143" t="n">
-        <v>185</v>
+        <v>182.7777777777778</v>
       </c>
       <c r="AG143" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>12888888.88888889</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>79.66666666666667</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>184.2727272727273</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>3927272.727272727</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>76</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>179.9090909090909</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>72.36363636363636</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>8129545.454545454</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>78.81818181818181</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>28.0625</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>183.3125</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>2609375</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>72.3125</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BE143" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH143" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="AI143" t="n">
-        <v>18970000</v>
-      </c>
-      <c r="AJ143" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AK143" t="n">
-        <v>24.09090909090909</v>
-      </c>
-      <c r="AL143" t="n">
-        <v>181.8181818181818</v>
-      </c>
-      <c r="AM143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN143" t="n">
-        <v>71.09090909090909</v>
-      </c>
-      <c r="AO143" t="n">
-        <v>3847727.272727273</v>
-      </c>
-      <c r="AP143" t="n">
-        <v>76.72727272727273</v>
-      </c>
-      <c r="AQ143" t="n">
-        <v>26.08333333333333</v>
-      </c>
-      <c r="AR143" t="n">
-        <v>182.3333333333333</v>
-      </c>
-      <c r="AS143" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AT143" t="n">
-        <v>72.75</v>
-      </c>
-      <c r="AU143" t="n">
-        <v>9826041.666666666</v>
-      </c>
-      <c r="AV143" t="n">
-        <v>77.75</v>
-      </c>
-      <c r="AW143" t="n">
-        <v>23.22222222222222</v>
-      </c>
-      <c r="AX143" t="n">
-        <v>179.5555555555555</v>
-      </c>
-      <c r="AY143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ143" t="n">
-        <v>68.55555555555556</v>
-      </c>
-      <c r="BA143" t="n">
-        <v>3094444.444444444</v>
-      </c>
-      <c r="BB143" t="n">
-        <v>75.88888888888889</v>
-      </c>
-      <c r="BC143" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="BD143" t="n">
-        <v>185.1111111111111</v>
-      </c>
-      <c r="BE143" t="n">
-        <v>1.888888888888889</v>
-      </c>
       <c r="BF143" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BG143" t="n">
-        <v>721</v>
+        <v>308</v>
       </c>
       <c r="BH143" t="n">
-        <v>262600000</v>
+        <v>52500000</v>
       </c>
       <c r="BI143" t="n">
-        <v>744</v>
+        <v>321</v>
       </c>
       <c r="BJ143" t="n">
-        <v>25.75</v>
+        <v>26.625</v>
       </c>
       <c r="BK143" t="n">
-        <v>182</v>
+        <v>182.5</v>
       </c>
       <c r="BL143" t="n">
         <v>1</v>
@@ -28862,19 +28858,19 @@
         <v>8</v>
       </c>
       <c r="BN143" t="n">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="BO143" t="n">
-        <v>17700000</v>
+        <v>24900000</v>
       </c>
       <c r="BP143" t="n">
-        <v>599</v>
+        <v>590</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>WQHRStSj</t>
+          <t>4bSYk10n</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
@@ -28882,83 +28878,83 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">scott g 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">hillsborough
-  sheffield </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>39732</v>
+        <v>52305</v>
       </c>
       <c r="F144" t="n">
-        <v>33295</v>
+        <v>52196</v>
       </c>
       <c r="G144" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>llcCvIcG</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>MeKPSerA</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>1.79</v>
+        <v>2.43</v>
       </c>
       <c r="L144" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="M144" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="N144" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="O144" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="P144" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q144" t="n">
         <v>7</v>
       </c>
       <c r="R144" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S144" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T144" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>Y39YvFx6</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="W144" t="n">
         <v>48</v>
       </c>
       <c r="X144" t="n">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="Y144" t="n">
         <v>0</v>
@@ -28968,103 +28964,107 @@
       </c>
       <c r="AA144" t="inlineStr"/>
       <c r="AB144" t="inlineStr"/>
-      <c r="AC144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
       <c r="AD144" t="inlineStr"/>
       <c r="AE144" t="n">
-        <v>27.2</v>
+        <v>25.7</v>
       </c>
       <c r="AF144" t="n">
-        <v>182.1</v>
+        <v>185</v>
       </c>
       <c r="AG144" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AH144" t="n">
-        <v>67.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AI144" t="n">
-        <v>1260000</v>
+        <v>18970000</v>
       </c>
       <c r="AJ144" t="n">
-        <v>70.3</v>
+        <v>81.5</v>
       </c>
       <c r="AK144" t="n">
-        <v>28.9</v>
+        <v>24.09090909090909</v>
       </c>
       <c r="AL144" t="n">
-        <v>185.8</v>
+        <v>181.8181818181818</v>
       </c>
       <c r="AM144" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AN144" t="n">
-        <v>72.09999999999999</v>
+        <v>71.09090909090909</v>
       </c>
       <c r="AO144" t="n">
-        <v>2550000</v>
+        <v>3847727.272727273</v>
       </c>
       <c r="AP144" t="n">
-        <v>72.7</v>
+        <v>76.72727272727273</v>
       </c>
       <c r="AQ144" t="n">
-        <v>25.56521739130435</v>
+        <v>26.08333333333333</v>
       </c>
       <c r="AR144" t="n">
-        <v>185.5652173913043</v>
+        <v>182.3333333333333</v>
       </c>
       <c r="AS144" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AT144" t="n">
-        <v>66.65217391304348</v>
+        <v>72.75</v>
       </c>
       <c r="AU144" t="n">
-        <v>1218478.260869565</v>
+        <v>9826041.666666666</v>
       </c>
       <c r="AV144" t="n">
-        <v>70.69565217391305</v>
+        <v>77.75</v>
       </c>
       <c r="AW144" t="n">
-        <v>26.78260869565218</v>
+        <v>23.22222222222222</v>
       </c>
       <c r="AX144" t="n">
-        <v>182.8695652173913</v>
+        <v>179.5555555555555</v>
       </c>
       <c r="AY144" t="n">
-        <v>1.043478260869565</v>
+        <v>1</v>
       </c>
       <c r="AZ144" t="n">
-        <v>70.08695652173913</v>
+        <v>68.55555555555556</v>
       </c>
       <c r="BA144" t="n">
-        <v>2165217.391304348</v>
+        <v>3094444.444444444</v>
       </c>
       <c r="BB144" t="n">
-        <v>72.69565217391305</v>
+        <v>75.88888888888889</v>
       </c>
       <c r="BC144" t="n">
-        <v>26.5</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="BD144" t="n">
-        <v>172</v>
+        <v>185.1111111111111</v>
       </c>
       <c r="BE144" t="n">
-        <v>1</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="BF144" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BG144" t="n">
-        <v>137</v>
+        <v>721</v>
       </c>
       <c r="BH144" t="n">
-        <v>3100000</v>
+        <v>262600000</v>
       </c>
       <c r="BI144" t="n">
-        <v>142</v>
+        <v>744</v>
       </c>
       <c r="BJ144" t="n">
-        <v>23</v>
+        <v>25.75</v>
       </c>
       <c r="BK144" t="n">
         <v>182</v>
@@ -29073,16 +29073,16 @@
         <v>1</v>
       </c>
       <c r="BM144" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN144" t="n">
-        <v>140</v>
+        <v>562</v>
       </c>
       <c r="BO144" t="n">
-        <v>4700000</v>
+        <v>17700000</v>
       </c>
       <c r="BP144" t="n">
-        <v>151</v>
+        <v>599</v>
       </c>
     </row>
     <row r="145">
@@ -30852,7 +30852,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>QDlmloU5</t>
+          <t>4jI7yxbf</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
@@ -30860,21 +30860,21 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">madley r 
   eng </t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">emirates stadium
-  london </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>60704</v>
+        <v>32261</v>
       </c>
       <c r="F153" t="n">
-        <v>60238</v>
+        <v>31872</v>
       </c>
       <c r="G153" t="n">
         <v>5</v>
@@ -30884,59 +30884,59 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="K153" t="n">
-        <v>3.41</v>
+        <v>1.76</v>
       </c>
       <c r="L153" t="n">
-        <v>1.66</v>
+        <v>0.37</v>
       </c>
       <c r="M153" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="N153" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="O153" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="P153" t="n">
         <v>7</v>
       </c>
       <c r="Q153" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T153" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>zuJM7XDg</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="W153" t="n">
         <v>48</v>
       </c>
       <c r="X153" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="Y153" t="n">
         <v>0</v>
@@ -30948,85 +30948,81 @@
       <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr"/>
       <c r="AE153" t="n">
-        <v>24.25</v>
+        <v>26.9</v>
       </c>
       <c r="AF153" t="n">
-        <v>183.625</v>
+        <v>182.9</v>
       </c>
       <c r="AG153" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH153" t="n">
-        <v>83.625</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AI153" t="n">
-        <v>61562500</v>
+        <v>10470000</v>
       </c>
       <c r="AJ153" t="n">
-        <v>86.625</v>
+        <v>78.5</v>
       </c>
       <c r="AK153" t="n">
-        <v>22.22222222222222</v>
+        <v>25.63636363636364</v>
       </c>
       <c r="AL153" t="n">
-        <v>182.1111111111111</v>
+        <v>182.3636363636364</v>
       </c>
       <c r="AM153" t="n">
-        <v>1.777777777777778</v>
+        <v>1</v>
       </c>
       <c r="AN153" t="n">
-        <v>76.88888888888889</v>
+        <v>72.45454545454545</v>
       </c>
       <c r="AO153" t="n">
-        <v>22800000</v>
+        <v>4181818.181818182</v>
       </c>
       <c r="AP153" t="n">
-        <v>83.44444444444444</v>
+        <v>75.36363636363636</v>
       </c>
       <c r="AQ153" t="n">
-        <v>25.04545454545455</v>
+        <v>25.36842105263158</v>
       </c>
       <c r="AR153" t="n">
-        <v>179</v>
+        <v>181.0526315789474</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.772727272727273</v>
+        <v>1.421052631578947</v>
       </c>
       <c r="AT153" t="n">
-        <v>81.31818181818181</v>
+        <v>72.84210526315789</v>
       </c>
       <c r="AU153" t="n">
-        <v>36045454.54545455</v>
+        <v>5305263.157894737</v>
       </c>
       <c r="AV153" t="n">
-        <v>84.31818181818181</v>
+        <v>76.47368421052632</v>
       </c>
       <c r="AW153" t="n">
-        <v>25.10526315789474</v>
+        <v>24.45</v>
       </c>
       <c r="AX153" t="n">
-        <v>183.6315789473684</v>
+        <v>175.8</v>
       </c>
       <c r="AY153" t="n">
-        <v>2.052631578947369</v>
+        <v>1</v>
       </c>
       <c r="AZ153" t="n">
-        <v>74.42105263157895</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="BA153" t="n">
-        <v>12011842.10526316</v>
+        <v>3001250</v>
       </c>
       <c r="BB153" t="n">
-        <v>81.10526315789474</v>
+        <v>75.5</v>
       </c>
       <c r="BC153" t="inlineStr"/>
       <c r="BD153" t="inlineStr"/>
@@ -31036,31 +31032,31 @@
       <c r="BH153" t="inlineStr"/>
       <c r="BI153" t="inlineStr"/>
       <c r="BJ153" t="n">
-        <v>22.625</v>
+        <v>24.2</v>
       </c>
       <c r="BK153" t="n">
-        <v>183.625</v>
+        <v>180.6</v>
       </c>
       <c r="BL153" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BM153" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BN153" t="n">
-        <v>611</v>
+        <v>348</v>
       </c>
       <c r="BO153" t="n">
-        <v>174250000</v>
+        <v>13200000</v>
       </c>
       <c r="BP153" t="n">
-        <v>658</v>
+        <v>382</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>4jI7yxbf</t>
+          <t>QDlmloU5</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
@@ -31068,21 +31064,21 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley r 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
+          <t xml:space="preserve">emirates stadium
+  london </t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>32261</v>
+        <v>60704</v>
       </c>
       <c r="F154" t="n">
-        <v>31872</v>
+        <v>60238</v>
       </c>
       <c r="G154" t="n">
         <v>5</v>
@@ -31092,59 +31088,59 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="K154" t="n">
-        <v>1.76</v>
+        <v>3.41</v>
       </c>
       <c r="L154" t="n">
-        <v>0.37</v>
+        <v>1.66</v>
       </c>
       <c r="M154" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="N154" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="O154" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="P154" t="n">
         <v>7</v>
       </c>
       <c r="Q154" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S154" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T154" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="W154" t="n">
         <v>48</v>
       </c>
       <c r="X154" t="n">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="Y154" t="n">
         <v>0</v>
@@ -31156,81 +31152,85 @@
       <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr"/>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
       <c r="AE154" t="n">
-        <v>26.9</v>
+        <v>24.25</v>
       </c>
       <c r="AF154" t="n">
-        <v>182.9</v>
+        <v>183.625</v>
       </c>
       <c r="AG154" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH154" t="n">
-        <v>76.59999999999999</v>
+        <v>83.625</v>
       </c>
       <c r="AI154" t="n">
-        <v>10470000</v>
+        <v>61562500</v>
       </c>
       <c r="AJ154" t="n">
-        <v>78.5</v>
+        <v>86.625</v>
       </c>
       <c r="AK154" t="n">
-        <v>25.63636363636364</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AL154" t="n">
-        <v>182.3636363636364</v>
+        <v>182.1111111111111</v>
       </c>
       <c r="AM154" t="n">
-        <v>1</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AN154" t="n">
-        <v>72.45454545454545</v>
+        <v>76.88888888888889</v>
       </c>
       <c r="AO154" t="n">
-        <v>4181818.181818182</v>
+        <v>22800000</v>
       </c>
       <c r="AP154" t="n">
-        <v>75.36363636363636</v>
+        <v>83.44444444444444</v>
       </c>
       <c r="AQ154" t="n">
-        <v>25.36842105263158</v>
+        <v>25.04545454545455</v>
       </c>
       <c r="AR154" t="n">
-        <v>181.0526315789474</v>
+        <v>179</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.421052631578947</v>
+        <v>1.772727272727273</v>
       </c>
       <c r="AT154" t="n">
-        <v>72.84210526315789</v>
+        <v>81.31818181818181</v>
       </c>
       <c r="AU154" t="n">
-        <v>5305263.157894737</v>
+        <v>36045454.54545455</v>
       </c>
       <c r="AV154" t="n">
-        <v>76.47368421052632</v>
+        <v>84.31818181818181</v>
       </c>
       <c r="AW154" t="n">
-        <v>24.45</v>
+        <v>25.10526315789474</v>
       </c>
       <c r="AX154" t="n">
-        <v>175.8</v>
+        <v>183.6315789473684</v>
       </c>
       <c r="AY154" t="n">
-        <v>1</v>
+        <v>2.052631578947369</v>
       </c>
       <c r="AZ154" t="n">
-        <v>69.84999999999999</v>
+        <v>74.42105263157895</v>
       </c>
       <c r="BA154" t="n">
-        <v>3001250</v>
+        <v>12011842.10526316</v>
       </c>
       <c r="BB154" t="n">
-        <v>75.5</v>
+        <v>81.10526315789474</v>
       </c>
       <c r="BC154" t="inlineStr"/>
       <c r="BD154" t="inlineStr"/>
@@ -31240,247 +31240,25 @@
       <c r="BH154" t="inlineStr"/>
       <c r="BI154" t="inlineStr"/>
       <c r="BJ154" t="n">
-        <v>24.2</v>
+        <v>22.625</v>
       </c>
       <c r="BK154" t="n">
-        <v>180.6</v>
+        <v>183.625</v>
       </c>
       <c r="BL154" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BM154" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN154" t="n">
-        <v>348</v>
+        <v>611</v>
       </c>
       <c r="BO154" t="n">
-        <v>13200000</v>
+        <v>174250000</v>
       </c>
       <c r="BP154" t="n">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="1" t="inlineStr">
-        <is>
-          <t>hCE5NojB</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="n">
-        <v>45404.66666666666</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">harrington t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">riverside stadium
-  middlesbrough </t>
-        </is>
-      </c>
-      <c r="E155" t="n">
-        <v>34742</v>
-      </c>
-      <c r="F155" t="n">
-        <v>29333</v>
-      </c>
-      <c r="G155" t="n">
-        <v>3</v>
-      </c>
-      <c r="H155" t="n">
-        <v>4</v>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>6F0lvLNC</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="K155" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="L155" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M155" t="n">
-        <v>67</v>
-      </c>
-      <c r="N155" t="n">
-        <v>33</v>
-      </c>
-      <c r="O155" t="n">
-        <v>13</v>
-      </c>
-      <c r="P155" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>5</v>
-      </c>
-      <c r="R155" t="n">
-        <v>5</v>
-      </c>
-      <c r="S155" t="n">
-        <v>14</v>
-      </c>
-      <c r="T155" t="n">
-        <v>11</v>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
-      <c r="W155" t="n">
-        <v>48</v>
-      </c>
-      <c r="X155" t="n">
-        <v>485</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z155" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="AA155" t="inlineStr"/>
-      <c r="AB155" t="inlineStr"/>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>xxxpBZl2</t>
-        </is>
-      </c>
-      <c r="AE155" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AF155" t="n">
-        <v>181.1</v>
-      </c>
-      <c r="AG155" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH155" t="n">
-        <v>70</v>
-      </c>
-      <c r="AI155" t="n">
-        <v>2660000</v>
-      </c>
-      <c r="AJ155" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="AK155" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL155" t="n">
-        <v>185.2222222222222</v>
-      </c>
-      <c r="AM155" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AN155" t="n">
-        <v>74.22222222222223</v>
-      </c>
-      <c r="AO155" t="n">
-        <v>8588888.888888888</v>
-      </c>
-      <c r="AP155" t="n">
-        <v>80.55555555555556</v>
-      </c>
-      <c r="AQ155" t="n">
-        <v>22.86666666666667</v>
-      </c>
-      <c r="AR155" t="n">
-        <v>181.2666666666667</v>
-      </c>
-      <c r="AS155" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT155" t="n">
-        <v>66.46666666666667</v>
-      </c>
-      <c r="AU155" t="n">
-        <v>1776666.666666667</v>
-      </c>
-      <c r="AV155" t="n">
-        <v>73.33333333333333</v>
-      </c>
-      <c r="AW155" t="n">
-        <v>24.84210526315789</v>
-      </c>
-      <c r="AX155" t="n">
-        <v>179.7894736842105</v>
-      </c>
-      <c r="AY155" t="n">
-        <v>1.052631578947368</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>73.57894736842105</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>6136842.105263158</v>
-      </c>
-      <c r="BB155" t="n">
-        <v>77.26315789473684</v>
-      </c>
-      <c r="BC155" t="n">
-        <v>24.42857142857143</v>
-      </c>
-      <c r="BD155" t="n">
-        <v>184.7142857142857</v>
-      </c>
-      <c r="BE155" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF155" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG155" t="n">
-        <v>497</v>
-      </c>
-      <c r="BH155" t="n">
-        <v>21100000</v>
-      </c>
-      <c r="BI155" t="n">
-        <v>534</v>
-      </c>
-      <c r="BJ155" t="n">
-        <v>21</v>
-      </c>
-      <c r="BK155" t="n">
-        <v>193</v>
-      </c>
-      <c r="BL155" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM155" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN155" t="n">
-        <v>137</v>
-      </c>
-      <c r="BO155" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="BP155" t="n">
-        <v>158</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
